--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50CA5E7-C346-4A90-9CEB-D704FCEE522A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65ECC8EA-2BDF-4393-8C80-C1CAF6AA937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="336">
   <si>
     <t>lang_code</t>
   </si>
@@ -150,9 +150,6 @@
     <t>fra</t>
   </si>
   <si>
-    <t>Center A Ben Mansour</t>
-  </si>
-  <si>
     <t>P4238</t>
   </si>
   <si>
@@ -174,9 +171,6 @@
     <t>RBT</t>
   </si>
   <si>
-    <t>Centre A Ben Mansour</t>
-  </si>
-  <si>
     <t>Maroc</t>
   </si>
   <si>
@@ -1036,6 +1030,9 @@
   </si>
   <si>
     <t>CSB</t>
+  </si>
+  <si>
+    <t>Barnabys Centre</t>
   </si>
 </sst>
 </file>
@@ -1126,9 +1123,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1166,7 +1163,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1272,7 +1269,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1414,7 +1411,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1664,16 +1661,16 @@
         <v>10001</v>
       </c>
       <c r="C4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
         <v>41</v>
       </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>42</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
       </c>
       <c r="G4" t="s">
         <v>29</v>
@@ -1691,22 +1688,22 @@
         <v>779517433</v>
       </c>
       <c r="L4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M4">
         <v>3</v>
       </c>
       <c r="N4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O4" t="s">
         <v>32</v>
       </c>
       <c r="P4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q4" t="s">
         <v>46</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>47</v>
       </c>
       <c r="R4" t="s">
         <v>35</v>
@@ -1721,7 +1718,7 @@
         <v>38</v>
       </c>
       <c r="V4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W4" s="1" t="s">
         <v>39</v>
@@ -1735,19 +1732,19 @@
         <v>10001</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>335</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
       </c>
       <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
         <v>42</v>
       </c>
-      <c r="F5" t="s">
-        <v>43</v>
-      </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H5">
         <v>34.521169999999998</v>
@@ -1762,22 +1759,22 @@
         <v>993556086</v>
       </c>
       <c r="L5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M5">
         <v>3</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O5" t="s">
         <v>32</v>
       </c>
       <c r="P5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q5" t="s">
         <v>46</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>47</v>
       </c>
       <c r="R5" t="s">
         <v>35</v>
@@ -1786,13 +1783,13 @@
         <v>36</v>
       </c>
       <c r="T5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U5" t="s">
         <v>38</v>
       </c>
       <c r="V5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W5" s="1" t="s">
         <v>39</v>
@@ -1806,16 +1803,16 @@
         <v>10002</v>
       </c>
       <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" t="s">
         <v>52</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
       </c>
       <c r="G6" t="s">
         <v>29</v>
@@ -1833,22 +1830,22 @@
         <v>753476995</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M6">
         <v>2</v>
       </c>
       <c r="N6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O6" t="s">
         <v>32</v>
       </c>
       <c r="P6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q6" t="s">
         <v>46</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>47</v>
       </c>
       <c r="R6" t="s">
         <v>35</v>
@@ -1877,19 +1874,19 @@
         <v>10002</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H7">
         <v>34.360207000000003</v>
@@ -1904,22 +1901,22 @@
         <v>984996886</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M7">
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O7" t="s">
         <v>32</v>
       </c>
       <c r="P7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q7" t="s">
         <v>46</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>47</v>
       </c>
       <c r="R7" t="s">
         <v>35</v>
@@ -1928,7 +1925,7 @@
         <v>36</v>
       </c>
       <c r="T7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U7" t="s">
         <v>38</v>
@@ -1948,16 +1945,16 @@
         <v>10003</v>
       </c>
       <c r="C8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s">
         <v>57</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>
@@ -1975,22 +1972,22 @@
         <v>734239083</v>
       </c>
       <c r="L8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M8">
         <v>4</v>
       </c>
       <c r="N8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O8" t="s">
         <v>32</v>
       </c>
       <c r="P8" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q8" t="s">
         <v>46</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>47</v>
       </c>
       <c r="R8" t="s">
         <v>35</v>
@@ -2005,7 +2002,7 @@
         <v>38</v>
       </c>
       <c r="V8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>39</v>
@@ -2019,19 +2016,19 @@
         <v>10003</v>
       </c>
       <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
         <v>57</v>
       </c>
-      <c r="D9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
       <c r="G9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H9">
         <v>34.405692000000002</v>
@@ -2046,22 +2043,22 @@
         <v>675470523</v>
       </c>
       <c r="L9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M9">
         <v>4</v>
       </c>
       <c r="N9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O9" t="s">
         <v>32</v>
       </c>
       <c r="P9" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q9" t="s">
         <v>46</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>47</v>
       </c>
       <c r="R9" t="s">
         <v>35</v>
@@ -2070,13 +2067,13 @@
         <v>36</v>
       </c>
       <c r="T9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U9" t="s">
         <v>38</v>
       </c>
       <c r="V9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>39</v>
@@ -2090,16 +2087,16 @@
         <v>10004</v>
       </c>
       <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" t="s">
         <v>63</v>
-      </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
@@ -2117,22 +2114,22 @@
         <v>937997757</v>
       </c>
       <c r="L10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M10">
         <v>2</v>
       </c>
       <c r="N10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O10" t="s">
         <v>32</v>
       </c>
       <c r="P10" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q10" t="s">
         <v>46</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>47</v>
       </c>
       <c r="R10" t="s">
         <v>35</v>
@@ -2147,7 +2144,7 @@
         <v>38</v>
       </c>
       <c r="V10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>39</v>
@@ -2161,19 +2158,19 @@
         <v>10004</v>
       </c>
       <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s">
         <v>67</v>
       </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H11">
         <v>34.287878999999997</v>
@@ -2188,22 +2185,22 @@
         <v>852492117</v>
       </c>
       <c r="L11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M11">
         <v>2</v>
       </c>
       <c r="N11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O11" t="s">
         <v>32</v>
       </c>
       <c r="P11" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q11" t="s">
         <v>46</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>47</v>
       </c>
       <c r="R11" t="s">
         <v>35</v>
@@ -2212,13 +2209,13 @@
         <v>36</v>
       </c>
       <c r="T11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U11" t="s">
         <v>38</v>
       </c>
       <c r="V11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>39</v>
@@ -2232,19 +2229,19 @@
         <v>10005</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H12">
         <v>34.256413999999999</v>
@@ -2259,22 +2256,22 @@
         <v>887311749</v>
       </c>
       <c r="L12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O12" t="s">
         <v>32</v>
       </c>
       <c r="P12" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q12" t="s">
         <v>46</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>47</v>
       </c>
       <c r="R12" t="s">
         <v>35</v>
@@ -2289,7 +2286,7 @@
         <v>38</v>
       </c>
       <c r="V12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>39</v>
@@ -2303,19 +2300,19 @@
         <v>10005</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H13">
         <v>34.256413999999999</v>
@@ -2330,22 +2327,22 @@
         <v>658302699</v>
       </c>
       <c r="L13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" t="s">
         <v>32</v>
       </c>
       <c r="P13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q13" t="s">
         <v>46</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>47</v>
       </c>
       <c r="R13" t="s">
         <v>35</v>
@@ -2354,13 +2351,13 @@
         <v>36</v>
       </c>
       <c r="T13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U13" t="s">
         <v>38</v>
       </c>
       <c r="V13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>39</v>
@@ -2374,19 +2371,19 @@
         <v>10006</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H14">
         <v>34.262476999999997</v>
@@ -2401,22 +2398,22 @@
         <v>915790305</v>
       </c>
       <c r="L14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M14">
         <v>5</v>
       </c>
       <c r="N14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O14" t="s">
         <v>32</v>
       </c>
       <c r="P14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q14" t="s">
         <v>46</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>47</v>
       </c>
       <c r="R14" t="s">
         <v>35</v>
@@ -2431,7 +2428,7 @@
         <v>38</v>
       </c>
       <c r="V14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>39</v>
@@ -2445,19 +2442,19 @@
         <v>10006</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H15">
         <v>34.262476999999997</v>
@@ -2472,22 +2469,22 @@
         <v>888439793</v>
       </c>
       <c r="L15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M15">
         <v>5</v>
       </c>
       <c r="N15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O15" t="s">
         <v>32</v>
       </c>
       <c r="P15" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q15" t="s">
         <v>46</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>47</v>
       </c>
       <c r="R15" t="s">
         <v>35</v>
@@ -2496,13 +2493,13 @@
         <v>36</v>
       </c>
       <c r="T15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U15" t="s">
         <v>38</v>
       </c>
       <c r="V15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>39</v>
@@ -2516,16 +2513,16 @@
         <v>10007</v>
       </c>
       <c r="C16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>80</v>
+      </c>
+      <c r="F16" t="s">
         <v>81</v>
-      </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" t="s">
-        <v>83</v>
       </c>
       <c r="G16" t="s">
         <v>29</v>
@@ -2543,22 +2540,22 @@
         <v>811552880</v>
       </c>
       <c r="L16" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M16">
         <v>2</v>
       </c>
       <c r="N16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O16" t="s">
         <v>32</v>
       </c>
       <c r="P16" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q16" t="s">
         <v>46</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>47</v>
       </c>
       <c r="R16" t="s">
         <v>35</v>
@@ -2573,7 +2570,7 @@
         <v>38</v>
       </c>
       <c r="V16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>39</v>
@@ -2587,19 +2584,19 @@
         <v>10007</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H17">
         <v>34.192861000000001</v>
@@ -2614,22 +2611,22 @@
         <v>753640112</v>
       </c>
       <c r="L17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M17">
         <v>2</v>
       </c>
       <c r="N17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O17" t="s">
         <v>32</v>
       </c>
       <c r="P17" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q17" t="s">
         <v>46</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>47</v>
       </c>
       <c r="R17" t="s">
         <v>35</v>
@@ -2638,13 +2635,13 @@
         <v>36</v>
       </c>
       <c r="T17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U17" t="s">
         <v>38</v>
       </c>
       <c r="V17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>39</v>
@@ -2658,16 +2655,16 @@
         <v>10008</v>
       </c>
       <c r="C18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" t="s">
         <v>88</v>
-      </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" t="s">
-        <v>89</v>
-      </c>
-      <c r="F18" t="s">
-        <v>90</v>
       </c>
       <c r="G18" t="s">
         <v>29</v>
@@ -2685,22 +2682,22 @@
         <v>695325692</v>
       </c>
       <c r="L18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M18">
         <v>2</v>
       </c>
       <c r="N18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O18" t="s">
         <v>32</v>
       </c>
       <c r="P18" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q18" t="s">
         <v>46</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>47</v>
       </c>
       <c r="R18" t="s">
         <v>35</v>
@@ -2715,7 +2712,7 @@
         <v>38</v>
       </c>
       <c r="V18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>39</v>
@@ -2729,19 +2726,19 @@
         <v>10008</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H19">
         <v>34.522413999999998</v>
@@ -2756,22 +2753,22 @@
         <v>862899075</v>
       </c>
       <c r="L19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M19">
         <v>2</v>
       </c>
       <c r="N19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O19" t="s">
         <v>32</v>
       </c>
       <c r="P19" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q19" t="s">
         <v>46</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>47</v>
       </c>
       <c r="R19" t="s">
         <v>35</v>
@@ -2780,13 +2777,13 @@
         <v>36</v>
       </c>
       <c r="T19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U19" t="s">
         <v>38</v>
       </c>
       <c r="V19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>39</v>
@@ -2800,16 +2797,16 @@
         <v>10009</v>
       </c>
       <c r="C20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
+        <v>94</v>
+      </c>
+      <c r="F20" t="s">
         <v>95</v>
-      </c>
-      <c r="D20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" t="s">
-        <v>97</v>
       </c>
       <c r="G20" t="s">
         <v>29</v>
@@ -2827,22 +2824,22 @@
         <v>745360421</v>
       </c>
       <c r="L20" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M20">
         <v>2</v>
       </c>
       <c r="N20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O20" t="s">
         <v>32</v>
       </c>
       <c r="P20" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q20" t="s">
         <v>46</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>47</v>
       </c>
       <c r="R20" t="s">
         <v>35</v>
@@ -2854,10 +2851,10 @@
         <v>37</v>
       </c>
       <c r="U20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V20" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>39</v>
@@ -2871,19 +2868,19 @@
         <v>10009</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
         <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H21">
         <v>33.998232000000002</v>
@@ -2898,22 +2895,22 @@
         <v>676186831</v>
       </c>
       <c r="L21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M21">
         <v>2</v>
       </c>
       <c r="N21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O21" t="s">
         <v>32</v>
       </c>
       <c r="P21" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q21" t="s">
         <v>46</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>47</v>
       </c>
       <c r="R21" t="s">
         <v>35</v>
@@ -2922,13 +2919,13 @@
         <v>36</v>
       </c>
       <c r="T21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>39</v>
@@ -2942,16 +2939,16 @@
         <v>10010</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D22" t="s">
         <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F22" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G22" t="s">
         <v>29</v>
@@ -2969,22 +2966,22 @@
         <v>766074745</v>
       </c>
       <c r="L22" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M22">
         <v>2</v>
       </c>
       <c r="N22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O22" t="s">
         <v>32</v>
       </c>
       <c r="P22" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q22" t="s">
         <v>46</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>47</v>
       </c>
       <c r="R22" t="s">
         <v>35</v>
@@ -2996,10 +2993,10 @@
         <v>37</v>
       </c>
       <c r="U22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V22" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>39</v>
@@ -3013,19 +3010,19 @@
         <v>10010</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
         <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G23" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H23">
         <v>34.017502</v>
@@ -3040,22 +3037,22 @@
         <v>773606891</v>
       </c>
       <c r="L23" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M23">
         <v>2</v>
       </c>
       <c r="N23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O23" t="s">
         <v>32</v>
       </c>
       <c r="P23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q23" t="s">
         <v>46</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>47</v>
       </c>
       <c r="R23" t="s">
         <v>35</v>
@@ -3064,13 +3061,13 @@
         <v>36</v>
       </c>
       <c r="T23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V23" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>39</v>
@@ -3084,16 +3081,16 @@
         <v>10011</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
         <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G24" t="s">
         <v>29</v>
@@ -3111,22 +3108,22 @@
         <v>787248921</v>
       </c>
       <c r="L24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M24">
         <v>2</v>
       </c>
       <c r="N24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O24" t="s">
         <v>32</v>
       </c>
       <c r="P24" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q24" t="s">
         <v>46</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>47</v>
       </c>
       <c r="R24" t="s">
         <v>35</v>
@@ -3138,10 +3135,10 @@
         <v>37</v>
       </c>
       <c r="U24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W24" s="1" t="s">
         <v>39</v>
@@ -3155,19 +3152,19 @@
         <v>10011</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
         <v>26</v>
       </c>
       <c r="E25" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H25">
         <v>33.986607999999997</v>
@@ -3182,22 +3179,22 @@
         <v>878691008</v>
       </c>
       <c r="L25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M25">
         <v>2</v>
       </c>
       <c r="N25" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O25" t="s">
         <v>32</v>
       </c>
       <c r="P25" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q25" t="s">
         <v>46</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>47</v>
       </c>
       <c r="R25" t="s">
         <v>35</v>
@@ -3206,13 +3203,13 @@
         <v>36</v>
       </c>
       <c r="T25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W25" s="1" t="s">
         <v>39</v>
@@ -3226,16 +3223,16 @@
         <v>10012</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D26" t="s">
         <v>26</v>
       </c>
       <c r="E26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G26" t="s">
         <v>29</v>
@@ -3253,22 +3250,22 @@
         <v>838412388</v>
       </c>
       <c r="L26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M26">
         <v>2</v>
       </c>
       <c r="N26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O26" t="s">
         <v>32</v>
       </c>
       <c r="P26" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q26" t="s">
         <v>46</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>47</v>
       </c>
       <c r="R26" t="s">
         <v>35</v>
@@ -3280,10 +3277,10 @@
         <v>37</v>
       </c>
       <c r="U26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W26" s="1" t="s">
         <v>39</v>
@@ -3297,19 +3294,19 @@
         <v>10012</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
         <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G27" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H27">
         <v>33.978102999999997</v>
@@ -3324,22 +3321,22 @@
         <v>719952201</v>
       </c>
       <c r="L27" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M27">
         <v>2</v>
       </c>
       <c r="N27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O27" t="s">
         <v>32</v>
       </c>
       <c r="P27" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q27" t="s">
         <v>46</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>47</v>
       </c>
       <c r="R27" t="s">
         <v>35</v>
@@ -3348,13 +3345,13 @@
         <v>36</v>
       </c>
       <c r="T27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V27" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W27" s="1" t="s">
         <v>39</v>
@@ -3368,16 +3365,16 @@
         <v>10013</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
         <v>26</v>
       </c>
       <c r="E28" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F28" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G28" t="s">
         <v>29</v>
@@ -3395,22 +3392,22 @@
         <v>751913644</v>
       </c>
       <c r="L28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M28">
         <v>2</v>
       </c>
       <c r="N28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O28" t="s">
         <v>32</v>
       </c>
       <c r="P28" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q28" t="s">
         <v>46</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>47</v>
       </c>
       <c r="R28" t="s">
         <v>35</v>
@@ -3422,10 +3419,10 @@
         <v>37</v>
       </c>
       <c r="U28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V28" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>39</v>
@@ -3439,19 +3436,19 @@
         <v>10013</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
         <v>26</v>
       </c>
       <c r="E29" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H29">
         <v>33.953930999999997</v>
@@ -3466,22 +3463,22 @@
         <v>956537434</v>
       </c>
       <c r="L29" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M29">
         <v>2</v>
       </c>
       <c r="N29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O29" t="s">
         <v>32</v>
       </c>
       <c r="P29" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q29" t="s">
         <v>46</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>47</v>
       </c>
       <c r="R29" t="s">
         <v>35</v>
@@ -3490,13 +3487,13 @@
         <v>36</v>
       </c>
       <c r="T29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V29" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W29" s="1" t="s">
         <v>39</v>
@@ -3510,16 +3507,16 @@
         <v>10014</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s">
         <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G30" t="s">
         <v>29</v>
@@ -3537,22 +3534,22 @@
         <v>965639376</v>
       </c>
       <c r="L30" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M30">
         <v>2</v>
       </c>
       <c r="N30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O30" t="s">
         <v>32</v>
       </c>
       <c r="P30" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q30" t="s">
         <v>46</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>47</v>
       </c>
       <c r="R30" t="s">
         <v>35</v>
@@ -3564,10 +3561,10 @@
         <v>37</v>
       </c>
       <c r="U30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V30" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="W30" s="1" t="s">
         <v>39</v>
@@ -3581,19 +3578,19 @@
         <v>10014</v>
       </c>
       <c r="C31" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F31" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H31">
         <v>34.027757000000001</v>
@@ -3608,22 +3605,22 @@
         <v>781039430</v>
       </c>
       <c r="L31" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M31">
         <v>2</v>
       </c>
       <c r="N31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O31" t="s">
         <v>32</v>
       </c>
       <c r="P31" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q31" t="s">
         <v>46</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>47</v>
       </c>
       <c r="R31" t="s">
         <v>35</v>
@@ -3632,13 +3629,13 @@
         <v>36</v>
       </c>
       <c r="T31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V31" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>39</v>
@@ -3652,16 +3649,16 @@
         <v>10015</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
       </c>
       <c r="E32" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G32" t="s">
         <v>29</v>
@@ -3679,22 +3676,22 @@
         <v>803062069</v>
       </c>
       <c r="L32" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M32">
         <v>2</v>
       </c>
       <c r="N32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O32" t="s">
         <v>32</v>
       </c>
       <c r="P32" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q32" t="s">
         <v>46</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>47</v>
       </c>
       <c r="R32" t="s">
         <v>35</v>
@@ -3706,10 +3703,10 @@
         <v>37</v>
       </c>
       <c r="U32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>39</v>
@@ -3723,19 +3720,19 @@
         <v>10015</v>
       </c>
       <c r="C33" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
         <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G33" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H33">
         <v>33.995612000000001</v>
@@ -3750,22 +3747,22 @@
         <v>731435978</v>
       </c>
       <c r="L33" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M33">
         <v>2</v>
       </c>
       <c r="N33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O33" t="s">
         <v>32</v>
       </c>
       <c r="P33" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q33" t="s">
         <v>46</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>47</v>
       </c>
       <c r="R33" t="s">
         <v>35</v>
@@ -3774,13 +3771,13 @@
         <v>36</v>
       </c>
       <c r="T33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>39</v>
@@ -3788,25 +3785,25 @@
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C34" t="s">
+        <v>133</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" t="s">
         <v>135</v>
       </c>
-      <c r="D34" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="5" t="s">
+      <c r="G34" t="s">
         <v>136</v>
-      </c>
-      <c r="F34" t="s">
-        <v>137</v>
-      </c>
-      <c r="G34" t="s">
-        <v>138</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -3856,25 +3853,25 @@
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B35" s="1">
         <v>10001</v>
       </c>
       <c r="C35" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D35" t="s">
         <v>26</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F35" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G35" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H35">
         <v>34.521169999999998</v>
@@ -3889,22 +3886,22 @@
         <v>779517433</v>
       </c>
       <c r="L35" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M35">
         <v>3</v>
       </c>
       <c r="N35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O35" t="s">
         <v>32</v>
       </c>
       <c r="P35" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q35" t="s">
         <v>46</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>47</v>
       </c>
       <c r="R35" t="s">
         <v>35</v>
@@ -3919,7 +3916,7 @@
         <v>38</v>
       </c>
       <c r="V35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>39</v>
@@ -3927,25 +3924,25 @@
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B36" s="1">
         <v>10002</v>
       </c>
       <c r="C36" t="s">
+        <v>140</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" t="s">
+        <v>141</v>
+      </c>
+      <c r="F36" t="s">
         <v>142</v>
       </c>
-      <c r="D36" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" t="s">
-        <v>143</v>
-      </c>
-      <c r="F36" t="s">
-        <v>144</v>
-      </c>
       <c r="G36" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H36">
         <v>34.360207000000003</v>
@@ -3960,22 +3957,22 @@
         <v>753476995</v>
       </c>
       <c r="L36" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M36">
         <v>2</v>
       </c>
       <c r="N36" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O36" t="s">
         <v>32</v>
       </c>
       <c r="P36" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q36" t="s">
         <v>46</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>47</v>
       </c>
       <c r="R36" t="s">
         <v>35</v>
@@ -3998,25 +3995,25 @@
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B37" s="1">
         <v>10003</v>
       </c>
       <c r="C37" t="s">
+        <v>144</v>
+      </c>
+      <c r="D37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" t="s">
+        <v>145</v>
+      </c>
+      <c r="F37" t="s">
         <v>146</v>
       </c>
-      <c r="D37" t="s">
-        <v>26</v>
-      </c>
-      <c r="E37" t="s">
-        <v>147</v>
-      </c>
-      <c r="F37" t="s">
-        <v>148</v>
-      </c>
       <c r="G37" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H37">
         <v>34.405692000000002</v>
@@ -4031,22 +4028,22 @@
         <v>734239083</v>
       </c>
       <c r="L37" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M37">
         <v>4</v>
       </c>
       <c r="N37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O37" t="s">
         <v>32</v>
       </c>
       <c r="P37" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q37" t="s">
         <v>46</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>47</v>
       </c>
       <c r="R37" t="s">
         <v>35</v>
@@ -4061,7 +4058,7 @@
         <v>38</v>
       </c>
       <c r="V37" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="W37" s="1" t="s">
         <v>39</v>
@@ -4069,25 +4066,25 @@
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B38" s="1">
         <v>10004</v>
       </c>
       <c r="C38" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" t="s">
+        <v>149</v>
+      </c>
+      <c r="F38" t="s">
         <v>150</v>
       </c>
-      <c r="D38" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" t="s">
-        <v>151</v>
-      </c>
-      <c r="F38" t="s">
-        <v>152</v>
-      </c>
       <c r="G38" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H38">
         <v>34.287878999999997</v>
@@ -4102,22 +4099,22 @@
         <v>937997757</v>
       </c>
       <c r="L38" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O38" t="s">
         <v>32</v>
       </c>
       <c r="P38" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q38" t="s">
         <v>46</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>47</v>
       </c>
       <c r="R38" t="s">
         <v>35</v>
@@ -4132,7 +4129,7 @@
         <v>38</v>
       </c>
       <c r="V38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W38" s="1" t="s">
         <v>39</v>
@@ -4140,25 +4137,25 @@
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B39" s="1">
         <v>10005</v>
       </c>
       <c r="C39" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" t="s">
+        <v>153</v>
+      </c>
+      <c r="F39" t="s">
+        <v>150</v>
+      </c>
+      <c r="G39" t="s">
         <v>154</v>
-      </c>
-      <c r="D39" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" t="s">
-        <v>155</v>
-      </c>
-      <c r="F39" t="s">
-        <v>152</v>
-      </c>
-      <c r="G39" t="s">
-        <v>156</v>
       </c>
       <c r="H39">
         <v>34.256413999999999</v>
@@ -4173,22 +4170,22 @@
         <v>887311749</v>
       </c>
       <c r="L39" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O39" t="s">
         <v>32</v>
       </c>
       <c r="P39" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q39" t="s">
         <v>46</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>47</v>
       </c>
       <c r="R39" t="s">
         <v>35</v>
@@ -4203,7 +4200,7 @@
         <v>38</v>
       </c>
       <c r="V39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W39" s="1" t="s">
         <v>39</v>
@@ -4211,25 +4208,25 @@
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B40" s="1">
         <v>10006</v>
       </c>
       <c r="C40" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D40" t="s">
         <v>26</v>
       </c>
       <c r="E40" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F40" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H40">
         <v>34.262476999999997</v>
@@ -4244,22 +4241,22 @@
         <v>915790305</v>
       </c>
       <c r="L40" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M40">
         <v>5</v>
       </c>
       <c r="N40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O40" t="s">
         <v>32</v>
       </c>
       <c r="P40" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q40" t="s">
         <v>46</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>47</v>
       </c>
       <c r="R40" t="s">
         <v>35</v>
@@ -4274,7 +4271,7 @@
         <v>38</v>
       </c>
       <c r="V40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W40" s="1" t="s">
         <v>39</v>
@@ -4282,25 +4279,25 @@
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B41" s="1">
         <v>10007</v>
       </c>
       <c r="C41" t="s">
+        <v>159</v>
+      </c>
+      <c r="D41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" t="s">
+        <v>160</v>
+      </c>
+      <c r="F41" t="s">
         <v>161</v>
       </c>
-      <c r="D41" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41" t="s">
-        <v>162</v>
-      </c>
-      <c r="F41" t="s">
-        <v>163</v>
-      </c>
       <c r="G41" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H41">
         <v>34.192861000000001</v>
@@ -4315,22 +4312,22 @@
         <v>811552880</v>
       </c>
       <c r="L41" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="M41">
         <v>2</v>
       </c>
       <c r="N41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O41" t="s">
         <v>32</v>
       </c>
       <c r="P41" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q41" t="s">
         <v>46</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>47</v>
       </c>
       <c r="R41" t="s">
         <v>35</v>
@@ -4345,7 +4342,7 @@
         <v>38</v>
       </c>
       <c r="V41" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="W41" s="1" t="s">
         <v>39</v>
@@ -4353,25 +4350,25 @@
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B42" s="1">
         <v>10008</v>
       </c>
       <c r="C42" t="s">
+        <v>163</v>
+      </c>
+      <c r="D42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" t="s">
+        <v>164</v>
+      </c>
+      <c r="F42" t="s">
         <v>165</v>
       </c>
-      <c r="D42" t="s">
-        <v>26</v>
-      </c>
-      <c r="E42" t="s">
-        <v>166</v>
-      </c>
-      <c r="F42" t="s">
-        <v>167</v>
-      </c>
       <c r="G42" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H42">
         <v>34.522413999999998</v>
@@ -4386,22 +4383,22 @@
         <v>695325692</v>
       </c>
       <c r="L42" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="M42">
         <v>2</v>
       </c>
       <c r="N42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O42" t="s">
         <v>32</v>
       </c>
       <c r="P42" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q42" t="s">
         <v>46</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>47</v>
       </c>
       <c r="R42" t="s">
         <v>35</v>
@@ -4416,7 +4413,7 @@
         <v>38</v>
       </c>
       <c r="V42" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W42" s="1" t="s">
         <v>39</v>
@@ -4424,25 +4421,25 @@
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B43" s="1">
         <v>10009</v>
       </c>
       <c r="C43" t="s">
+        <v>167</v>
+      </c>
+      <c r="D43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" t="s">
+        <v>168</v>
+      </c>
+      <c r="F43" t="s">
         <v>169</v>
       </c>
-      <c r="D43" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" t="s">
-        <v>170</v>
-      </c>
-      <c r="F43" t="s">
-        <v>171</v>
-      </c>
       <c r="G43" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H43">
         <v>33.998232000000002</v>
@@ -4457,22 +4454,22 @@
         <v>745360421</v>
       </c>
       <c r="L43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M43">
         <v>2</v>
       </c>
       <c r="N43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O43" t="s">
         <v>32</v>
       </c>
       <c r="P43" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q43" t="s">
         <v>46</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>47</v>
       </c>
       <c r="R43" t="s">
         <v>35</v>
@@ -4484,10 +4481,10 @@
         <v>37</v>
       </c>
       <c r="U43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V43" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W43" s="1" t="s">
         <v>39</v>
@@ -4495,25 +4492,25 @@
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B44" s="1">
         <v>10010</v>
       </c>
       <c r="C44" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D44" t="s">
         <v>26</v>
       </c>
       <c r="E44" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F44" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H44">
         <v>34.017502</v>
@@ -4528,22 +4525,22 @@
         <v>766074745</v>
       </c>
       <c r="L44" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="M44">
         <v>2</v>
       </c>
       <c r="N44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O44" t="s">
         <v>32</v>
       </c>
       <c r="P44" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q44" t="s">
         <v>46</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>47</v>
       </c>
       <c r="R44" t="s">
         <v>35</v>
@@ -4555,10 +4552,10 @@
         <v>37</v>
       </c>
       <c r="U44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V44" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="W44" s="1" t="s">
         <v>39</v>
@@ -4566,25 +4563,25 @@
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B45" s="1">
         <v>10011</v>
       </c>
       <c r="C45" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D45" t="s">
         <v>26</v>
       </c>
       <c r="E45" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F45" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H45">
         <v>33.986607999999997</v>
@@ -4599,22 +4596,22 @@
         <v>787248921</v>
       </c>
       <c r="L45" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M45">
         <v>2</v>
       </c>
       <c r="N45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O45" t="s">
         <v>32</v>
       </c>
       <c r="P45" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q45" t="s">
         <v>46</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>47</v>
       </c>
       <c r="R45" t="s">
         <v>35</v>
@@ -4626,10 +4623,10 @@
         <v>37</v>
       </c>
       <c r="U45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V45" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W45" s="1" t="s">
         <v>39</v>
@@ -4637,25 +4634,25 @@
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B46" s="1">
         <v>10012</v>
       </c>
       <c r="C46" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D46" t="s">
         <v>26</v>
       </c>
       <c r="E46" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F46" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H46">
         <v>33.978102999999997</v>
@@ -4670,22 +4667,22 @@
         <v>838412388</v>
       </c>
       <c r="L46" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M46">
         <v>2</v>
       </c>
       <c r="N46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O46" t="s">
         <v>32</v>
       </c>
       <c r="P46" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q46" t="s">
         <v>46</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>47</v>
       </c>
       <c r="R46" t="s">
         <v>35</v>
@@ -4697,10 +4694,10 @@
         <v>37</v>
       </c>
       <c r="U46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V46" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W46" s="1" t="s">
         <v>39</v>
@@ -4708,25 +4705,25 @@
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B47" s="1">
         <v>10013</v>
       </c>
       <c r="C47" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D47" t="s">
         <v>26</v>
       </c>
       <c r="E47" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F47" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H47">
         <v>33.953930999999997</v>
@@ -4741,22 +4738,22 @@
         <v>751913644</v>
       </c>
       <c r="L47" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M47">
         <v>2</v>
       </c>
       <c r="N47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O47" t="s">
         <v>32</v>
       </c>
       <c r="P47" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q47" t="s">
         <v>46</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>47</v>
       </c>
       <c r="R47" t="s">
         <v>35</v>
@@ -4768,10 +4765,10 @@
         <v>37</v>
       </c>
       <c r="U47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V47" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W47" s="1" t="s">
         <v>39</v>
@@ -4779,25 +4776,25 @@
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B48" s="1">
         <v>10014</v>
       </c>
       <c r="C48" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D48" t="s">
         <v>26</v>
       </c>
       <c r="E48" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F48" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H48">
         <v>34.027757000000001</v>
@@ -4812,22 +4809,22 @@
         <v>965639376</v>
       </c>
       <c r="L48" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M48">
         <v>2</v>
       </c>
       <c r="N48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O48" t="s">
         <v>32</v>
       </c>
       <c r="P48" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q48" t="s">
         <v>46</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>47</v>
       </c>
       <c r="R48" t="s">
         <v>35</v>
@@ -4839,10 +4836,10 @@
         <v>37</v>
       </c>
       <c r="U48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V48" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="W48" s="1" t="s">
         <v>39</v>
@@ -4850,25 +4847,25 @@
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B49" s="1">
         <v>10015</v>
       </c>
       <c r="C49" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D49" t="s">
         <v>26</v>
       </c>
       <c r="E49" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F49" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H49">
         <v>33.995612000000001</v>
@@ -4883,22 +4880,22 @@
         <v>803062069</v>
       </c>
       <c r="L49" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M49">
         <v>2</v>
       </c>
       <c r="N49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O49" t="s">
         <v>32</v>
       </c>
       <c r="P49" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q49" t="s">
         <v>46</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>47</v>
       </c>
       <c r="R49" t="s">
         <v>35</v>
@@ -4910,10 +4907,10 @@
         <v>37</v>
       </c>
       <c r="U49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V49" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W49" s="1" t="s">
         <v>39</v>
@@ -4921,25 +4918,25 @@
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C50" t="s">
+        <v>190</v>
+      </c>
+      <c r="D50" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" t="s">
+        <v>191</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="D50" t="s">
-        <v>26</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="G50" t="s">
         <v>193</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="G50" t="s">
-        <v>195</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -4989,25 +4986,25 @@
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B51" s="1">
         <v>10001</v>
       </c>
       <c r="C51" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D51" t="s">
         <v>26</v>
       </c>
       <c r="E51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F51" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G51" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H51">
         <v>34.521169999999998</v>
@@ -5022,22 +5019,22 @@
         <v>779517433</v>
       </c>
       <c r="L51" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M51">
         <v>3</v>
       </c>
       <c r="N51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O51" t="s">
         <v>32</v>
       </c>
       <c r="P51" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q51" t="s">
         <v>46</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>47</v>
       </c>
       <c r="R51" t="s">
         <v>35</v>
@@ -5052,7 +5049,7 @@
         <v>38</v>
       </c>
       <c r="V51" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W51" s="1" t="s">
         <v>39</v>
@@ -5060,25 +5057,25 @@
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B52" s="1">
         <v>10002</v>
       </c>
       <c r="C52" t="s">
+        <v>197</v>
+      </c>
+      <c r="D52" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" t="s">
+        <v>198</v>
+      </c>
+      <c r="F52" t="s">
         <v>199</v>
       </c>
-      <c r="D52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E52" t="s">
-        <v>200</v>
-      </c>
-      <c r="F52" t="s">
-        <v>201</v>
-      </c>
       <c r="G52" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H52">
         <v>34.360207000000003</v>
@@ -5093,22 +5090,22 @@
         <v>753476995</v>
       </c>
       <c r="L52" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M52">
         <v>2</v>
       </c>
       <c r="N52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O52" t="s">
         <v>32</v>
       </c>
       <c r="P52" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q52" t="s">
         <v>46</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>47</v>
       </c>
       <c r="R52" t="s">
         <v>35</v>
@@ -5131,25 +5128,25 @@
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B53" s="1">
         <v>10003</v>
       </c>
       <c r="C53" t="s">
+        <v>201</v>
+      </c>
+      <c r="D53" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53" t="s">
+        <v>202</v>
+      </c>
+      <c r="F53" t="s">
         <v>203</v>
       </c>
-      <c r="D53" t="s">
-        <v>26</v>
-      </c>
-      <c r="E53" t="s">
-        <v>204</v>
-      </c>
-      <c r="F53" t="s">
-        <v>205</v>
-      </c>
       <c r="G53" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H53">
         <v>34.405692000000002</v>
@@ -5164,22 +5161,22 @@
         <v>734239083</v>
       </c>
       <c r="L53" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="M53">
         <v>4</v>
       </c>
       <c r="N53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O53" t="s">
         <v>32</v>
       </c>
       <c r="P53" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q53" t="s">
         <v>46</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>47</v>
       </c>
       <c r="R53" t="s">
         <v>35</v>
@@ -5194,7 +5191,7 @@
         <v>38</v>
       </c>
       <c r="V53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="W53" s="1" t="s">
         <v>39</v>
@@ -5202,25 +5199,25 @@
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B54" s="1">
         <v>10004</v>
       </c>
       <c r="C54" t="s">
+        <v>205</v>
+      </c>
+      <c r="D54" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54" t="s">
+        <v>206</v>
+      </c>
+      <c r="F54" t="s">
         <v>207</v>
       </c>
-      <c r="D54" t="s">
-        <v>26</v>
-      </c>
-      <c r="E54" t="s">
-        <v>208</v>
-      </c>
-      <c r="F54" t="s">
-        <v>209</v>
-      </c>
       <c r="G54" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H54">
         <v>34.287878999999997</v>
@@ -5235,22 +5232,22 @@
         <v>937997757</v>
       </c>
       <c r="L54" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M54">
         <v>2</v>
       </c>
       <c r="N54" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O54" t="s">
         <v>32</v>
       </c>
       <c r="P54" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q54" t="s">
         <v>46</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>47</v>
       </c>
       <c r="R54" t="s">
         <v>35</v>
@@ -5265,7 +5262,7 @@
         <v>38</v>
       </c>
       <c r="V54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W54" s="1" t="s">
         <v>39</v>
@@ -5273,25 +5270,25 @@
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B55" s="1">
         <v>10005</v>
       </c>
       <c r="C55" t="s">
+        <v>209</v>
+      </c>
+      <c r="D55" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" t="s">
+        <v>210</v>
+      </c>
+      <c r="F55" t="s">
+        <v>207</v>
+      </c>
+      <c r="G55" t="s">
         <v>211</v>
-      </c>
-      <c r="D55" t="s">
-        <v>26</v>
-      </c>
-      <c r="E55" t="s">
-        <v>212</v>
-      </c>
-      <c r="F55" t="s">
-        <v>209</v>
-      </c>
-      <c r="G55" t="s">
-        <v>213</v>
       </c>
       <c r="H55">
         <v>34.256413999999999</v>
@@ -5306,22 +5303,22 @@
         <v>887311749</v>
       </c>
       <c r="L55" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O55" t="s">
         <v>32</v>
       </c>
       <c r="P55" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q55" t="s">
         <v>46</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>47</v>
       </c>
       <c r="R55" t="s">
         <v>35</v>
@@ -5336,7 +5333,7 @@
         <v>38</v>
       </c>
       <c r="V55" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W55" s="1" t="s">
         <v>39</v>
@@ -5344,25 +5341,25 @@
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B56" s="1">
         <v>10006</v>
       </c>
       <c r="C56" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D56" t="s">
         <v>26</v>
       </c>
       <c r="E56" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F56" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G56" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H56">
         <v>34.262476999999997</v>
@@ -5377,22 +5374,22 @@
         <v>915790305</v>
       </c>
       <c r="L56" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M56">
         <v>5</v>
       </c>
       <c r="N56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O56" t="s">
         <v>32</v>
       </c>
       <c r="P56" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q56" t="s">
         <v>46</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>47</v>
       </c>
       <c r="R56" t="s">
         <v>35</v>
@@ -5407,7 +5404,7 @@
         <v>38</v>
       </c>
       <c r="V56" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W56" s="1" t="s">
         <v>39</v>
@@ -5415,25 +5412,25 @@
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B57" s="1">
         <v>10007</v>
       </c>
       <c r="C57" t="s">
+        <v>216</v>
+      </c>
+      <c r="D57" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57" t="s">
+        <v>217</v>
+      </c>
+      <c r="F57" t="s">
         <v>218</v>
       </c>
-      <c r="D57" t="s">
-        <v>26</v>
-      </c>
-      <c r="E57" t="s">
-        <v>219</v>
-      </c>
-      <c r="F57" t="s">
-        <v>220</v>
-      </c>
       <c r="G57" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H57">
         <v>34.192861000000001</v>
@@ -5448,22 +5445,22 @@
         <v>811552880</v>
       </c>
       <c r="L57" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="M57">
         <v>2</v>
       </c>
       <c r="N57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O57" t="s">
         <v>32</v>
       </c>
       <c r="P57" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q57" t="s">
         <v>46</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>47</v>
       </c>
       <c r="R57" t="s">
         <v>35</v>
@@ -5478,7 +5475,7 @@
         <v>38</v>
       </c>
       <c r="V57" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="W57" s="1" t="s">
         <v>39</v>
@@ -5486,25 +5483,25 @@
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B58" s="1">
         <v>10008</v>
       </c>
       <c r="C58" t="s">
+        <v>220</v>
+      </c>
+      <c r="D58" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" t="s">
+        <v>221</v>
+      </c>
+      <c r="F58" t="s">
         <v>222</v>
       </c>
-      <c r="D58" t="s">
-        <v>26</v>
-      </c>
-      <c r="E58" t="s">
-        <v>223</v>
-      </c>
-      <c r="F58" t="s">
-        <v>224</v>
-      </c>
       <c r="G58" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H58">
         <v>34.522413999999998</v>
@@ -5519,22 +5516,22 @@
         <v>695325692</v>
       </c>
       <c r="L58" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M58">
         <v>2</v>
       </c>
       <c r="N58" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O58" t="s">
         <v>32</v>
       </c>
       <c r="P58" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q58" t="s">
         <v>46</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>47</v>
       </c>
       <c r="R58" t="s">
         <v>35</v>
@@ -5549,7 +5546,7 @@
         <v>38</v>
       </c>
       <c r="V58" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W58" s="1" t="s">
         <v>39</v>
@@ -5557,25 +5554,25 @@
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B59" s="1">
         <v>10009</v>
       </c>
       <c r="C59" t="s">
+        <v>224</v>
+      </c>
+      <c r="D59" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" t="s">
+        <v>225</v>
+      </c>
+      <c r="F59" t="s">
         <v>226</v>
       </c>
-      <c r="D59" t="s">
-        <v>26</v>
-      </c>
-      <c r="E59" t="s">
-        <v>227</v>
-      </c>
-      <c r="F59" t="s">
-        <v>228</v>
-      </c>
       <c r="G59" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H59">
         <v>33.998232000000002</v>
@@ -5590,22 +5587,22 @@
         <v>745360421</v>
       </c>
       <c r="L59" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M59">
         <v>2</v>
       </c>
       <c r="N59" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O59" t="s">
         <v>32</v>
       </c>
       <c r="P59" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q59" t="s">
         <v>46</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>47</v>
       </c>
       <c r="R59" t="s">
         <v>35</v>
@@ -5617,10 +5614,10 @@
         <v>37</v>
       </c>
       <c r="U59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V59" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W59" s="1" t="s">
         <v>39</v>
@@ -5628,25 +5625,25 @@
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B60" s="1">
         <v>10010</v>
       </c>
       <c r="C60" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D60" t="s">
         <v>26</v>
       </c>
       <c r="E60" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F60" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H60">
         <v>34.017502</v>
@@ -5661,22 +5658,22 @@
         <v>766074745</v>
       </c>
       <c r="L60" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M60">
         <v>2</v>
       </c>
       <c r="N60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O60" t="s">
         <v>32</v>
       </c>
       <c r="P60" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q60" t="s">
         <v>46</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>47</v>
       </c>
       <c r="R60" t="s">
         <v>35</v>
@@ -5688,10 +5685,10 @@
         <v>37</v>
       </c>
       <c r="U60" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V60" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="W60" s="1" t="s">
         <v>39</v>
@@ -5699,25 +5696,25 @@
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B61" s="1">
         <v>10011</v>
       </c>
       <c r="C61" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D61" t="s">
         <v>26</v>
       </c>
       <c r="E61" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F61" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H61">
         <v>33.986607999999997</v>
@@ -5732,22 +5729,22 @@
         <v>787248921</v>
       </c>
       <c r="L61" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="M61">
         <v>2</v>
       </c>
       <c r="N61" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O61" t="s">
         <v>32</v>
       </c>
       <c r="P61" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q61" t="s">
         <v>46</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>47</v>
       </c>
       <c r="R61" t="s">
         <v>35</v>
@@ -5759,10 +5756,10 @@
         <v>37</v>
       </c>
       <c r="U61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V61" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W61" s="1" t="s">
         <v>39</v>
@@ -5770,25 +5767,25 @@
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B62" s="1">
         <v>10012</v>
       </c>
       <c r="C62" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D62" t="s">
         <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F62" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H62">
         <v>33.978102999999997</v>
@@ -5803,22 +5800,22 @@
         <v>838412388</v>
       </c>
       <c r="L62" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="M62">
         <v>2</v>
       </c>
       <c r="N62" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O62" t="s">
         <v>32</v>
       </c>
       <c r="P62" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q62" t="s">
         <v>46</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>47</v>
       </c>
       <c r="R62" t="s">
         <v>35</v>
@@ -5830,10 +5827,10 @@
         <v>37</v>
       </c>
       <c r="U62" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V62" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W62" s="1" t="s">
         <v>39</v>
@@ -5841,25 +5838,25 @@
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B63" s="1">
         <v>10013</v>
       </c>
       <c r="C63" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D63" t="s">
         <v>26</v>
       </c>
       <c r="E63" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F63" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H63">
         <v>33.953930999999997</v>
@@ -5874,22 +5871,22 @@
         <v>751913644</v>
       </c>
       <c r="L63" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="M63">
         <v>2</v>
       </c>
       <c r="N63" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O63" t="s">
         <v>32</v>
       </c>
       <c r="P63" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q63" t="s">
         <v>46</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>47</v>
       </c>
       <c r="R63" t="s">
         <v>35</v>
@@ -5901,10 +5898,10 @@
         <v>37</v>
       </c>
       <c r="U63" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V63" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W63" s="1" t="s">
         <v>39</v>
@@ -5912,25 +5909,25 @@
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B64" s="1">
         <v>10014</v>
       </c>
       <c r="C64" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D64" t="s">
         <v>26</v>
       </c>
       <c r="E64" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F64" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H64">
         <v>34.027757000000001</v>
@@ -5945,22 +5942,22 @@
         <v>965639376</v>
       </c>
       <c r="L64" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M64">
         <v>2</v>
       </c>
       <c r="N64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O64" t="s">
         <v>32</v>
       </c>
       <c r="P64" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q64" t="s">
         <v>46</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>47</v>
       </c>
       <c r="R64" t="s">
         <v>35</v>
@@ -5972,10 +5969,10 @@
         <v>37</v>
       </c>
       <c r="U64" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V64" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="W64" s="1" t="s">
         <v>39</v>
@@ -5983,25 +5980,25 @@
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B65" s="1">
         <v>10015</v>
       </c>
       <c r="C65" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D65" t="s">
         <v>26</v>
       </c>
       <c r="E65" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F65" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H65">
         <v>33.995612000000001</v>
@@ -6016,22 +6013,22 @@
         <v>803062069</v>
       </c>
       <c r="L65" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O65" t="s">
         <v>32</v>
       </c>
       <c r="P65" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q65" t="s">
         <v>46</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>47</v>
       </c>
       <c r="R65" t="s">
         <v>35</v>
@@ -6043,10 +6040,10 @@
         <v>37</v>
       </c>
       <c r="U65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V65" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W65" s="1" t="s">
         <v>39</v>
@@ -6054,25 +6051,25 @@
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C66" t="s">
+        <v>247</v>
+      </c>
+      <c r="D66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F66" t="s">
         <v>249</v>
       </c>
-      <c r="D66" t="s">
-        <v>26</v>
-      </c>
-      <c r="E66" s="5" t="s">
+      <c r="G66" t="s">
         <v>250</v>
-      </c>
-      <c r="F66" t="s">
-        <v>251</v>
-      </c>
-      <c r="G66" t="s">
-        <v>252</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -6122,25 +6119,25 @@
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B67" s="1">
         <v>10001</v>
       </c>
       <c r="C67" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D67" t="s">
         <v>26</v>
       </c>
       <c r="E67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F67" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G67" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H67">
         <v>34.521169999999998</v>
@@ -6155,22 +6152,22 @@
         <v>779517433</v>
       </c>
       <c r="L67" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M67">
         <v>3</v>
       </c>
       <c r="N67" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O67" t="s">
         <v>32</v>
       </c>
       <c r="P67" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q67" t="s">
         <v>46</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>47</v>
       </c>
       <c r="R67" t="s">
         <v>35</v>
@@ -6185,7 +6182,7 @@
         <v>38</v>
       </c>
       <c r="V67" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W67" s="1" t="s">
         <v>39</v>
@@ -6193,25 +6190,25 @@
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B68" s="1">
         <v>10002</v>
       </c>
       <c r="C68" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D68" t="s">
         <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F68" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G68" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H68">
         <v>34.360207000000003</v>
@@ -6226,22 +6223,22 @@
         <v>753476995</v>
       </c>
       <c r="L68" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O68" t="s">
         <v>32</v>
       </c>
       <c r="P68" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q68" t="s">
         <v>46</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>47</v>
       </c>
       <c r="R68" t="s">
         <v>35</v>
@@ -6264,25 +6261,25 @@
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B69" s="1">
         <v>10003</v>
       </c>
       <c r="C69" t="s">
+        <v>257</v>
+      </c>
+      <c r="D69" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" t="s">
+        <v>258</v>
+      </c>
+      <c r="F69" t="s">
         <v>259</v>
       </c>
-      <c r="D69" t="s">
-        <v>26</v>
-      </c>
-      <c r="E69" t="s">
-        <v>260</v>
-      </c>
-      <c r="F69" t="s">
-        <v>261</v>
-      </c>
       <c r="G69" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H69">
         <v>34.405692000000002</v>
@@ -6297,22 +6294,22 @@
         <v>734239083</v>
       </c>
       <c r="L69" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M69">
         <v>4</v>
       </c>
       <c r="N69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O69" t="s">
         <v>32</v>
       </c>
       <c r="P69" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q69" t="s">
         <v>46</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>47</v>
       </c>
       <c r="R69" t="s">
         <v>35</v>
@@ -6327,7 +6324,7 @@
         <v>38</v>
       </c>
       <c r="V69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="W69" s="1" t="s">
         <v>39</v>
@@ -6335,25 +6332,25 @@
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B70" s="1">
         <v>10004</v>
       </c>
       <c r="C70" t="s">
+        <v>261</v>
+      </c>
+      <c r="D70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" t="s">
+        <v>262</v>
+      </c>
+      <c r="F70" t="s">
         <v>263</v>
       </c>
-      <c r="D70" t="s">
-        <v>26</v>
-      </c>
-      <c r="E70" t="s">
-        <v>264</v>
-      </c>
-      <c r="F70" t="s">
-        <v>265</v>
-      </c>
       <c r="G70" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H70">
         <v>34.287878999999997</v>
@@ -6368,22 +6365,22 @@
         <v>937997757</v>
       </c>
       <c r="L70" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O70" t="s">
         <v>32</v>
       </c>
       <c r="P70" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q70" t="s">
         <v>46</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>47</v>
       </c>
       <c r="R70" t="s">
         <v>35</v>
@@ -6398,7 +6395,7 @@
         <v>38</v>
       </c>
       <c r="V70" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W70" s="1" t="s">
         <v>39</v>
@@ -6406,25 +6403,25 @@
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B71" s="1">
         <v>10005</v>
       </c>
       <c r="C71" t="s">
+        <v>265</v>
+      </c>
+      <c r="D71" t="s">
+        <v>26</v>
+      </c>
+      <c r="E71" t="s">
+        <v>266</v>
+      </c>
+      <c r="F71" t="s">
+        <v>263</v>
+      </c>
+      <c r="G71" t="s">
         <v>267</v>
-      </c>
-      <c r="D71" t="s">
-        <v>26</v>
-      </c>
-      <c r="E71" t="s">
-        <v>268</v>
-      </c>
-      <c r="F71" t="s">
-        <v>265</v>
-      </c>
-      <c r="G71" t="s">
-        <v>269</v>
       </c>
       <c r="H71">
         <v>34.256413999999999</v>
@@ -6439,22 +6436,22 @@
         <v>887311749</v>
       </c>
       <c r="L71" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O71" t="s">
         <v>32</v>
       </c>
       <c r="P71" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q71" t="s">
         <v>46</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>47</v>
       </c>
       <c r="R71" t="s">
         <v>35</v>
@@ -6469,7 +6466,7 @@
         <v>38</v>
       </c>
       <c r="V71" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W71" s="1" t="s">
         <v>39</v>
@@ -6477,25 +6474,25 @@
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B72" s="1">
         <v>10006</v>
       </c>
       <c r="C72" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D72" t="s">
         <v>26</v>
       </c>
       <c r="E72" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F72" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G72" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H72">
         <v>34.262476999999997</v>
@@ -6510,22 +6507,22 @@
         <v>915790305</v>
       </c>
       <c r="L72" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M72">
         <v>5</v>
       </c>
       <c r="N72" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O72" t="s">
         <v>32</v>
       </c>
       <c r="P72" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q72" t="s">
         <v>46</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>47</v>
       </c>
       <c r="R72" t="s">
         <v>35</v>
@@ -6540,7 +6537,7 @@
         <v>38</v>
       </c>
       <c r="V72" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W72" s="1" t="s">
         <v>39</v>
@@ -6548,25 +6545,25 @@
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B73" s="1">
         <v>10007</v>
       </c>
       <c r="C73" t="s">
+        <v>272</v>
+      </c>
+      <c r="D73" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" t="s">
+        <v>273</v>
+      </c>
+      <c r="F73" t="s">
         <v>274</v>
       </c>
-      <c r="D73" t="s">
-        <v>26</v>
-      </c>
-      <c r="E73" t="s">
-        <v>275</v>
-      </c>
-      <c r="F73" t="s">
-        <v>276</v>
-      </c>
       <c r="G73" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H73">
         <v>34.192861000000001</v>
@@ -6581,22 +6578,22 @@
         <v>811552880</v>
       </c>
       <c r="L73" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="M73">
         <v>2</v>
       </c>
       <c r="N73" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O73" t="s">
         <v>32</v>
       </c>
       <c r="P73" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q73" t="s">
         <v>46</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>47</v>
       </c>
       <c r="R73" t="s">
         <v>35</v>
@@ -6611,7 +6608,7 @@
         <v>38</v>
       </c>
       <c r="V73" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="W73" s="1" t="s">
         <v>39</v>
@@ -6619,25 +6616,25 @@
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B74" s="1">
         <v>10008</v>
       </c>
       <c r="C74" t="s">
+        <v>276</v>
+      </c>
+      <c r="D74" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" t="s">
+        <v>277</v>
+      </c>
+      <c r="F74" t="s">
         <v>278</v>
       </c>
-      <c r="D74" t="s">
-        <v>26</v>
-      </c>
-      <c r="E74" t="s">
-        <v>279</v>
-      </c>
-      <c r="F74" t="s">
-        <v>280</v>
-      </c>
       <c r="G74" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H74">
         <v>34.522413999999998</v>
@@ -6652,22 +6649,22 @@
         <v>695325692</v>
       </c>
       <c r="L74" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="M74">
         <v>2</v>
       </c>
       <c r="N74" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O74" t="s">
         <v>32</v>
       </c>
       <c r="P74" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q74" t="s">
         <v>46</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>47</v>
       </c>
       <c r="R74" t="s">
         <v>35</v>
@@ -6682,7 +6679,7 @@
         <v>38</v>
       </c>
       <c r="V74" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W74" s="1" t="s">
         <v>39</v>
@@ -6690,25 +6687,25 @@
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B75" s="1">
         <v>10009</v>
       </c>
       <c r="C75" t="s">
+        <v>280</v>
+      </c>
+      <c r="D75" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75" t="s">
+        <v>281</v>
+      </c>
+      <c r="F75" t="s">
         <v>282</v>
       </c>
-      <c r="D75" t="s">
-        <v>26</v>
-      </c>
-      <c r="E75" t="s">
-        <v>283</v>
-      </c>
-      <c r="F75" t="s">
-        <v>284</v>
-      </c>
       <c r="G75" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H75">
         <v>33.998232000000002</v>
@@ -6723,22 +6720,22 @@
         <v>745360421</v>
       </c>
       <c r="L75" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="M75">
         <v>2</v>
       </c>
       <c r="N75" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O75" t="s">
         <v>32</v>
       </c>
       <c r="P75" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q75" t="s">
         <v>46</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>47</v>
       </c>
       <c r="R75" t="s">
         <v>35</v>
@@ -6750,10 +6747,10 @@
         <v>37</v>
       </c>
       <c r="U75" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V75" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W75" s="1" t="s">
         <v>39</v>
@@ -6761,25 +6758,25 @@
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B76" s="1">
         <v>10010</v>
       </c>
       <c r="C76" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D76" t="s">
         <v>26</v>
       </c>
       <c r="E76" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F76" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H76">
         <v>34.017502</v>
@@ -6794,22 +6791,22 @@
         <v>766074745</v>
       </c>
       <c r="L76" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="M76">
         <v>2</v>
       </c>
       <c r="N76" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O76" t="s">
         <v>32</v>
       </c>
       <c r="P76" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q76" t="s">
         <v>46</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>47</v>
       </c>
       <c r="R76" t="s">
         <v>35</v>
@@ -6821,10 +6818,10 @@
         <v>37</v>
       </c>
       <c r="U76" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V76" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="W76" s="1" t="s">
         <v>39</v>
@@ -6832,25 +6829,25 @@
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B77" s="1">
         <v>10011</v>
       </c>
       <c r="C77" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D77" t="s">
         <v>26</v>
       </c>
       <c r="E77" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="F77" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H77">
         <v>33.986607999999997</v>
@@ -6865,22 +6862,22 @@
         <v>787248921</v>
       </c>
       <c r="L77" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M77">
         <v>2</v>
       </c>
       <c r="N77" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O77" t="s">
         <v>32</v>
       </c>
       <c r="P77" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q77" t="s">
         <v>46</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>47</v>
       </c>
       <c r="R77" t="s">
         <v>35</v>
@@ -6892,10 +6889,10 @@
         <v>37</v>
       </c>
       <c r="U77" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V77" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W77" s="1" t="s">
         <v>39</v>
@@ -6903,25 +6900,25 @@
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B78" s="1">
         <v>10012</v>
       </c>
       <c r="C78" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D78" t="s">
         <v>26</v>
       </c>
       <c r="E78" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F78" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H78">
         <v>33.978102999999997</v>
@@ -6936,22 +6933,22 @@
         <v>838412388</v>
       </c>
       <c r="L78" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M78">
         <v>2</v>
       </c>
       <c r="N78" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O78" t="s">
         <v>32</v>
       </c>
       <c r="P78" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q78" t="s">
         <v>46</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>47</v>
       </c>
       <c r="R78" t="s">
         <v>35</v>
@@ -6963,10 +6960,10 @@
         <v>37</v>
       </c>
       <c r="U78" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V78" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W78" s="1" t="s">
         <v>39</v>
@@ -6974,25 +6971,25 @@
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B79" s="1">
         <v>10013</v>
       </c>
       <c r="C79" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D79" t="s">
         <v>26</v>
       </c>
       <c r="E79" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F79" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H79">
         <v>33.953930999999997</v>
@@ -7007,22 +7004,22 @@
         <v>751913644</v>
       </c>
       <c r="L79" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="M79">
         <v>2</v>
       </c>
       <c r="N79" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O79" t="s">
         <v>32</v>
       </c>
       <c r="P79" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q79" t="s">
         <v>46</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>47</v>
       </c>
       <c r="R79" t="s">
         <v>35</v>
@@ -7034,10 +7031,10 @@
         <v>37</v>
       </c>
       <c r="U79" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V79" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W79" s="1" t="s">
         <v>39</v>
@@ -7045,25 +7042,25 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B80" s="1">
         <v>10014</v>
       </c>
       <c r="C80" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D80" t="s">
         <v>26</v>
       </c>
       <c r="E80" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F80" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H80">
         <v>34.027757000000001</v>
@@ -7078,22 +7075,22 @@
         <v>965639376</v>
       </c>
       <c r="L80" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="M80">
         <v>2</v>
       </c>
       <c r="N80" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O80" t="s">
         <v>32</v>
       </c>
       <c r="P80" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q80" t="s">
         <v>46</v>
-      </c>
-      <c r="Q80" t="s">
-        <v>47</v>
       </c>
       <c r="R80" t="s">
         <v>35</v>
@@ -7105,10 +7102,10 @@
         <v>37</v>
       </c>
       <c r="U80" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V80" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="W80" s="1" t="s">
         <v>39</v>
@@ -7116,25 +7113,25 @@
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B81" s="1">
         <v>10015</v>
       </c>
       <c r="C81" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D81" t="s">
         <v>26</v>
       </c>
       <c r="E81" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F81" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H81">
         <v>33.995612000000001</v>
@@ -7149,22 +7146,22 @@
         <v>803062069</v>
       </c>
       <c r="L81" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="M81">
         <v>2</v>
       </c>
       <c r="N81" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O81" t="s">
         <v>32</v>
       </c>
       <c r="P81" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q81" t="s">
         <v>46</v>
-      </c>
-      <c r="Q81" t="s">
-        <v>47</v>
       </c>
       <c r="R81" t="s">
         <v>35</v>
@@ -7176,10 +7173,10 @@
         <v>37</v>
       </c>
       <c r="U81" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V81" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W81" s="1" t="s">
         <v>39</v>
@@ -7187,25 +7184,25 @@
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B82">
         <v>10137</v>
       </c>
       <c r="C82" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D82" t="s">
         <v>26</v>
       </c>
       <c r="E82" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F82" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G82" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H82">
         <v>34.360207000000003</v>
@@ -7220,7 +7217,7 @@
         <v>753476995</v>
       </c>
       <c r="L82" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M82">
         <v>2</v>
@@ -7258,25 +7255,25 @@
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B83">
         <v>10138</v>
       </c>
       <c r="C83" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D83" t="s">
         <v>26</v>
       </c>
       <c r="E83" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F83" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G83" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H83">
         <v>34.405692000000002</v>
@@ -7291,7 +7288,7 @@
         <v>734239083</v>
       </c>
       <c r="L83" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M83">
         <v>4</v>
@@ -7321,7 +7318,7 @@
         <v>38</v>
       </c>
       <c r="V83" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="W83" s="1" t="s">
         <v>39</v>
@@ -7329,25 +7326,25 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B84">
         <v>10139</v>
       </c>
       <c r="C84" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D84" t="s">
         <v>26</v>
       </c>
       <c r="E84" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F84" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G84" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H84">
         <v>34.256413999999999</v>
@@ -7362,7 +7359,7 @@
         <v>887311749</v>
       </c>
       <c r="L84" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M84">
         <v>1</v>
@@ -7392,7 +7389,7 @@
         <v>38</v>
       </c>
       <c r="V84" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W84" s="1" t="s">
         <v>39</v>
@@ -7400,25 +7397,25 @@
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B85">
         <v>10140</v>
       </c>
       <c r="C85" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D85" t="s">
         <v>26</v>
       </c>
       <c r="E85" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F85" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G85" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H85">
         <v>34.262476999999997</v>
@@ -7433,7 +7430,7 @@
         <v>915790305</v>
       </c>
       <c r="L85" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M85">
         <v>5</v>
@@ -7463,7 +7460,7 @@
         <v>38</v>
       </c>
       <c r="V85" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="W85" s="1" t="s">
         <v>39</v>
@@ -7471,25 +7468,25 @@
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B86">
         <v>10141</v>
       </c>
       <c r="C86" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D86" t="s">
         <v>26</v>
       </c>
       <c r="E86" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F86" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G86" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="H86">
         <v>34.192861000000001</v>
@@ -7504,7 +7501,7 @@
         <v>811552880</v>
       </c>
       <c r="L86" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M86">
         <v>2</v>
@@ -7534,7 +7531,7 @@
         <v>38</v>
       </c>
       <c r="V86" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="W86" s="1" t="s">
         <v>39</v>
@@ -7542,25 +7539,25 @@
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B87">
         <v>10142</v>
       </c>
       <c r="C87" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D87" t="s">
         <v>26</v>
       </c>
       <c r="E87" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F87" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G87" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H87">
         <v>33.998232000000002</v>
@@ -7575,7 +7572,7 @@
         <v>745360421</v>
       </c>
       <c r="L87" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="M87">
         <v>2</v>
@@ -7602,10 +7599,10 @@
         <v>37</v>
       </c>
       <c r="U87" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V87" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W87" s="1" t="s">
         <v>39</v>
@@ -7613,25 +7610,25 @@
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B88">
         <v>10143</v>
       </c>
       <c r="C88" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D88" t="s">
         <v>26</v>
       </c>
       <c r="E88" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F88" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G88" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H88">
         <v>34.017502</v>
@@ -7646,7 +7643,7 @@
         <v>766074745</v>
       </c>
       <c r="L88" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="M88">
         <v>2</v>
@@ -7673,10 +7670,10 @@
         <v>37</v>
       </c>
       <c r="U88" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V88" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="W88" s="1" t="s">
         <v>39</v>
@@ -7684,25 +7681,25 @@
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B89">
         <v>10144</v>
       </c>
       <c r="C89" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D89" t="s">
         <v>26</v>
       </c>
       <c r="E89" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F89" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G89" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H89">
         <v>33.986607999999997</v>
@@ -7717,7 +7714,7 @@
         <v>787248921</v>
       </c>
       <c r="L89" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="M89">
         <v>2</v>
@@ -7744,10 +7741,10 @@
         <v>37</v>
       </c>
       <c r="U89" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V89" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W89" s="1" t="s">
         <v>39</v>
@@ -7755,25 +7752,25 @@
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B90">
         <v>10145</v>
       </c>
       <c r="C90" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D90" t="s">
         <v>26</v>
       </c>
       <c r="E90" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F90" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G90" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H90">
         <v>33.978102999999997</v>
@@ -7788,7 +7785,7 @@
         <v>838412388</v>
       </c>
       <c r="L90" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M90">
         <v>2</v>
@@ -7815,10 +7812,10 @@
         <v>37</v>
       </c>
       <c r="U90" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V90" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W90" s="1" t="s">
         <v>39</v>
@@ -7826,25 +7823,25 @@
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B91">
         <v>10146</v>
       </c>
       <c r="C91" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D91" t="s">
         <v>26</v>
       </c>
       <c r="E91" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F91" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G91" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H91">
         <v>33.953930999999997</v>
@@ -7859,7 +7856,7 @@
         <v>751913644</v>
       </c>
       <c r="L91" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="M91">
         <v>2</v>
@@ -7886,10 +7883,10 @@
         <v>37</v>
       </c>
       <c r="U91" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V91" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="W91" s="1" t="s">
         <v>39</v>
@@ -7897,25 +7894,25 @@
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B92">
         <v>10147</v>
       </c>
       <c r="C92" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D92" t="s">
         <v>26</v>
       </c>
       <c r="E92" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F92" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G92" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H92">
         <v>34.027757000000001</v>
@@ -7930,7 +7927,7 @@
         <v>965639376</v>
       </c>
       <c r="L92" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M92">
         <v>2</v>
@@ -7957,10 +7954,10 @@
         <v>37</v>
       </c>
       <c r="U92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V92" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="W92" s="1" t="s">
         <v>39</v>
@@ -7968,25 +7965,25 @@
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B93">
         <v>10148</v>
       </c>
       <c r="C93" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D93" t="s">
         <v>26</v>
       </c>
       <c r="E93" t="s">
+        <v>41</v>
+      </c>
+      <c r="F93" t="s">
         <v>42</v>
       </c>
-      <c r="F93" t="s">
-        <v>43</v>
-      </c>
       <c r="G93" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H93">
         <v>12.89515492</v>
@@ -8001,7 +7998,7 @@
         <v>779517433</v>
       </c>
       <c r="L93" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="M93">
         <v>3</v>
@@ -8031,7 +8028,7 @@
         <v>38</v>
       </c>
       <c r="V93" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W93" s="1" t="s">
         <v>39</v>
@@ -8039,25 +8036,25 @@
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B94">
         <v>10149</v>
       </c>
       <c r="C94" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D94" t="s">
         <v>26</v>
       </c>
       <c r="E94" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F94" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G94" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H94">
         <v>12.89515492</v>
@@ -8072,7 +8069,7 @@
         <v>937997757</v>
       </c>
       <c r="L94" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M94">
         <v>2</v>
@@ -8102,7 +8099,7 @@
         <v>38</v>
       </c>
       <c r="V94" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W94" s="1" t="s">
         <v>39</v>
@@ -8110,25 +8107,25 @@
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B95">
         <v>10150</v>
       </c>
       <c r="C95" t="s">
+        <v>316</v>
+      </c>
+      <c r="D95" t="s">
+        <v>26</v>
+      </c>
+      <c r="E95" t="s">
+        <v>128</v>
+      </c>
+      <c r="F95" t="s">
+        <v>95</v>
+      </c>
+      <c r="G95" t="s">
         <v>318</v>
-      </c>
-      <c r="D95" t="s">
-        <v>26</v>
-      </c>
-      <c r="E95" t="s">
-        <v>130</v>
-      </c>
-      <c r="F95" t="s">
-        <v>97</v>
-      </c>
-      <c r="G95" t="s">
-        <v>320</v>
       </c>
       <c r="H95">
         <v>33.995612000000001</v>
@@ -8143,7 +8140,7 @@
         <v>803062069</v>
       </c>
       <c r="L95" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="M95">
         <v>2</v>
@@ -8170,10 +8167,10 @@
         <v>37</v>
       </c>
       <c r="U95" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V95" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="W95" s="1" t="s">
         <v>39</v>
@@ -8181,25 +8178,25 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B96">
         <v>10151</v>
       </c>
       <c r="C96" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D96" t="s">
         <v>26</v>
       </c>
       <c r="E96" t="s">
+        <v>321</v>
+      </c>
+      <c r="F96" t="s">
+        <v>322</v>
+      </c>
+      <c r="G96" t="s">
         <v>323</v>
-      </c>
-      <c r="F96" t="s">
-        <v>324</v>
-      </c>
-      <c r="G96" t="s">
-        <v>325</v>
       </c>
       <c r="H96">
         <v>78.547799999999995</v>
@@ -8214,7 +8211,7 @@
         <v>9663089998</v>
       </c>
       <c r="L96" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="M96">
         <v>0</v>
@@ -8238,13 +8235,13 @@
         <v>0</v>
       </c>
       <c r="T96" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="U96" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V96" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="W96" s="1" t="s">
         <v>39</v>

--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE7CDB4-06D1-4ADC-8729-3D6382ABC5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8125BF4A-63F7-4DB7-BFB3-E7F018E4C43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2140" yWindow="6800" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>lang_code</t>
   </si>
@@ -117,9 +117,6 @@
     <t>MyCountry</t>
   </si>
   <si>
-    <t>MOR</t>
-  </si>
-  <si>
     <t>24:00:00</t>
   </si>
   <si>
@@ -139,9 +136,6 @@
   </si>
   <si>
     <t>(GTM+01:00) CENTRAL EUROPEAN TIME</t>
-  </si>
-  <si>
-    <t>KTA</t>
   </si>
   <si>
     <t>TRUE</t>
@@ -661,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -670,34 +664,34 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
         <v>31</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>32</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>34</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>35</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>36</v>
-      </c>
-      <c r="T2" t="s">
-        <v>37</v>
       </c>
       <c r="U2" t="s">
         <v>38</v>
       </c>
       <c r="V2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="5:7" x14ac:dyDescent="0.35">

--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8125BF4A-63F7-4DB7-BFB3-E7F018E4C43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D28E87-8E68-4306-902C-2A2D883F9F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4180" yWindow="4180" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
   <si>
     <t>lang_code</t>
   </si>
@@ -103,9 +103,6 @@
   </si>
   <si>
     <t>Virtual centre</t>
-  </si>
-  <si>
-    <t>REG</t>
   </si>
   <si>
     <t>Virtual address 1</t>
@@ -637,16 +634,16 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>28</v>
-      </c>
-      <c r="G2" t="s">
-        <v>29</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -655,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -664,34 +661,34 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" t="s">
         <v>30</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>31</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>33</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>34</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>35</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="U2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" t="s">
-        <v>38</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="34" spans="5:7" x14ac:dyDescent="0.35">

--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D28E87-8E68-4306-902C-2A2D883F9F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DCE186-7A97-46DE-ADD3-8ED8E0E11005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4180" yWindow="4180" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22650" yWindow="7820" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>lang_code</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>UTO</t>
+  </si>
+  <si>
+    <t>REG</t>
   </si>
 </sst>
 </file>
@@ -634,7 +637,7 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>26</v>

--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF15062-A65D-403A-9F7D-D4D7B3252263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50CA5E7-C346-4A90-9CEB-D704FCEE522A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25620" yWindow="4000" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -36,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="337">
   <si>
     <t>lang_code</t>
   </si>
@@ -125,6 +114,12 @@
     <t>Virtual address 2</t>
   </si>
   <si>
+    <t>MyCountry</t>
+  </si>
+  <si>
+    <t>MOR</t>
+  </si>
+  <si>
     <t>24:00:00</t>
   </si>
   <si>
@@ -146,10 +141,901 @@
     <t>(GTM+01:00) CENTRAL EUROPEAN TIME</t>
   </si>
   <si>
+    <t>KTA</t>
+  </si>
+  <si>
     <t>TRUE</t>
   </si>
   <si>
-    <t>UTO</t>
+    <t>fra</t>
+  </si>
+  <si>
+    <t>Center A Ben Mansour</t>
+  </si>
+  <si>
+    <t>P4238</t>
+  </si>
+  <si>
+    <t>Ben Mansour</t>
+  </si>
+  <si>
+    <t>John Doe</t>
+  </si>
+  <si>
+    <t>8:00:00</t>
+  </si>
+  <si>
+    <t>9:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>RBT</t>
+  </si>
+  <si>
+    <t>Centre A Ben Mansour</t>
+  </si>
+  <si>
+    <t>Maroc</t>
+  </si>
+  <si>
+    <t>GTM + 01h00) HEURE EUROPEENNE CENTRALE</t>
+  </si>
+  <si>
+    <t>Rural Municipal Mnasra</t>
+  </si>
+  <si>
+    <t>Route De Moulay Bousselham</t>
+  </si>
+  <si>
+    <t>Douar Sbih Menacera</t>
+  </si>
+  <si>
+    <t>John Smith</t>
+  </si>
+  <si>
+    <t>Commune Rurale Mnasra</t>
+  </si>
+  <si>
+    <t>Souk Khemiss Mograne</t>
+  </si>
+  <si>
+    <t>Route N1</t>
+  </si>
+  <si>
+    <t>Mograne</t>
+  </si>
+  <si>
+    <t>Mario Speedwagon</t>
+  </si>
+  <si>
+    <t>SAL</t>
+  </si>
+  <si>
+    <t>la route N1</t>
+  </si>
+  <si>
+    <t>Center Assam</t>
+  </si>
+  <si>
+    <t>7 Km Tangier Road</t>
+  </si>
+  <si>
+    <t>Kenitra</t>
+  </si>
+  <si>
+    <t>Paige Turner</t>
+  </si>
+  <si>
+    <t>centre assam</t>
+  </si>
+  <si>
+    <t>km 7 route de Tanger</t>
+  </si>
+  <si>
+    <t>Kénitra</t>
+  </si>
+  <si>
+    <t>Center Mehdia</t>
+  </si>
+  <si>
+    <t>Mehdia Road Amria mehdia</t>
+  </si>
+  <si>
+    <t>Walter Melon</t>
+  </si>
+  <si>
+    <t>BSN</t>
+  </si>
+  <si>
+    <t>centre mehdia</t>
+  </si>
+  <si>
+    <t>route de mehdia Amria mehdia</t>
+  </si>
+  <si>
+    <t>Center Ouled Oujih</t>
+  </si>
+  <si>
+    <t>Bloc 1 G1 N113</t>
+  </si>
+  <si>
+    <t>Barb Ackue</t>
+  </si>
+  <si>
+    <t>NDR</t>
+  </si>
+  <si>
+    <t>center Ouled Oujih</t>
+  </si>
+  <si>
+    <t>Center Sidi Taibi</t>
+  </si>
+  <si>
+    <t>Rabat Road</t>
+  </si>
+  <si>
+    <t>Sidi Taibi</t>
+  </si>
+  <si>
+    <t>Monty Carlo</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>centre Sidi Taibi</t>
+  </si>
+  <si>
+    <t>Route de Rabat</t>
+  </si>
+  <si>
+    <t>Center Sidi Allal Tazi</t>
+  </si>
+  <si>
+    <t>National Road</t>
+  </si>
+  <si>
+    <t>Alla Tazi</t>
+  </si>
+  <si>
+    <t>Cliff Hanger</t>
+  </si>
+  <si>
+    <t>SAF</t>
+  </si>
+  <si>
+    <t>centre Sidi Allal Tazi</t>
+  </si>
+  <si>
+    <t>route nationale</t>
+  </si>
+  <si>
+    <t>Center Agdal</t>
+  </si>
+  <si>
+    <t>French Avenue</t>
+  </si>
+  <si>
+    <t>Rabat</t>
+  </si>
+  <si>
+    <t>Robin Banks</t>
+  </si>
+  <si>
+    <t>YSF</t>
+  </si>
+  <si>
+    <t>centre Agdal</t>
+  </si>
+  <si>
+    <t>avenue de France</t>
+  </si>
+  <si>
+    <t>Center Hassan</t>
+  </si>
+  <si>
+    <t>Avenue Amir Moulay Abdellah</t>
+  </si>
+  <si>
+    <t>Max Emum</t>
+  </si>
+  <si>
+    <t>TTA</t>
+  </si>
+  <si>
+    <t>centre Hassan</t>
+  </si>
+  <si>
+    <t>avenue de Amir Moulay Abdellah</t>
+  </si>
+  <si>
+    <t>Center Souissi</t>
+  </si>
+  <si>
+    <t>Avenue Mohamed VI</t>
+  </si>
+  <si>
+    <t>Minnie Mum</t>
+  </si>
+  <si>
+    <t>TZT</t>
+  </si>
+  <si>
+    <t>centre Souissi</t>
+  </si>
+  <si>
+    <t>avenue de Mohammed VI</t>
+  </si>
+  <si>
+    <t>Center Madinat Al Irfane</t>
+  </si>
+  <si>
+    <t>Avenue Allal Al Fassi</t>
+  </si>
+  <si>
+    <t>Bill Yerds</t>
+  </si>
+  <si>
+    <t>centre Madinat Al Irfane</t>
+  </si>
+  <si>
+    <t>avenue de Allal Al Fassi</t>
+  </si>
+  <si>
+    <t>Center Hay Riad</t>
+  </si>
+  <si>
+    <t>Avenue Al Araar</t>
+  </si>
+  <si>
+    <t>Dan Druff</t>
+  </si>
+  <si>
+    <t>centre Hay Riad</t>
+  </si>
+  <si>
+    <t>avenue de Al Araar</t>
+  </si>
+  <si>
+    <t>Center Medina</t>
+  </si>
+  <si>
+    <t>Street of the Consuls</t>
+  </si>
+  <si>
+    <t>Rick Shaw</t>
+  </si>
+  <si>
+    <t>centre Medina</t>
+  </si>
+  <si>
+    <t>Rue des Consuls</t>
+  </si>
+  <si>
+    <t>Center Youssoufia</t>
+  </si>
+  <si>
+    <t>Avenue Ouzguita</t>
+  </si>
+  <si>
+    <t>Mick Donalds</t>
+  </si>
+  <si>
+    <t>centre Youssoufia</t>
+  </si>
+  <si>
+    <t>avenue de Ouzguita</t>
+  </si>
+  <si>
+    <t>kan</t>
+  </si>
+  <si>
+    <t>ವರ್ಚುವಲ್ ಸೆಂಟರ್</t>
+  </si>
+  <si>
+    <t>ವರ್ಚುವಲ್ ವಿಳಾಸ 1</t>
+  </si>
+  <si>
+    <t>ವರ್ಚುವಲ್ ವಿಳಾಸ 2</t>
+  </si>
+  <si>
+    <t>ನನ್ನ ದೇಶ</t>
+  </si>
+  <si>
+    <t>ಸೆಂಟರ್ ಎ ಬೆನ್ ಮನ್ಸೂರ್</t>
+  </si>
+  <si>
+    <t>ಬೆನ್ ಮನ್ಸೂರ್</t>
+  </si>
+  <si>
+    <t>ಜಾನ್ ಡೋ</t>
+  </si>
+  <si>
+    <t>ಗ್ರಾಮೀಣ ಪುರಸಭೆ ಮ್ನಾಸ್ರಾ</t>
+  </si>
+  <si>
+    <t>ಮಾರ್ಗ ಡಿ ಮೌಲೆ ಬೌಸೆಲ್‌ಹ್ಯಾಮ್</t>
+  </si>
+  <si>
+    <t>ಡೌರ್ ಸ್ಬಿಹ್ ಮೆನಾಸೆರಾ</t>
+  </si>
+  <si>
+    <t>ಜಾನ್ ಸ್ಮಿತ್</t>
+  </si>
+  <si>
+    <t>ಸೌಕ್ ಖೆಮಿಸ್ ಮೊಗ್ರಾನ್</t>
+  </si>
+  <si>
+    <t>ಮಾರ್ಗ N1</t>
+  </si>
+  <si>
+    <t>ಮೈಗ್ರೇನ್</t>
+  </si>
+  <si>
+    <t>ಮಾರಿಯೋ ಸ್ಪೀಡ್‌ವ್ಯಾಗನ್</t>
+  </si>
+  <si>
+    <t>ಕೇಂದ್ರ ಅಸ್ಸಾಂ</t>
+  </si>
+  <si>
+    <t>7 ಕಿಮೀ ಟ್ಯಾಂಜಿಯರ್ ರಸ್ತೆ</t>
+  </si>
+  <si>
+    <t>ಕೆನಿತ್ರಾ</t>
+  </si>
+  <si>
+    <t>ಪೈಜ್ ಟರ್ನರ್</t>
+  </si>
+  <si>
+    <t>ಸೆಂಟರ್ ಮೆಹದಿಯಾ</t>
+  </si>
+  <si>
+    <t>ಮೆಹದಿಯಾ ರಸ್ತೆ ಅಮ್ರಿಯಾ ಮೆಹದಿಯಾ</t>
+  </si>
+  <si>
+    <t>ಮರೋಕ್</t>
+  </si>
+  <si>
+    <t>ವಾಲ್ಟರ್ ಕಲ್ಲಂಗಡಿ</t>
+  </si>
+  <si>
+    <t>ಸೆಂಟರ್ Ouled Oujih</t>
+  </si>
+  <si>
+    <t>ಬ್ಲಾಕ್ 1 G1 N113</t>
+  </si>
+  <si>
+    <t>ಬಾರ್ಬ್ ಅಕ್ಯು</t>
+  </si>
+  <si>
+    <t>ಕೇಂದ್ರ ಸಿಡಿ ತೈಬಿ</t>
+  </si>
+  <si>
+    <t>ರಬತ್ ರಸ್ತೆ</t>
+  </si>
+  <si>
+    <t>ಸಿಡಿ ತೈಬಿ</t>
+  </si>
+  <si>
+    <t>ಮಾಂಟೆ ಕಾರ್ಲೊ</t>
+  </si>
+  <si>
+    <t>ಸೆಂಟರ್ ಸಿಡಿ ಅಲ್ಲಲ್ ತಾಜಿ</t>
+  </si>
+  <si>
+    <t>ರಾಷ್ಟ್ರೀಯ ರಸ್ತೆ</t>
+  </si>
+  <si>
+    <t>ಅಲ್ಲಾ ತಾಜಿ</t>
+  </si>
+  <si>
+    <t>ಕ್ಲಿಫ್ ಹ್ಯಾಂಗರ್</t>
+  </si>
+  <si>
+    <t>ಕೇಂದ್ರ ಅಗ್ಡಾಲ್</t>
+  </si>
+  <si>
+    <t>ಫ್ರೆಂಚ್ ಅವೆನ್ಯೂ</t>
+  </si>
+  <si>
+    <t>ರಬತ್</t>
+  </si>
+  <si>
+    <t>ರಾಬಿನ್ ಬ್ಯಾಂಕ್ಸ್</t>
+  </si>
+  <si>
+    <t>ಕೇಂದ್ರ ಹಾಸನ</t>
+  </si>
+  <si>
+    <t>ಅವೆನ್ಯೂ ಅಮೀರ್ ಮೌಲೆ ಅಬ್ದುಲ್ಲಾ</t>
+  </si>
+  <si>
+    <t>ಮ್ಯಾಕ್ಸ್ ಎಮುಮ್</t>
+  </si>
+  <si>
+    <t>ಸೆಂಟರ್ ಸೌಸಿ</t>
+  </si>
+  <si>
+    <t>ಅವೆನ್ಯೂ ಮೊಹಮ್ಮದ್ VI</t>
+  </si>
+  <si>
+    <t>ಮಿನ್ನಿ ಅಮ್ಮ</t>
+  </si>
+  <si>
+    <t>ಸೆಂಟರ್ ಮದೀನತ್ ಅಲ್ ಇರ್ಫಾನೆ</t>
+  </si>
+  <si>
+    <t>ಅವೆನ್ಯೂ ಅಲ್ಲಲ್ ಅಲ್ ಫಾಸ್ಸಿ</t>
+  </si>
+  <si>
+    <t>ಬಿಲ್ ಯಾರ್ಡ್ಸ್</t>
+  </si>
+  <si>
+    <t>ಸೆಂಟರ್ ಹೇ ರಿಯಾಡ್</t>
+  </si>
+  <si>
+    <t>ಅವೆನ್ಯೂ ಅಲ್ ಅರಾರ್</t>
+  </si>
+  <si>
+    <t>ಡಾನ್ ಡ್ರಫ್</t>
+  </si>
+  <si>
+    <t>ಸೆಂಟರ್ ಮದೀನಾ</t>
+  </si>
+  <si>
+    <t>ಕಾನ್ಸುಲ್‌ಗಳ ಬೀದಿ</t>
+  </si>
+  <si>
+    <t>ರಿಕ್ ಶಾ</t>
+  </si>
+  <si>
+    <t>ಸೆಂಟರ್ ಯೂಸೌಫಿಯಾ</t>
+  </si>
+  <si>
+    <t>ಅವೆನ್ಯೂ ಔಜ್ಗುಯಿಟಾ</t>
+  </si>
+  <si>
+    <t>ಮಿಕ್ ಡೊನಾಲ್ಡ್ಸ್</t>
+  </si>
+  <si>
+    <t>hin</t>
+  </si>
+  <si>
+    <t>आभासी केंद्र</t>
+  </si>
+  <si>
+    <t>आभासी पता 1</t>
+  </si>
+  <si>
+    <t>आभासी पता 2</t>
+  </si>
+  <si>
+    <t>मेरा देश</t>
+  </si>
+  <si>
+    <t>सेंटर ए बेन मंसूर</t>
+  </si>
+  <si>
+    <t>बेन मंसूर</t>
+  </si>
+  <si>
+    <t>जॉन डो</t>
+  </si>
+  <si>
+    <t>ग्रामीण नगर मनसराय</t>
+  </si>
+  <si>
+    <t>रूट डी मौले बौसेलहैम</t>
+  </si>
+  <si>
+    <t>डौर सबिह मेनसेरा</t>
+  </si>
+  <si>
+    <t>जॉन स्मिथ</t>
+  </si>
+  <si>
+    <t>सूक खेमिस मोग्रेन</t>
+  </si>
+  <si>
+    <t>मार्ग N1</t>
+  </si>
+  <si>
+    <t>माइग्रेन</t>
+  </si>
+  <si>
+    <t>मारियो स्पीडवैगन</t>
+  </si>
+  <si>
+    <t>केंद्र असम</t>
+  </si>
+  <si>
+    <t>7 किमी टंगेर रोड</t>
+  </si>
+  <si>
+    <t>केनिट्रा</t>
+  </si>
+  <si>
+    <t>पैगे टर्नर</t>
+  </si>
+  <si>
+    <t>केंद्र मेहदिया</t>
+  </si>
+  <si>
+    <t>मेहदिया रोड अमरिया मेहदिया</t>
+  </si>
+  <si>
+    <t>मारोसी</t>
+  </si>
+  <si>
+    <t>वाल्टर मेलन</t>
+  </si>
+  <si>
+    <t>केंद्र औलेड औजिहो</t>
+  </si>
+  <si>
+    <t>ब्लॉक 1 G1 N113</t>
+  </si>
+  <si>
+    <t>बार्ब एक्यू</t>
+  </si>
+  <si>
+    <t>केंद्र सिदी ताइबिक</t>
+  </si>
+  <si>
+    <t>रबत रोड</t>
+  </si>
+  <si>
+    <t>सिदी ताइबि</t>
+  </si>
+  <si>
+    <t>मौंटे कारलो</t>
+  </si>
+  <si>
+    <t>केंद्र सिदी अल्लाल ताज़िक</t>
+  </si>
+  <si>
+    <t>राष्ट्रीय सड़क</t>
+  </si>
+  <si>
+    <t>अल्ला ताज़िक</t>
+  </si>
+  <si>
+    <t>चट्टान हैंगर</t>
+  </si>
+  <si>
+    <t>केंद्र Agdal</t>
+  </si>
+  <si>
+    <t>फ्रेंच एवेन्यू</t>
+  </si>
+  <si>
+    <t>रबात</t>
+  </si>
+  <si>
+    <t>रॉबिन बैंक्स</t>
+  </si>
+  <si>
+    <t>केंद्र हसन</t>
+  </si>
+  <si>
+    <t>एवेन्यू अमीर मौले अब्देलाह</t>
+  </si>
+  <si>
+    <t>मैक्स एमम</t>
+  </si>
+  <si>
+    <t>केंद्र सूसी</t>
+  </si>
+  <si>
+    <t>एवेन्यू मोहम्मद VI</t>
+  </si>
+  <si>
+    <t>मिन्नी माँ</t>
+  </si>
+  <si>
+    <t>केंद्र मदीनत अल इरफान</t>
+  </si>
+  <si>
+    <t>एवेन्यू अल्लाल अल फसी</t>
+  </si>
+  <si>
+    <t>बिल येर्ड्स</t>
+  </si>
+  <si>
+    <t>केंद्र हे Riad</t>
+  </si>
+  <si>
+    <t>एवेन्यू अल अरारी</t>
+  </si>
+  <si>
+    <t>रूसी</t>
+  </si>
+  <si>
+    <t>केंद्र मदीना</t>
+  </si>
+  <si>
+    <t>कौंसल की सड़क</t>
+  </si>
+  <si>
+    <t>रिक शॉ</t>
+  </si>
+  <si>
+    <t>केंद्र युसूफिया</t>
+  </si>
+  <si>
+    <t>एवेन्यू औजगुइटा</t>
+  </si>
+  <si>
+    <t>मिक डोनाल्ड्स</t>
+  </si>
+  <si>
+    <t>tam</t>
+  </si>
+  <si>
+    <t>மெய்நிகர் மையம்</t>
+  </si>
+  <si>
+    <t>மெய்நிகர் முகவரி 1</t>
+  </si>
+  <si>
+    <t>மெய்நிகர் முகவரி 2</t>
+  </si>
+  <si>
+    <t>என் நாடு</t>
+  </si>
+  <si>
+    <t>சென்டர் ஏ பென் மன்சூர்</t>
+  </si>
+  <si>
+    <t>பென் மன்சூர்</t>
+  </si>
+  <si>
+    <t>ஜான் டோ</t>
+  </si>
+  <si>
+    <t>கிராமப்புற முனிசிபல் மனாஸ்ரா</t>
+  </si>
+  <si>
+    <t>பாதை டி மௌலே பௌசல்ஹாம்</t>
+  </si>
+  <si>
+    <t>ஜான் ஸ்மித்</t>
+  </si>
+  <si>
+    <t>Souk Kemiss Mograne</t>
+  </si>
+  <si>
+    <t>பாதை N1</t>
+  </si>
+  <si>
+    <t>ஒற்றைத் தலைவலி</t>
+  </si>
+  <si>
+    <t>மரியோ ஸ்பீட்வேகன்</t>
+  </si>
+  <si>
+    <t>அசாம் மையம்</t>
+  </si>
+  <si>
+    <t>7 கிமீ டேன்ஜியர் சாலை</t>
+  </si>
+  <si>
+    <t>கெனிட்ரா</t>
+  </si>
+  <si>
+    <t>பைஜ் டர்னர்</t>
+  </si>
+  <si>
+    <t>மையம் மெஹதியா</t>
+  </si>
+  <si>
+    <t>மெஹ்தியா சாலை அம்ரியா மெஹதியா</t>
+  </si>
+  <si>
+    <t>மரோக்</t>
+  </si>
+  <si>
+    <t>வால்டர் முலாம்பழம்</t>
+  </si>
+  <si>
+    <t>மையம் Ouled Oujih</t>
+  </si>
+  <si>
+    <t>தொகுதி 1 G1 N113</t>
+  </si>
+  <si>
+    <t>பார்ப் அக்யூ</t>
+  </si>
+  <si>
+    <t>மையம் சிடி தைபி</t>
+  </si>
+  <si>
+    <t>ரபாத் சாலை</t>
+  </si>
+  <si>
+    <t>சிடி தைபி</t>
+  </si>
+  <si>
+    <t>மான்டே கார்லோ</t>
+  </si>
+  <si>
+    <t>மையம் சிடி அல்லல் தாஜி</t>
+  </si>
+  <si>
+    <t>தேசிய சாலை</t>
+  </si>
+  <si>
+    <t>அல்லா தாசி</t>
+  </si>
+  <si>
+    <t>கிளிஃப் ஹேங்கர்</t>
+  </si>
+  <si>
+    <t>மையம் அக்டல்</t>
+  </si>
+  <si>
+    <t>பிரஞ்சு அவென்யூ</t>
+  </si>
+  <si>
+    <t>ரபாத்</t>
+  </si>
+  <si>
+    <t>ராபின் வங்கிகள்</t>
+  </si>
+  <si>
+    <t>மையம் ஹாசன்</t>
+  </si>
+  <si>
+    <t>அவென்யூ அமீர் மௌலே அப்தெல்லா</t>
+  </si>
+  <si>
+    <t>அதிகபட்ச ஈமம்</t>
+  </si>
+  <si>
+    <t>மையம் Souissi</t>
+  </si>
+  <si>
+    <t>அவென்யூ முகமது VI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> மின்னி அம்மா</t>
+  </si>
+  <si>
+    <t>மதீனத் அல் இர்ஃபேன் மையம்</t>
+  </si>
+  <si>
+    <t>அவென்யூ அல்லால் அல் ஃபாஸி</t>
+  </si>
+  <si>
+    <t>பில் யார்ட்ஸ்</t>
+  </si>
+  <si>
+    <t>மையம் ஹே ரியாட்</t>
+  </si>
+  <si>
+    <t>அவென்யூ அல் அரார்</t>
+  </si>
+  <si>
+    <t>டான் ட்ரஃப்</t>
+  </si>
+  <si>
+    <t>மதீனா மையம்</t>
+  </si>
+  <si>
+    <t>தூதரகத்தின் தெரு</t>
+  </si>
+  <si>
+    <t>ரிக் ஷா</t>
+  </si>
+  <si>
+    <t>மையம் யூசுஃபியா</t>
+  </si>
+  <si>
+    <t>அவென்யூ Ouzguita</t>
+  </si>
+  <si>
+    <t>மிக் டொனால்ட்ஸ்</t>
+  </si>
+  <si>
+    <t>spa</t>
+  </si>
+  <si>
+    <t>Mnasra Rural Municipal</t>
+  </si>
+  <si>
+    <t>Zoco Khemiss Mograne</t>
+  </si>
+  <si>
+    <t>Centro Mehdia</t>
+  </si>
+  <si>
+    <t>Centro Ouled Oujih</t>
+  </si>
+  <si>
+    <t>Centro Sidi Taibi</t>
+  </si>
+  <si>
+    <t>Centro Agdal</t>
+  </si>
+  <si>
+    <t>Centro Hassan</t>
+  </si>
+  <si>
+    <t>Centro Souissi</t>
+  </si>
+  <si>
+    <t>Centro Madinat Al Irfane</t>
+  </si>
+  <si>
+    <t>Centro Hay Riad</t>
+  </si>
+  <si>
+    <t>Centro Medina</t>
+  </si>
+  <si>
+    <t>Centro A Ben Mansour</t>
+  </si>
+  <si>
+    <t>Centro de Assam</t>
+  </si>
+  <si>
+    <t>Centro Youssoufia</t>
+  </si>
+  <si>
+    <t>Centro de pruebas Sidi Allal Tazi</t>
+  </si>
+  <si>
+    <t>Mi pais</t>
+  </si>
+  <si>
+    <t>marruecos</t>
+  </si>
+  <si>
+    <t>País</t>
+  </si>
+  <si>
+    <t>National Road Test</t>
+  </si>
+  <si>
+    <t>Prueba de Alla Tazi</t>
+  </si>
+  <si>
+    <t>Prueba de mi país</t>
+  </si>
+  <si>
+    <t>Walter Melón</t>
+  </si>
+  <si>
+    <t>Barb Accue</t>
+  </si>
+  <si>
+    <t>Robin Bancos</t>
+  </si>
+  <si>
+    <t>mamá minnie</t>
+  </si>
+  <si>
+    <t>Caspa</t>
+  </si>
+  <si>
+    <t>Bicitaxi</t>
+  </si>
+  <si>
+    <t>Juan Pérez</t>
+  </si>
+  <si>
+    <t>mick donalds</t>
+  </si>
+  <si>
+    <t>Prueba de suspensión de acantilados</t>
+  </si>
+  <si>
+    <t>Test Time zone</t>
+  </si>
+  <si>
+    <t>CSB</t>
   </si>
 </sst>
 </file>
@@ -206,7 +1092,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -218,6 +1104,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -236,9 +1126,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -276,7 +1166,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -382,7 +1272,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -524,7 +1414,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -532,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W96"/>
   <sheetFormatPr defaultColWidth="11.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.26953125" customWidth="1"/>
@@ -650,7 +1540,7 @@
         <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -659,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -668,34 +1558,6696 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
         <v>29</v>
       </c>
-      <c r="O2" t="s">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P2" t="s">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="O3" t="s">
         <v>32</v>
       </c>
-      <c r="R2" t="s">
+      <c r="P3" t="s">
         <v>33</v>
       </c>
-      <c r="S2" t="s">
+      <c r="Q3" t="s">
         <v>34</v>
       </c>
-      <c r="T2" t="s">
+      <c r="R3" t="s">
         <v>35</v>
       </c>
-      <c r="U2" t="s">
+      <c r="S3" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" t="s">
         <v>37</v>
       </c>
-      <c r="V2" t="s">
+      <c r="U3" t="s">
+        <v>38</v>
+      </c>
+      <c r="V3" t="s">
+        <v>30</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="1">
+        <v>10001</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4">
+        <v>34.521169999999998</v>
+      </c>
+      <c r="I4">
+        <v>-6.4532749999999997</v>
+      </c>
+      <c r="J4" s="2">
+        <v>14022</v>
+      </c>
+      <c r="K4">
+        <v>779517433</v>
+      </c>
+      <c r="L4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4">
+        <v>3</v>
+      </c>
+      <c r="N4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R4" t="s">
+        <v>35</v>
+      </c>
+      <c r="S4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" t="s">
         <v>37</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="U4" t="s">
+        <v>38</v>
+      </c>
+      <c r="V4" t="s">
+        <v>48</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="1">
+        <v>10001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>34.521169999999998</v>
+      </c>
+      <c r="I5">
+        <v>-6.4532749999999997</v>
+      </c>
+      <c r="J5" s="2">
+        <v>14022</v>
+      </c>
+      <c r="K5">
+        <v>993556086</v>
+      </c>
+      <c r="L5" t="s">
+        <v>44</v>
+      </c>
+      <c r="M5">
+        <v>3</v>
+      </c>
+      <c r="N5" t="s">
+        <v>45</v>
+      </c>
+      <c r="O5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>47</v>
+      </c>
+      <c r="R5" t="s">
+        <v>35</v>
+      </c>
+      <c r="S5" t="s">
         <v>36</v>
+      </c>
+      <c r="T5" t="s">
+        <v>51</v>
+      </c>
+      <c r="U5" t="s">
+        <v>38</v>
+      </c>
+      <c r="V5" t="s">
+        <v>48</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="1">
+        <v>10002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6">
+        <v>34.360207000000003</v>
+      </c>
+      <c r="I6">
+        <v>-6.5500749999999996</v>
+      </c>
+      <c r="J6" s="2">
+        <v>14053</v>
+      </c>
+      <c r="K6">
+        <v>753476995</v>
+      </c>
+      <c r="L6" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6" t="s">
+        <v>45</v>
+      </c>
+      <c r="O6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6" t="s">
+        <v>35</v>
+      </c>
+      <c r="S6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" t="s">
+        <v>37</v>
+      </c>
+      <c r="U6" t="s">
+        <v>38</v>
+      </c>
+      <c r="V6" t="s">
+        <v>38</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="1">
+        <v>10002</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>34.360207000000003</v>
+      </c>
+      <c r="I7">
+        <v>-6.5500749999999996</v>
+      </c>
+      <c r="J7" s="2">
+        <v>14053</v>
+      </c>
+      <c r="K7">
+        <v>984996886</v>
+      </c>
+      <c r="L7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7" t="s">
+        <v>45</v>
+      </c>
+      <c r="O7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R7" t="s">
+        <v>35</v>
+      </c>
+      <c r="S7" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" t="s">
+        <v>51</v>
+      </c>
+      <c r="U7" t="s">
+        <v>38</v>
+      </c>
+      <c r="V7" t="s">
+        <v>38</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1">
+        <v>10003</v>
+      </c>
+      <c r="C8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>34.405692000000002</v>
+      </c>
+      <c r="I8">
+        <v>-6.4333679999999998</v>
+      </c>
+      <c r="J8" s="2">
+        <v>14023</v>
+      </c>
+      <c r="K8">
+        <v>734239083</v>
+      </c>
+      <c r="L8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M8">
+        <v>4</v>
+      </c>
+      <c r="N8" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>47</v>
+      </c>
+      <c r="R8" t="s">
+        <v>35</v>
+      </c>
+      <c r="S8" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" t="s">
+        <v>37</v>
+      </c>
+      <c r="U8" t="s">
+        <v>38</v>
+      </c>
+      <c r="V8" t="s">
+        <v>61</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="1">
+        <v>10003</v>
+      </c>
+      <c r="C9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9">
+        <v>34.405692000000002</v>
+      </c>
+      <c r="I9">
+        <v>-6.4333679999999998</v>
+      </c>
+      <c r="J9" s="2">
+        <v>14023</v>
+      </c>
+      <c r="K9">
+        <v>675470523</v>
+      </c>
+      <c r="L9" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9">
+        <v>4</v>
+      </c>
+      <c r="N9" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>47</v>
+      </c>
+      <c r="R9" t="s">
+        <v>35</v>
+      </c>
+      <c r="S9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" t="s">
+        <v>51</v>
+      </c>
+      <c r="U9" t="s">
+        <v>38</v>
+      </c>
+      <c r="V9" t="s">
+        <v>61</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1">
+        <v>10004</v>
+      </c>
+      <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10">
+        <v>34.287878999999997</v>
+      </c>
+      <c r="I10">
+        <v>-6.5164280000000003</v>
+      </c>
+      <c r="J10" s="2">
+        <v>14000</v>
+      </c>
+      <c r="K10">
+        <v>937997757</v>
+      </c>
+      <c r="L10" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10">
+        <v>2</v>
+      </c>
+      <c r="N10" t="s">
+        <v>45</v>
+      </c>
+      <c r="O10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>47</v>
+      </c>
+      <c r="R10" t="s">
+        <v>35</v>
+      </c>
+      <c r="S10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T10" t="s">
+        <v>37</v>
+      </c>
+      <c r="U10" t="s">
+        <v>38</v>
+      </c>
+      <c r="V10" t="s">
+        <v>48</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="1">
+        <v>10004</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11">
+        <v>34.287878999999997</v>
+      </c>
+      <c r="I11">
+        <v>-6.5164280000000003</v>
+      </c>
+      <c r="J11" s="2">
+        <v>14000</v>
+      </c>
+      <c r="K11">
+        <v>852492117</v>
+      </c>
+      <c r="L11" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11">
+        <v>2</v>
+      </c>
+      <c r="N11" t="s">
+        <v>45</v>
+      </c>
+      <c r="O11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>47</v>
+      </c>
+      <c r="R11" t="s">
+        <v>35</v>
+      </c>
+      <c r="S11" t="s">
+        <v>36</v>
+      </c>
+      <c r="T11" t="s">
+        <v>51</v>
+      </c>
+      <c r="U11" t="s">
+        <v>38</v>
+      </c>
+      <c r="V11" t="s">
+        <v>48</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1">
+        <v>10005</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12">
+        <v>34.256413999999999</v>
+      </c>
+      <c r="I12">
+        <v>-6.6754990000000003</v>
+      </c>
+      <c r="J12" s="2">
+        <v>14110</v>
+      </c>
+      <c r="K12">
+        <v>887311749</v>
+      </c>
+      <c r="L12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P12" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>47</v>
+      </c>
+      <c r="R12" t="s">
+        <v>35</v>
+      </c>
+      <c r="S12" t="s">
+        <v>36</v>
+      </c>
+      <c r="T12" t="s">
+        <v>37</v>
+      </c>
+      <c r="U12" t="s">
+        <v>38</v>
+      </c>
+      <c r="V12" t="s">
+        <v>73</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="1">
+        <v>10005</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13">
+        <v>34.256413999999999</v>
+      </c>
+      <c r="I13">
+        <v>-6.6754990000000003</v>
+      </c>
+      <c r="J13" s="2">
+        <v>14110</v>
+      </c>
+      <c r="K13">
+        <v>658302699</v>
+      </c>
+      <c r="L13" t="s">
+        <v>72</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13" t="s">
+        <v>45</v>
+      </c>
+      <c r="O13" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>47</v>
+      </c>
+      <c r="R13" t="s">
+        <v>35</v>
+      </c>
+      <c r="S13" t="s">
+        <v>36</v>
+      </c>
+      <c r="T13" t="s">
+        <v>51</v>
+      </c>
+      <c r="U13" t="s">
+        <v>38</v>
+      </c>
+      <c r="V13" t="s">
+        <v>73</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1">
+        <v>10006</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14">
+        <v>34.262476999999997</v>
+      </c>
+      <c r="I14">
+        <v>-6.6186049999999996</v>
+      </c>
+      <c r="J14" s="2">
+        <v>14080</v>
+      </c>
+      <c r="K14">
+        <v>915790305</v>
+      </c>
+      <c r="L14" t="s">
+        <v>78</v>
+      </c>
+      <c r="M14">
+        <v>5</v>
+      </c>
+      <c r="N14" t="s">
+        <v>45</v>
+      </c>
+      <c r="O14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P14" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>47</v>
+      </c>
+      <c r="R14" t="s">
+        <v>35</v>
+      </c>
+      <c r="S14" t="s">
+        <v>36</v>
+      </c>
+      <c r="T14" t="s">
+        <v>37</v>
+      </c>
+      <c r="U14" t="s">
+        <v>38</v>
+      </c>
+      <c r="V14" t="s">
+        <v>79</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1">
+        <v>10006</v>
+      </c>
+      <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15">
+        <v>34.262476999999997</v>
+      </c>
+      <c r="I15">
+        <v>-6.6186049999999996</v>
+      </c>
+      <c r="J15" s="2">
+        <v>14080</v>
+      </c>
+      <c r="K15">
+        <v>888439793</v>
+      </c>
+      <c r="L15" t="s">
+        <v>78</v>
+      </c>
+      <c r="M15">
+        <v>5</v>
+      </c>
+      <c r="N15" t="s">
+        <v>45</v>
+      </c>
+      <c r="O15" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>47</v>
+      </c>
+      <c r="R15" t="s">
+        <v>35</v>
+      </c>
+      <c r="S15" t="s">
+        <v>36</v>
+      </c>
+      <c r="T15" t="s">
+        <v>51</v>
+      </c>
+      <c r="U15" t="s">
+        <v>38</v>
+      </c>
+      <c r="V15" t="s">
+        <v>79</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1">
+        <v>10007</v>
+      </c>
+      <c r="C16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16">
+        <v>34.192861000000001</v>
+      </c>
+      <c r="I16">
+        <v>-6.683662</v>
+      </c>
+      <c r="J16" s="2">
+        <v>14025</v>
+      </c>
+      <c r="K16">
+        <v>811552880</v>
+      </c>
+      <c r="L16" t="s">
+        <v>84</v>
+      </c>
+      <c r="M16">
+        <v>2</v>
+      </c>
+      <c r="N16" t="s">
+        <v>45</v>
+      </c>
+      <c r="O16" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>47</v>
+      </c>
+      <c r="R16" t="s">
+        <v>35</v>
+      </c>
+      <c r="S16" t="s">
+        <v>36</v>
+      </c>
+      <c r="T16" t="s">
+        <v>37</v>
+      </c>
+      <c r="U16" t="s">
+        <v>38</v>
+      </c>
+      <c r="V16" t="s">
+        <v>85</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="1">
+        <v>10007</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17">
+        <v>34.192861000000001</v>
+      </c>
+      <c r="I17">
+        <v>-6.683662</v>
+      </c>
+      <c r="J17" s="2">
+        <v>14025</v>
+      </c>
+      <c r="K17">
+        <v>753640112</v>
+      </c>
+      <c r="L17" t="s">
+        <v>84</v>
+      </c>
+      <c r="M17">
+        <v>2</v>
+      </c>
+      <c r="N17" t="s">
+        <v>45</v>
+      </c>
+      <c r="O17" t="s">
+        <v>32</v>
+      </c>
+      <c r="P17" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>47</v>
+      </c>
+      <c r="R17" t="s">
+        <v>35</v>
+      </c>
+      <c r="S17" t="s">
+        <v>36</v>
+      </c>
+      <c r="T17" t="s">
+        <v>51</v>
+      </c>
+      <c r="U17" t="s">
+        <v>38</v>
+      </c>
+      <c r="V17" t="s">
+        <v>85</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="1">
+        <v>10008</v>
+      </c>
+      <c r="C18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+      <c r="F18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18">
+        <v>34.522413999999998</v>
+      </c>
+      <c r="I18">
+        <v>-6.3204710000000004</v>
+      </c>
+      <c r="J18" s="2">
+        <v>14050</v>
+      </c>
+      <c r="K18">
+        <v>695325692</v>
+      </c>
+      <c r="L18" t="s">
+        <v>91</v>
+      </c>
+      <c r="M18">
+        <v>2</v>
+      </c>
+      <c r="N18" t="s">
+        <v>45</v>
+      </c>
+      <c r="O18" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>47</v>
+      </c>
+      <c r="R18" t="s">
+        <v>35</v>
+      </c>
+      <c r="S18" t="s">
+        <v>36</v>
+      </c>
+      <c r="T18" t="s">
+        <v>37</v>
+      </c>
+      <c r="U18" t="s">
+        <v>38</v>
+      </c>
+      <c r="V18" t="s">
+        <v>92</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="1">
+        <v>10008</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19">
+        <v>34.522413999999998</v>
+      </c>
+      <c r="I19">
+        <v>-6.3204710000000004</v>
+      </c>
+      <c r="J19" s="2">
+        <v>14050</v>
+      </c>
+      <c r="K19">
+        <v>862899075</v>
+      </c>
+      <c r="L19" t="s">
+        <v>91</v>
+      </c>
+      <c r="M19">
+        <v>2</v>
+      </c>
+      <c r="N19" t="s">
+        <v>45</v>
+      </c>
+      <c r="O19" t="s">
+        <v>32</v>
+      </c>
+      <c r="P19" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>47</v>
+      </c>
+      <c r="R19" t="s">
+        <v>35</v>
+      </c>
+      <c r="S19" t="s">
+        <v>36</v>
+      </c>
+      <c r="T19" t="s">
+        <v>51</v>
+      </c>
+      <c r="U19" t="s">
+        <v>38</v>
+      </c>
+      <c r="V19" t="s">
+        <v>92</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="1">
+        <v>10009</v>
+      </c>
+      <c r="C20" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20">
+        <v>33.998232000000002</v>
+      </c>
+      <c r="I20">
+        <v>-6.8457280000000003</v>
+      </c>
+      <c r="J20" s="2">
+        <v>10106</v>
+      </c>
+      <c r="K20">
+        <v>745360421</v>
+      </c>
+      <c r="L20" t="s">
+        <v>98</v>
+      </c>
+      <c r="M20">
+        <v>2</v>
+      </c>
+      <c r="N20" t="s">
+        <v>45</v>
+      </c>
+      <c r="O20" t="s">
+        <v>32</v>
+      </c>
+      <c r="P20" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>47</v>
+      </c>
+      <c r="R20" t="s">
+        <v>35</v>
+      </c>
+      <c r="S20" t="s">
+        <v>36</v>
+      </c>
+      <c r="T20" t="s">
+        <v>37</v>
+      </c>
+      <c r="U20" t="s">
+        <v>48</v>
+      </c>
+      <c r="V20" t="s">
+        <v>99</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="1">
+        <v>10009</v>
+      </c>
+      <c r="C21" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21">
+        <v>33.998232000000002</v>
+      </c>
+      <c r="I21">
+        <v>-6.8457280000000003</v>
+      </c>
+      <c r="J21" s="2">
+        <v>10106</v>
+      </c>
+      <c r="K21">
+        <v>676186831</v>
+      </c>
+      <c r="L21" t="s">
+        <v>98</v>
+      </c>
+      <c r="M21">
+        <v>2</v>
+      </c>
+      <c r="N21" t="s">
+        <v>45</v>
+      </c>
+      <c r="O21" t="s">
+        <v>32</v>
+      </c>
+      <c r="P21" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>47</v>
+      </c>
+      <c r="R21" t="s">
+        <v>35</v>
+      </c>
+      <c r="S21" t="s">
+        <v>36</v>
+      </c>
+      <c r="T21" t="s">
+        <v>51</v>
+      </c>
+      <c r="U21" t="s">
+        <v>48</v>
+      </c>
+      <c r="V21" t="s">
+        <v>99</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="1">
+        <v>10010</v>
+      </c>
+      <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22">
+        <v>34.017502</v>
+      </c>
+      <c r="I22">
+        <v>-6.8347449999999998</v>
+      </c>
+      <c r="J22" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K22">
+        <v>766074745</v>
+      </c>
+      <c r="L22" t="s">
+        <v>104</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22" t="s">
+        <v>45</v>
+      </c>
+      <c r="O22" t="s">
+        <v>32</v>
+      </c>
+      <c r="P22" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>47</v>
+      </c>
+      <c r="R22" t="s">
+        <v>35</v>
+      </c>
+      <c r="S22" t="s">
+        <v>36</v>
+      </c>
+      <c r="T22" t="s">
+        <v>37</v>
+      </c>
+      <c r="U22" t="s">
+        <v>48</v>
+      </c>
+      <c r="V22" t="s">
+        <v>105</v>
+      </c>
+      <c r="W22" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="1">
+        <v>10010</v>
+      </c>
+      <c r="C23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" t="s">
+        <v>50</v>
+      </c>
+      <c r="H23">
+        <v>34.017502</v>
+      </c>
+      <c r="I23">
+        <v>-6.8347449999999998</v>
+      </c>
+      <c r="J23" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K23">
+        <v>773606891</v>
+      </c>
+      <c r="L23" t="s">
+        <v>104</v>
+      </c>
+      <c r="M23">
+        <v>2</v>
+      </c>
+      <c r="N23" t="s">
+        <v>45</v>
+      </c>
+      <c r="O23" t="s">
+        <v>32</v>
+      </c>
+      <c r="P23" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>47</v>
+      </c>
+      <c r="R23" t="s">
+        <v>35</v>
+      </c>
+      <c r="S23" t="s">
+        <v>36</v>
+      </c>
+      <c r="T23" t="s">
+        <v>51</v>
+      </c>
+      <c r="U23" t="s">
+        <v>48</v>
+      </c>
+      <c r="V23" t="s">
+        <v>105</v>
+      </c>
+      <c r="W23" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>10011</v>
+      </c>
+      <c r="C24" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24">
+        <v>33.986607999999997</v>
+      </c>
+      <c r="I24">
+        <v>-6.8288729999999997</v>
+      </c>
+      <c r="J24" s="2">
+        <v>10105</v>
+      </c>
+      <c r="K24">
+        <v>787248921</v>
+      </c>
+      <c r="L24" t="s">
+        <v>110</v>
+      </c>
+      <c r="M24">
+        <v>2</v>
+      </c>
+      <c r="N24" t="s">
+        <v>45</v>
+      </c>
+      <c r="O24" t="s">
+        <v>32</v>
+      </c>
+      <c r="P24" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>47</v>
+      </c>
+      <c r="R24" t="s">
+        <v>35</v>
+      </c>
+      <c r="S24" t="s">
+        <v>36</v>
+      </c>
+      <c r="T24" t="s">
+        <v>37</v>
+      </c>
+      <c r="U24" t="s">
+        <v>48</v>
+      </c>
+      <c r="V24" t="s">
+        <v>111</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="1">
+        <v>10011</v>
+      </c>
+      <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" t="s">
+        <v>97</v>
+      </c>
+      <c r="G25" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25">
+        <v>33.986607999999997</v>
+      </c>
+      <c r="I25">
+        <v>-6.8288729999999997</v>
+      </c>
+      <c r="J25" s="2">
+        <v>10105</v>
+      </c>
+      <c r="K25">
+        <v>878691008</v>
+      </c>
+      <c r="L25" t="s">
+        <v>110</v>
+      </c>
+      <c r="M25">
+        <v>2</v>
+      </c>
+      <c r="N25" t="s">
+        <v>45</v>
+      </c>
+      <c r="O25" t="s">
+        <v>32</v>
+      </c>
+      <c r="P25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>47</v>
+      </c>
+      <c r="R25" t="s">
+        <v>35</v>
+      </c>
+      <c r="S25" t="s">
+        <v>36</v>
+      </c>
+      <c r="T25" t="s">
+        <v>51</v>
+      </c>
+      <c r="U25" t="s">
+        <v>48</v>
+      </c>
+      <c r="V25" t="s">
+        <v>111</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>10012</v>
+      </c>
+      <c r="C26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" t="s">
+        <v>97</v>
+      </c>
+      <c r="G26" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26">
+        <v>33.978102999999997</v>
+      </c>
+      <c r="I26">
+        <v>-6.8678489999999996</v>
+      </c>
+      <c r="J26" s="2">
+        <v>10112</v>
+      </c>
+      <c r="K26">
+        <v>838412388</v>
+      </c>
+      <c r="L26" t="s">
+        <v>116</v>
+      </c>
+      <c r="M26">
+        <v>2</v>
+      </c>
+      <c r="N26" t="s">
+        <v>45</v>
+      </c>
+      <c r="O26" t="s">
+        <v>32</v>
+      </c>
+      <c r="P26" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>47</v>
+      </c>
+      <c r="R26" t="s">
+        <v>35</v>
+      </c>
+      <c r="S26" t="s">
+        <v>36</v>
+      </c>
+      <c r="T26" t="s">
+        <v>37</v>
+      </c>
+      <c r="U26" t="s">
+        <v>48</v>
+      </c>
+      <c r="V26" t="s">
+        <v>92</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="1">
+        <v>10012</v>
+      </c>
+      <c r="C27" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" t="s">
+        <v>50</v>
+      </c>
+      <c r="H27">
+        <v>33.978102999999997</v>
+      </c>
+      <c r="I27">
+        <v>-6.8678489999999996</v>
+      </c>
+      <c r="J27" s="2">
+        <v>10112</v>
+      </c>
+      <c r="K27">
+        <v>719952201</v>
+      </c>
+      <c r="L27" t="s">
+        <v>116</v>
+      </c>
+      <c r="M27">
+        <v>2</v>
+      </c>
+      <c r="N27" t="s">
+        <v>45</v>
+      </c>
+      <c r="O27" t="s">
+        <v>32</v>
+      </c>
+      <c r="P27" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>47</v>
+      </c>
+      <c r="R27" t="s">
+        <v>35</v>
+      </c>
+      <c r="S27" t="s">
+        <v>36</v>
+      </c>
+      <c r="T27" t="s">
+        <v>51</v>
+      </c>
+      <c r="U27" t="s">
+        <v>48</v>
+      </c>
+      <c r="V27" t="s">
+        <v>92</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="1">
+        <v>10013</v>
+      </c>
+      <c r="C28" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
+        <v>120</v>
+      </c>
+      <c r="F28" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" t="s">
+        <v>29</v>
+      </c>
+      <c r="H28">
+        <v>33.953930999999997</v>
+      </c>
+      <c r="I28">
+        <v>-6.8747350000000003</v>
+      </c>
+      <c r="J28" s="2">
+        <v>10104</v>
+      </c>
+      <c r="K28">
+        <v>751913644</v>
+      </c>
+      <c r="L28" t="s">
+        <v>121</v>
+      </c>
+      <c r="M28">
+        <v>2</v>
+      </c>
+      <c r="N28" t="s">
+        <v>45</v>
+      </c>
+      <c r="O28" t="s">
+        <v>32</v>
+      </c>
+      <c r="P28" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>47</v>
+      </c>
+      <c r="R28" t="s">
+        <v>35</v>
+      </c>
+      <c r="S28" t="s">
+        <v>36</v>
+      </c>
+      <c r="T28" t="s">
+        <v>37</v>
+      </c>
+      <c r="U28" t="s">
+        <v>48</v>
+      </c>
+      <c r="V28" t="s">
+        <v>99</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="1">
+        <v>10013</v>
+      </c>
+      <c r="C29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D29" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" t="s">
+        <v>123</v>
+      </c>
+      <c r="F29" t="s">
+        <v>97</v>
+      </c>
+      <c r="G29" t="s">
+        <v>50</v>
+      </c>
+      <c r="H29">
+        <v>33.953930999999997</v>
+      </c>
+      <c r="I29">
+        <v>-6.8747350000000003</v>
+      </c>
+      <c r="J29" s="2">
+        <v>10104</v>
+      </c>
+      <c r="K29">
+        <v>956537434</v>
+      </c>
+      <c r="L29" t="s">
+        <v>121</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+      <c r="N29" t="s">
+        <v>45</v>
+      </c>
+      <c r="O29" t="s">
+        <v>32</v>
+      </c>
+      <c r="P29" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>47</v>
+      </c>
+      <c r="R29" t="s">
+        <v>35</v>
+      </c>
+      <c r="S29" t="s">
+        <v>36</v>
+      </c>
+      <c r="T29" t="s">
+        <v>51</v>
+      </c>
+      <c r="U29" t="s">
+        <v>48</v>
+      </c>
+      <c r="V29" t="s">
+        <v>99</v>
+      </c>
+      <c r="W29" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="1">
+        <v>10014</v>
+      </c>
+      <c r="C30" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
+        <v>125</v>
+      </c>
+      <c r="F30" t="s">
+        <v>97</v>
+      </c>
+      <c r="G30" t="s">
+        <v>29</v>
+      </c>
+      <c r="H30">
+        <v>34.027757000000001</v>
+      </c>
+      <c r="I30">
+        <v>-6.8341469999999997</v>
+      </c>
+      <c r="J30" s="2">
+        <v>10036</v>
+      </c>
+      <c r="K30">
+        <v>965639376</v>
+      </c>
+      <c r="L30" t="s">
+        <v>126</v>
+      </c>
+      <c r="M30">
+        <v>2</v>
+      </c>
+      <c r="N30" t="s">
+        <v>45</v>
+      </c>
+      <c r="O30" t="s">
+        <v>32</v>
+      </c>
+      <c r="P30" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>47</v>
+      </c>
+      <c r="R30" t="s">
+        <v>35</v>
+      </c>
+      <c r="S30" t="s">
+        <v>36</v>
+      </c>
+      <c r="T30" t="s">
+        <v>37</v>
+      </c>
+      <c r="U30" t="s">
+        <v>48</v>
+      </c>
+      <c r="V30" t="s">
+        <v>105</v>
+      </c>
+      <c r="W30" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="1">
+        <v>10014</v>
+      </c>
+      <c r="C31" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" t="s">
+        <v>97</v>
+      </c>
+      <c r="G31" t="s">
+        <v>50</v>
+      </c>
+      <c r="H31">
+        <v>34.027757000000001</v>
+      </c>
+      <c r="I31">
+        <v>-6.8341469999999997</v>
+      </c>
+      <c r="J31" s="2">
+        <v>10036</v>
+      </c>
+      <c r="K31">
+        <v>781039430</v>
+      </c>
+      <c r="L31" t="s">
+        <v>126</v>
+      </c>
+      <c r="M31">
+        <v>2</v>
+      </c>
+      <c r="N31" t="s">
+        <v>45</v>
+      </c>
+      <c r="O31" t="s">
+        <v>32</v>
+      </c>
+      <c r="P31" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>47</v>
+      </c>
+      <c r="R31" t="s">
+        <v>35</v>
+      </c>
+      <c r="S31" t="s">
+        <v>36</v>
+      </c>
+      <c r="T31" t="s">
+        <v>51</v>
+      </c>
+      <c r="U31" t="s">
+        <v>48</v>
+      </c>
+      <c r="V31" t="s">
+        <v>105</v>
+      </c>
+      <c r="W31" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="1">
+        <v>10015</v>
+      </c>
+      <c r="C32" t="s">
+        <v>129</v>
+      </c>
+      <c r="D32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" t="s">
+        <v>130</v>
+      </c>
+      <c r="F32" t="s">
+        <v>97</v>
+      </c>
+      <c r="G32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32">
+        <v>33.995612000000001</v>
+      </c>
+      <c r="I32">
+        <v>-6.8152809999999997</v>
+      </c>
+      <c r="J32" s="2">
+        <v>10190</v>
+      </c>
+      <c r="K32">
+        <v>803062069</v>
+      </c>
+      <c r="L32" t="s">
+        <v>131</v>
+      </c>
+      <c r="M32">
+        <v>2</v>
+      </c>
+      <c r="N32" t="s">
+        <v>45</v>
+      </c>
+      <c r="O32" t="s">
+        <v>32</v>
+      </c>
+      <c r="P32" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>47</v>
+      </c>
+      <c r="R32" t="s">
+        <v>35</v>
+      </c>
+      <c r="S32" t="s">
+        <v>36</v>
+      </c>
+      <c r="T32" t="s">
+        <v>37</v>
+      </c>
+      <c r="U32" t="s">
+        <v>48</v>
+      </c>
+      <c r="V32" t="s">
+        <v>111</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1">
+        <v>10015</v>
+      </c>
+      <c r="C33" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F33" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" t="s">
+        <v>50</v>
+      </c>
+      <c r="H33">
+        <v>33.995612000000001</v>
+      </c>
+      <c r="I33">
+        <v>-6.8152809999999997</v>
+      </c>
+      <c r="J33" s="2">
+        <v>10190</v>
+      </c>
+      <c r="K33">
+        <v>731435978</v>
+      </c>
+      <c r="L33" t="s">
+        <v>131</v>
+      </c>
+      <c r="M33">
+        <v>2</v>
+      </c>
+      <c r="N33" t="s">
+        <v>45</v>
+      </c>
+      <c r="O33" t="s">
+        <v>32</v>
+      </c>
+      <c r="P33" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>47</v>
+      </c>
+      <c r="R33" t="s">
+        <v>35</v>
+      </c>
+      <c r="S33" t="s">
+        <v>36</v>
+      </c>
+      <c r="T33" t="s">
+        <v>51</v>
+      </c>
+      <c r="U33" t="s">
+        <v>48</v>
+      </c>
+      <c r="V33" t="s">
+        <v>111</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" t="s">
+        <v>135</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" t="s">
+        <v>137</v>
+      </c>
+      <c r="G34" t="s">
+        <v>138</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>31</v>
+      </c>
+      <c r="O34" t="s">
+        <v>32</v>
+      </c>
+      <c r="P34" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>34</v>
+      </c>
+      <c r="R34" t="s">
+        <v>35</v>
+      </c>
+      <c r="S34" t="s">
+        <v>36</v>
+      </c>
+      <c r="T34" t="s">
+        <v>37</v>
+      </c>
+      <c r="U34" t="s">
+        <v>38</v>
+      </c>
+      <c r="V34" t="s">
+        <v>30</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" s="1">
+        <v>10001</v>
+      </c>
+      <c r="C35" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" t="s">
+        <v>140</v>
+      </c>
+      <c r="G35" t="s">
+        <v>138</v>
+      </c>
+      <c r="H35">
+        <v>34.521169999999998</v>
+      </c>
+      <c r="I35">
+        <v>-6.4532749999999997</v>
+      </c>
+      <c r="J35" s="2">
+        <v>14022</v>
+      </c>
+      <c r="K35">
+        <v>779517433</v>
+      </c>
+      <c r="L35" t="s">
+        <v>141</v>
+      </c>
+      <c r="M35">
+        <v>3</v>
+      </c>
+      <c r="N35" t="s">
+        <v>45</v>
+      </c>
+      <c r="O35" t="s">
+        <v>32</v>
+      </c>
+      <c r="P35" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>47</v>
+      </c>
+      <c r="R35" t="s">
+        <v>35</v>
+      </c>
+      <c r="S35" t="s">
+        <v>36</v>
+      </c>
+      <c r="T35" t="s">
+        <v>37</v>
+      </c>
+      <c r="U35" t="s">
+        <v>38</v>
+      </c>
+      <c r="V35" t="s">
+        <v>48</v>
+      </c>
+      <c r="W35" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>134</v>
+      </c>
+      <c r="B36" s="1">
+        <v>10002</v>
+      </c>
+      <c r="C36" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" t="s">
+        <v>143</v>
+      </c>
+      <c r="F36" t="s">
+        <v>144</v>
+      </c>
+      <c r="G36" t="s">
+        <v>138</v>
+      </c>
+      <c r="H36">
+        <v>34.360207000000003</v>
+      </c>
+      <c r="I36">
+        <v>-6.5500749999999996</v>
+      </c>
+      <c r="J36" s="2">
+        <v>14053</v>
+      </c>
+      <c r="K36">
+        <v>753476995</v>
+      </c>
+      <c r="L36" t="s">
+        <v>145</v>
+      </c>
+      <c r="M36">
+        <v>2</v>
+      </c>
+      <c r="N36" t="s">
+        <v>45</v>
+      </c>
+      <c r="O36" t="s">
+        <v>32</v>
+      </c>
+      <c r="P36" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>47</v>
+      </c>
+      <c r="R36" t="s">
+        <v>35</v>
+      </c>
+      <c r="S36" t="s">
+        <v>36</v>
+      </c>
+      <c r="T36" t="s">
+        <v>37</v>
+      </c>
+      <c r="U36" t="s">
+        <v>38</v>
+      </c>
+      <c r="V36" t="s">
+        <v>38</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" s="1">
+        <v>10003</v>
+      </c>
+      <c r="C37" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" t="s">
+        <v>147</v>
+      </c>
+      <c r="F37" t="s">
+        <v>148</v>
+      </c>
+      <c r="G37" t="s">
+        <v>138</v>
+      </c>
+      <c r="H37">
+        <v>34.405692000000002</v>
+      </c>
+      <c r="I37">
+        <v>-6.4333679999999998</v>
+      </c>
+      <c r="J37" s="2">
+        <v>14023</v>
+      </c>
+      <c r="K37">
+        <v>734239083</v>
+      </c>
+      <c r="L37" t="s">
+        <v>149</v>
+      </c>
+      <c r="M37">
+        <v>4</v>
+      </c>
+      <c r="N37" t="s">
+        <v>45</v>
+      </c>
+      <c r="O37" t="s">
+        <v>32</v>
+      </c>
+      <c r="P37" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>47</v>
+      </c>
+      <c r="R37" t="s">
+        <v>35</v>
+      </c>
+      <c r="S37" t="s">
+        <v>36</v>
+      </c>
+      <c r="T37" t="s">
+        <v>37</v>
+      </c>
+      <c r="U37" t="s">
+        <v>38</v>
+      </c>
+      <c r="V37" t="s">
+        <v>61</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" s="1">
+        <v>10004</v>
+      </c>
+      <c r="C38" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" t="s">
+        <v>151</v>
+      </c>
+      <c r="F38" t="s">
+        <v>152</v>
+      </c>
+      <c r="G38" t="s">
+        <v>138</v>
+      </c>
+      <c r="H38">
+        <v>34.287878999999997</v>
+      </c>
+      <c r="I38">
+        <v>-6.5164280000000003</v>
+      </c>
+      <c r="J38" s="2">
+        <v>14000</v>
+      </c>
+      <c r="K38">
+        <v>937997757</v>
+      </c>
+      <c r="L38" t="s">
+        <v>153</v>
+      </c>
+      <c r="M38">
+        <v>2</v>
+      </c>
+      <c r="N38" t="s">
+        <v>45</v>
+      </c>
+      <c r="O38" t="s">
+        <v>32</v>
+      </c>
+      <c r="P38" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>47</v>
+      </c>
+      <c r="R38" t="s">
+        <v>35</v>
+      </c>
+      <c r="S38" t="s">
+        <v>36</v>
+      </c>
+      <c r="T38" t="s">
+        <v>37</v>
+      </c>
+      <c r="U38" t="s">
+        <v>38</v>
+      </c>
+      <c r="V38" t="s">
+        <v>48</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" s="1">
+        <v>10005</v>
+      </c>
+      <c r="C39" t="s">
+        <v>154</v>
+      </c>
+      <c r="D39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F39" t="s">
+        <v>152</v>
+      </c>
+      <c r="G39" t="s">
+        <v>156</v>
+      </c>
+      <c r="H39">
+        <v>34.256413999999999</v>
+      </c>
+      <c r="I39">
+        <v>-6.6754990000000003</v>
+      </c>
+      <c r="J39" s="2">
+        <v>14110</v>
+      </c>
+      <c r="K39">
+        <v>887311749</v>
+      </c>
+      <c r="L39" t="s">
+        <v>157</v>
+      </c>
+      <c r="M39">
+        <v>1</v>
+      </c>
+      <c r="N39" t="s">
+        <v>45</v>
+      </c>
+      <c r="O39" t="s">
+        <v>32</v>
+      </c>
+      <c r="P39" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>47</v>
+      </c>
+      <c r="R39" t="s">
+        <v>35</v>
+      </c>
+      <c r="S39" t="s">
+        <v>36</v>
+      </c>
+      <c r="T39" t="s">
+        <v>37</v>
+      </c>
+      <c r="U39" t="s">
+        <v>38</v>
+      </c>
+      <c r="V39" t="s">
+        <v>73</v>
+      </c>
+      <c r="W39" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>134</v>
+      </c>
+      <c r="B40" s="1">
+        <v>10006</v>
+      </c>
+      <c r="C40" t="s">
+        <v>158</v>
+      </c>
+      <c r="D40" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" t="s">
+        <v>159</v>
+      </c>
+      <c r="F40" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40" t="s">
+        <v>156</v>
+      </c>
+      <c r="H40">
+        <v>34.262476999999997</v>
+      </c>
+      <c r="I40">
+        <v>-6.6186049999999996</v>
+      </c>
+      <c r="J40" s="2">
+        <v>14080</v>
+      </c>
+      <c r="K40">
+        <v>915790305</v>
+      </c>
+      <c r="L40" t="s">
+        <v>160</v>
+      </c>
+      <c r="M40">
+        <v>5</v>
+      </c>
+      <c r="N40" t="s">
+        <v>45</v>
+      </c>
+      <c r="O40" t="s">
+        <v>32</v>
+      </c>
+      <c r="P40" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>47</v>
+      </c>
+      <c r="R40" t="s">
+        <v>35</v>
+      </c>
+      <c r="S40" t="s">
+        <v>36</v>
+      </c>
+      <c r="T40" t="s">
+        <v>37</v>
+      </c>
+      <c r="U40" t="s">
+        <v>38</v>
+      </c>
+      <c r="V40" t="s">
+        <v>79</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="1">
+        <v>10007</v>
+      </c>
+      <c r="C41" t="s">
+        <v>161</v>
+      </c>
+      <c r="D41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" t="s">
+        <v>162</v>
+      </c>
+      <c r="F41" t="s">
+        <v>163</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H41">
+        <v>34.192861000000001</v>
+      </c>
+      <c r="I41">
+        <v>-6.683662</v>
+      </c>
+      <c r="J41" s="2">
+        <v>14025</v>
+      </c>
+      <c r="K41">
+        <v>811552880</v>
+      </c>
+      <c r="L41" t="s">
+        <v>164</v>
+      </c>
+      <c r="M41">
+        <v>2</v>
+      </c>
+      <c r="N41" t="s">
+        <v>45</v>
+      </c>
+      <c r="O41" t="s">
+        <v>32</v>
+      </c>
+      <c r="P41" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>47</v>
+      </c>
+      <c r="R41" t="s">
+        <v>35</v>
+      </c>
+      <c r="S41" t="s">
+        <v>36</v>
+      </c>
+      <c r="T41" t="s">
+        <v>37</v>
+      </c>
+      <c r="U41" t="s">
+        <v>38</v>
+      </c>
+      <c r="V41" t="s">
+        <v>85</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>134</v>
+      </c>
+      <c r="B42" s="1">
+        <v>10008</v>
+      </c>
+      <c r="C42" t="s">
+        <v>165</v>
+      </c>
+      <c r="D42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" t="s">
+        <v>166</v>
+      </c>
+      <c r="F42" t="s">
+        <v>167</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H42">
+        <v>34.522413999999998</v>
+      </c>
+      <c r="I42">
+        <v>-6.3204710000000004</v>
+      </c>
+      <c r="J42" s="2">
+        <v>14050</v>
+      </c>
+      <c r="K42">
+        <v>695325692</v>
+      </c>
+      <c r="L42" t="s">
+        <v>168</v>
+      </c>
+      <c r="M42">
+        <v>2</v>
+      </c>
+      <c r="N42" t="s">
+        <v>45</v>
+      </c>
+      <c r="O42" t="s">
+        <v>32</v>
+      </c>
+      <c r="P42" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>47</v>
+      </c>
+      <c r="R42" t="s">
+        <v>35</v>
+      </c>
+      <c r="S42" t="s">
+        <v>36</v>
+      </c>
+      <c r="T42" t="s">
+        <v>37</v>
+      </c>
+      <c r="U42" t="s">
+        <v>38</v>
+      </c>
+      <c r="V42" t="s">
+        <v>92</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" s="1">
+        <v>10009</v>
+      </c>
+      <c r="C43" t="s">
+        <v>169</v>
+      </c>
+      <c r="D43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" t="s">
+        <v>170</v>
+      </c>
+      <c r="F43" t="s">
+        <v>171</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H43">
+        <v>33.998232000000002</v>
+      </c>
+      <c r="I43">
+        <v>-6.8457280000000003</v>
+      </c>
+      <c r="J43" s="2">
+        <v>10106</v>
+      </c>
+      <c r="K43">
+        <v>745360421</v>
+      </c>
+      <c r="L43" t="s">
+        <v>172</v>
+      </c>
+      <c r="M43">
+        <v>2</v>
+      </c>
+      <c r="N43" t="s">
+        <v>45</v>
+      </c>
+      <c r="O43" t="s">
+        <v>32</v>
+      </c>
+      <c r="P43" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>47</v>
+      </c>
+      <c r="R43" t="s">
+        <v>35</v>
+      </c>
+      <c r="S43" t="s">
+        <v>36</v>
+      </c>
+      <c r="T43" t="s">
+        <v>37</v>
+      </c>
+      <c r="U43" t="s">
+        <v>48</v>
+      </c>
+      <c r="V43" t="s">
+        <v>99</v>
+      </c>
+      <c r="W43" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" s="1">
+        <v>10010</v>
+      </c>
+      <c r="C44" t="s">
+        <v>173</v>
+      </c>
+      <c r="D44" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" t="s">
+        <v>174</v>
+      </c>
+      <c r="F44" t="s">
+        <v>171</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H44">
+        <v>34.017502</v>
+      </c>
+      <c r="I44">
+        <v>-6.8347449999999998</v>
+      </c>
+      <c r="J44" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K44">
+        <v>766074745</v>
+      </c>
+      <c r="L44" t="s">
+        <v>175</v>
+      </c>
+      <c r="M44">
+        <v>2</v>
+      </c>
+      <c r="N44" t="s">
+        <v>45</v>
+      </c>
+      <c r="O44" t="s">
+        <v>32</v>
+      </c>
+      <c r="P44" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>47</v>
+      </c>
+      <c r="R44" t="s">
+        <v>35</v>
+      </c>
+      <c r="S44" t="s">
+        <v>36</v>
+      </c>
+      <c r="T44" t="s">
+        <v>37</v>
+      </c>
+      <c r="U44" t="s">
+        <v>48</v>
+      </c>
+      <c r="V44" t="s">
+        <v>105</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>134</v>
+      </c>
+      <c r="B45" s="1">
+        <v>10011</v>
+      </c>
+      <c r="C45" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" t="s">
+        <v>177</v>
+      </c>
+      <c r="F45" t="s">
+        <v>171</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H45">
+        <v>33.986607999999997</v>
+      </c>
+      <c r="I45">
+        <v>-6.8288729999999997</v>
+      </c>
+      <c r="J45" s="2">
+        <v>10105</v>
+      </c>
+      <c r="K45">
+        <v>787248921</v>
+      </c>
+      <c r="L45" t="s">
+        <v>178</v>
+      </c>
+      <c r="M45">
+        <v>2</v>
+      </c>
+      <c r="N45" t="s">
+        <v>45</v>
+      </c>
+      <c r="O45" t="s">
+        <v>32</v>
+      </c>
+      <c r="P45" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>47</v>
+      </c>
+      <c r="R45" t="s">
+        <v>35</v>
+      </c>
+      <c r="S45" t="s">
+        <v>36</v>
+      </c>
+      <c r="T45" t="s">
+        <v>37</v>
+      </c>
+      <c r="U45" t="s">
+        <v>48</v>
+      </c>
+      <c r="V45" t="s">
+        <v>111</v>
+      </c>
+      <c r="W45" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" s="1">
+        <v>10012</v>
+      </c>
+      <c r="C46" t="s">
+        <v>179</v>
+      </c>
+      <c r="D46" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" t="s">
+        <v>180</v>
+      </c>
+      <c r="F46" t="s">
+        <v>171</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H46">
+        <v>33.978102999999997</v>
+      </c>
+      <c r="I46">
+        <v>-6.8678489999999996</v>
+      </c>
+      <c r="J46" s="2">
+        <v>10112</v>
+      </c>
+      <c r="K46">
+        <v>838412388</v>
+      </c>
+      <c r="L46" t="s">
+        <v>181</v>
+      </c>
+      <c r="M46">
+        <v>2</v>
+      </c>
+      <c r="N46" t="s">
+        <v>45</v>
+      </c>
+      <c r="O46" t="s">
+        <v>32</v>
+      </c>
+      <c r="P46" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>47</v>
+      </c>
+      <c r="R46" t="s">
+        <v>35</v>
+      </c>
+      <c r="S46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T46" t="s">
+        <v>37</v>
+      </c>
+      <c r="U46" t="s">
+        <v>48</v>
+      </c>
+      <c r="V46" t="s">
+        <v>92</v>
+      </c>
+      <c r="W46" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>134</v>
+      </c>
+      <c r="B47" s="1">
+        <v>10013</v>
+      </c>
+      <c r="C47" t="s">
+        <v>182</v>
+      </c>
+      <c r="D47" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" t="s">
+        <v>183</v>
+      </c>
+      <c r="F47" t="s">
+        <v>171</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H47">
+        <v>33.953930999999997</v>
+      </c>
+      <c r="I47">
+        <v>-6.8747350000000003</v>
+      </c>
+      <c r="J47" s="2">
+        <v>10104</v>
+      </c>
+      <c r="K47">
+        <v>751913644</v>
+      </c>
+      <c r="L47" t="s">
+        <v>184</v>
+      </c>
+      <c r="M47">
+        <v>2</v>
+      </c>
+      <c r="N47" t="s">
+        <v>45</v>
+      </c>
+      <c r="O47" t="s">
+        <v>32</v>
+      </c>
+      <c r="P47" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>47</v>
+      </c>
+      <c r="R47" t="s">
+        <v>35</v>
+      </c>
+      <c r="S47" t="s">
+        <v>36</v>
+      </c>
+      <c r="T47" t="s">
+        <v>37</v>
+      </c>
+      <c r="U47" t="s">
+        <v>48</v>
+      </c>
+      <c r="V47" t="s">
+        <v>99</v>
+      </c>
+      <c r="W47" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>134</v>
+      </c>
+      <c r="B48" s="1">
+        <v>10014</v>
+      </c>
+      <c r="C48" t="s">
+        <v>185</v>
+      </c>
+      <c r="D48" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" t="s">
+        <v>186</v>
+      </c>
+      <c r="F48" t="s">
+        <v>171</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H48">
+        <v>34.027757000000001</v>
+      </c>
+      <c r="I48">
+        <v>-6.8341469999999997</v>
+      </c>
+      <c r="J48" s="2">
+        <v>10036</v>
+      </c>
+      <c r="K48">
+        <v>965639376</v>
+      </c>
+      <c r="L48" t="s">
+        <v>187</v>
+      </c>
+      <c r="M48">
+        <v>2</v>
+      </c>
+      <c r="N48" t="s">
+        <v>45</v>
+      </c>
+      <c r="O48" t="s">
+        <v>32</v>
+      </c>
+      <c r="P48" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>47</v>
+      </c>
+      <c r="R48" t="s">
+        <v>35</v>
+      </c>
+      <c r="S48" t="s">
+        <v>36</v>
+      </c>
+      <c r="T48" t="s">
+        <v>37</v>
+      </c>
+      <c r="U48" t="s">
+        <v>48</v>
+      </c>
+      <c r="V48" t="s">
+        <v>105</v>
+      </c>
+      <c r="W48" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B49" s="1">
+        <v>10015</v>
+      </c>
+      <c r="C49" t="s">
+        <v>188</v>
+      </c>
+      <c r="D49" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" t="s">
+        <v>189</v>
+      </c>
+      <c r="F49" t="s">
+        <v>171</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="H49">
+        <v>33.995612000000001</v>
+      </c>
+      <c r="I49">
+        <v>-6.8152809999999997</v>
+      </c>
+      <c r="J49" s="2">
+        <v>10190</v>
+      </c>
+      <c r="K49">
+        <v>803062069</v>
+      </c>
+      <c r="L49" t="s">
+        <v>190</v>
+      </c>
+      <c r="M49">
+        <v>2</v>
+      </c>
+      <c r="N49" t="s">
+        <v>45</v>
+      </c>
+      <c r="O49" t="s">
+        <v>32</v>
+      </c>
+      <c r="P49" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>47</v>
+      </c>
+      <c r="R49" t="s">
+        <v>35</v>
+      </c>
+      <c r="S49" t="s">
+        <v>36</v>
+      </c>
+      <c r="T49" t="s">
+        <v>37</v>
+      </c>
+      <c r="U49" t="s">
+        <v>48</v>
+      </c>
+      <c r="V49" t="s">
+        <v>111</v>
+      </c>
+      <c r="W49" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>191</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>192</v>
+      </c>
+      <c r="D50" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" t="s">
+        <v>193</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="G50" t="s">
+        <v>195</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50" t="s">
+        <v>31</v>
+      </c>
+      <c r="O50" t="s">
+        <v>32</v>
+      </c>
+      <c r="P50" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>34</v>
+      </c>
+      <c r="R50" t="s">
+        <v>35</v>
+      </c>
+      <c r="S50" t="s">
+        <v>36</v>
+      </c>
+      <c r="T50" t="s">
+        <v>37</v>
+      </c>
+      <c r="U50" t="s">
+        <v>38</v>
+      </c>
+      <c r="V50" t="s">
+        <v>30</v>
+      </c>
+      <c r="W50" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>191</v>
+      </c>
+      <c r="B51" s="1">
+        <v>10001</v>
+      </c>
+      <c r="C51" t="s">
+        <v>196</v>
+      </c>
+      <c r="D51" t="s">
+        <v>26</v>
+      </c>
+      <c r="E51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" t="s">
+        <v>197</v>
+      </c>
+      <c r="G51" t="s">
+        <v>195</v>
+      </c>
+      <c r="H51">
+        <v>34.521169999999998</v>
+      </c>
+      <c r="I51">
+        <v>-6.4532749999999997</v>
+      </c>
+      <c r="J51" s="2">
+        <v>14022</v>
+      </c>
+      <c r="K51">
+        <v>779517433</v>
+      </c>
+      <c r="L51" t="s">
+        <v>198</v>
+      </c>
+      <c r="M51">
+        <v>3</v>
+      </c>
+      <c r="N51" t="s">
+        <v>45</v>
+      </c>
+      <c r="O51" t="s">
+        <v>32</v>
+      </c>
+      <c r="P51" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>47</v>
+      </c>
+      <c r="R51" t="s">
+        <v>35</v>
+      </c>
+      <c r="S51" t="s">
+        <v>36</v>
+      </c>
+      <c r="T51" t="s">
+        <v>37</v>
+      </c>
+      <c r="U51" t="s">
+        <v>38</v>
+      </c>
+      <c r="V51" t="s">
+        <v>48</v>
+      </c>
+      <c r="W51" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>191</v>
+      </c>
+      <c r="B52" s="1">
+        <v>10002</v>
+      </c>
+      <c r="C52" t="s">
+        <v>199</v>
+      </c>
+      <c r="D52" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" t="s">
+        <v>200</v>
+      </c>
+      <c r="F52" t="s">
+        <v>201</v>
+      </c>
+      <c r="G52" t="s">
+        <v>195</v>
+      </c>
+      <c r="H52">
+        <v>34.360207000000003</v>
+      </c>
+      <c r="I52">
+        <v>-6.5500749999999996</v>
+      </c>
+      <c r="J52" s="2">
+        <v>14053</v>
+      </c>
+      <c r="K52">
+        <v>753476995</v>
+      </c>
+      <c r="L52" t="s">
+        <v>202</v>
+      </c>
+      <c r="M52">
+        <v>2</v>
+      </c>
+      <c r="N52" t="s">
+        <v>45</v>
+      </c>
+      <c r="O52" t="s">
+        <v>32</v>
+      </c>
+      <c r="P52" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>47</v>
+      </c>
+      <c r="R52" t="s">
+        <v>35</v>
+      </c>
+      <c r="S52" t="s">
+        <v>36</v>
+      </c>
+      <c r="T52" t="s">
+        <v>37</v>
+      </c>
+      <c r="U52" t="s">
+        <v>38</v>
+      </c>
+      <c r="V52" t="s">
+        <v>38</v>
+      </c>
+      <c r="W52" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>191</v>
+      </c>
+      <c r="B53" s="1">
+        <v>10003</v>
+      </c>
+      <c r="C53" t="s">
+        <v>203</v>
+      </c>
+      <c r="D53" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53" t="s">
+        <v>204</v>
+      </c>
+      <c r="F53" t="s">
+        <v>205</v>
+      </c>
+      <c r="G53" t="s">
+        <v>195</v>
+      </c>
+      <c r="H53">
+        <v>34.405692000000002</v>
+      </c>
+      <c r="I53">
+        <v>-6.4333679999999998</v>
+      </c>
+      <c r="J53" s="2">
+        <v>14023</v>
+      </c>
+      <c r="K53">
+        <v>734239083</v>
+      </c>
+      <c r="L53" t="s">
+        <v>206</v>
+      </c>
+      <c r="M53">
+        <v>4</v>
+      </c>
+      <c r="N53" t="s">
+        <v>45</v>
+      </c>
+      <c r="O53" t="s">
+        <v>32</v>
+      </c>
+      <c r="P53" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>47</v>
+      </c>
+      <c r="R53" t="s">
+        <v>35</v>
+      </c>
+      <c r="S53" t="s">
+        <v>36</v>
+      </c>
+      <c r="T53" t="s">
+        <v>37</v>
+      </c>
+      <c r="U53" t="s">
+        <v>38</v>
+      </c>
+      <c r="V53" t="s">
+        <v>61</v>
+      </c>
+      <c r="W53" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>191</v>
+      </c>
+      <c r="B54" s="1">
+        <v>10004</v>
+      </c>
+      <c r="C54" t="s">
+        <v>207</v>
+      </c>
+      <c r="D54" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54" t="s">
+        <v>208</v>
+      </c>
+      <c r="F54" t="s">
+        <v>209</v>
+      </c>
+      <c r="G54" t="s">
+        <v>195</v>
+      </c>
+      <c r="H54">
+        <v>34.287878999999997</v>
+      </c>
+      <c r="I54">
+        <v>-6.5164280000000003</v>
+      </c>
+      <c r="J54" s="2">
+        <v>14000</v>
+      </c>
+      <c r="K54">
+        <v>937997757</v>
+      </c>
+      <c r="L54" t="s">
+        <v>210</v>
+      </c>
+      <c r="M54">
+        <v>2</v>
+      </c>
+      <c r="N54" t="s">
+        <v>45</v>
+      </c>
+      <c r="O54" t="s">
+        <v>32</v>
+      </c>
+      <c r="P54" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>47</v>
+      </c>
+      <c r="R54" t="s">
+        <v>35</v>
+      </c>
+      <c r="S54" t="s">
+        <v>36</v>
+      </c>
+      <c r="T54" t="s">
+        <v>37</v>
+      </c>
+      <c r="U54" t="s">
+        <v>38</v>
+      </c>
+      <c r="V54" t="s">
+        <v>48</v>
+      </c>
+      <c r="W54" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>191</v>
+      </c>
+      <c r="B55" s="1">
+        <v>10005</v>
+      </c>
+      <c r="C55" t="s">
+        <v>211</v>
+      </c>
+      <c r="D55" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" t="s">
+        <v>212</v>
+      </c>
+      <c r="F55" t="s">
+        <v>209</v>
+      </c>
+      <c r="G55" t="s">
+        <v>213</v>
+      </c>
+      <c r="H55">
+        <v>34.256413999999999</v>
+      </c>
+      <c r="I55">
+        <v>-6.6754990000000003</v>
+      </c>
+      <c r="J55" s="2">
+        <v>14110</v>
+      </c>
+      <c r="K55">
+        <v>887311749</v>
+      </c>
+      <c r="L55" t="s">
+        <v>214</v>
+      </c>
+      <c r="M55">
+        <v>1</v>
+      </c>
+      <c r="N55" t="s">
+        <v>45</v>
+      </c>
+      <c r="O55" t="s">
+        <v>32</v>
+      </c>
+      <c r="P55" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>47</v>
+      </c>
+      <c r="R55" t="s">
+        <v>35</v>
+      </c>
+      <c r="S55" t="s">
+        <v>36</v>
+      </c>
+      <c r="T55" t="s">
+        <v>37</v>
+      </c>
+      <c r="U55" t="s">
+        <v>38</v>
+      </c>
+      <c r="V55" t="s">
+        <v>73</v>
+      </c>
+      <c r="W55" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>191</v>
+      </c>
+      <c r="B56" s="1">
+        <v>10006</v>
+      </c>
+      <c r="C56" t="s">
+        <v>215</v>
+      </c>
+      <c r="D56" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" t="s">
+        <v>216</v>
+      </c>
+      <c r="F56" t="s">
+        <v>209</v>
+      </c>
+      <c r="G56" t="s">
+        <v>213</v>
+      </c>
+      <c r="H56">
+        <v>34.262476999999997</v>
+      </c>
+      <c r="I56">
+        <v>-6.6186049999999996</v>
+      </c>
+      <c r="J56" s="2">
+        <v>14080</v>
+      </c>
+      <c r="K56">
+        <v>915790305</v>
+      </c>
+      <c r="L56" t="s">
+        <v>217</v>
+      </c>
+      <c r="M56">
+        <v>5</v>
+      </c>
+      <c r="N56" t="s">
+        <v>45</v>
+      </c>
+      <c r="O56" t="s">
+        <v>32</v>
+      </c>
+      <c r="P56" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>47</v>
+      </c>
+      <c r="R56" t="s">
+        <v>35</v>
+      </c>
+      <c r="S56" t="s">
+        <v>36</v>
+      </c>
+      <c r="T56" t="s">
+        <v>37</v>
+      </c>
+      <c r="U56" t="s">
+        <v>38</v>
+      </c>
+      <c r="V56" t="s">
+        <v>79</v>
+      </c>
+      <c r="W56" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>191</v>
+      </c>
+      <c r="B57" s="1">
+        <v>10007</v>
+      </c>
+      <c r="C57" t="s">
+        <v>218</v>
+      </c>
+      <c r="D57" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57" t="s">
+        <v>219</v>
+      </c>
+      <c r="F57" t="s">
+        <v>220</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H57">
+        <v>34.192861000000001</v>
+      </c>
+      <c r="I57">
+        <v>-6.683662</v>
+      </c>
+      <c r="J57" s="2">
+        <v>14025</v>
+      </c>
+      <c r="K57">
+        <v>811552880</v>
+      </c>
+      <c r="L57" t="s">
+        <v>221</v>
+      </c>
+      <c r="M57">
+        <v>2</v>
+      </c>
+      <c r="N57" t="s">
+        <v>45</v>
+      </c>
+      <c r="O57" t="s">
+        <v>32</v>
+      </c>
+      <c r="P57" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>47</v>
+      </c>
+      <c r="R57" t="s">
+        <v>35</v>
+      </c>
+      <c r="S57" t="s">
+        <v>36</v>
+      </c>
+      <c r="T57" t="s">
+        <v>37</v>
+      </c>
+      <c r="U57" t="s">
+        <v>38</v>
+      </c>
+      <c r="V57" t="s">
+        <v>85</v>
+      </c>
+      <c r="W57" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>191</v>
+      </c>
+      <c r="B58" s="1">
+        <v>10008</v>
+      </c>
+      <c r="C58" t="s">
+        <v>222</v>
+      </c>
+      <c r="D58" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" t="s">
+        <v>223</v>
+      </c>
+      <c r="F58" t="s">
+        <v>224</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H58">
+        <v>34.522413999999998</v>
+      </c>
+      <c r="I58">
+        <v>-6.3204710000000004</v>
+      </c>
+      <c r="J58" s="2">
+        <v>14050</v>
+      </c>
+      <c r="K58">
+        <v>695325692</v>
+      </c>
+      <c r="L58" t="s">
+        <v>225</v>
+      </c>
+      <c r="M58">
+        <v>2</v>
+      </c>
+      <c r="N58" t="s">
+        <v>45</v>
+      </c>
+      <c r="O58" t="s">
+        <v>32</v>
+      </c>
+      <c r="P58" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>47</v>
+      </c>
+      <c r="R58" t="s">
+        <v>35</v>
+      </c>
+      <c r="S58" t="s">
+        <v>36</v>
+      </c>
+      <c r="T58" t="s">
+        <v>37</v>
+      </c>
+      <c r="U58" t="s">
+        <v>38</v>
+      </c>
+      <c r="V58" t="s">
+        <v>92</v>
+      </c>
+      <c r="W58" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>191</v>
+      </c>
+      <c r="B59" s="1">
+        <v>10009</v>
+      </c>
+      <c r="C59" t="s">
+        <v>226</v>
+      </c>
+      <c r="D59" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" t="s">
+        <v>227</v>
+      </c>
+      <c r="F59" t="s">
+        <v>228</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H59">
+        <v>33.998232000000002</v>
+      </c>
+      <c r="I59">
+        <v>-6.8457280000000003</v>
+      </c>
+      <c r="J59" s="2">
+        <v>10106</v>
+      </c>
+      <c r="K59">
+        <v>745360421</v>
+      </c>
+      <c r="L59" t="s">
+        <v>229</v>
+      </c>
+      <c r="M59">
+        <v>2</v>
+      </c>
+      <c r="N59" t="s">
+        <v>45</v>
+      </c>
+      <c r="O59" t="s">
+        <v>32</v>
+      </c>
+      <c r="P59" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>47</v>
+      </c>
+      <c r="R59" t="s">
+        <v>35</v>
+      </c>
+      <c r="S59" t="s">
+        <v>36</v>
+      </c>
+      <c r="T59" t="s">
+        <v>37</v>
+      </c>
+      <c r="U59" t="s">
+        <v>48</v>
+      </c>
+      <c r="V59" t="s">
+        <v>99</v>
+      </c>
+      <c r="W59" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>191</v>
+      </c>
+      <c r="B60" s="1">
+        <v>10010</v>
+      </c>
+      <c r="C60" t="s">
+        <v>230</v>
+      </c>
+      <c r="D60" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" t="s">
+        <v>231</v>
+      </c>
+      <c r="F60" t="s">
+        <v>228</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H60">
+        <v>34.017502</v>
+      </c>
+      <c r="I60">
+        <v>-6.8347449999999998</v>
+      </c>
+      <c r="J60" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K60">
+        <v>766074745</v>
+      </c>
+      <c r="L60" t="s">
+        <v>232</v>
+      </c>
+      <c r="M60">
+        <v>2</v>
+      </c>
+      <c r="N60" t="s">
+        <v>45</v>
+      </c>
+      <c r="O60" t="s">
+        <v>32</v>
+      </c>
+      <c r="P60" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>47</v>
+      </c>
+      <c r="R60" t="s">
+        <v>35</v>
+      </c>
+      <c r="S60" t="s">
+        <v>36</v>
+      </c>
+      <c r="T60" t="s">
+        <v>37</v>
+      </c>
+      <c r="U60" t="s">
+        <v>48</v>
+      </c>
+      <c r="V60" t="s">
+        <v>105</v>
+      </c>
+      <c r="W60" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>191</v>
+      </c>
+      <c r="B61" s="1">
+        <v>10011</v>
+      </c>
+      <c r="C61" t="s">
+        <v>233</v>
+      </c>
+      <c r="D61" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" t="s">
+        <v>234</v>
+      </c>
+      <c r="F61" t="s">
+        <v>228</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H61">
+        <v>33.986607999999997</v>
+      </c>
+      <c r="I61">
+        <v>-6.8288729999999997</v>
+      </c>
+      <c r="J61" s="2">
+        <v>10105</v>
+      </c>
+      <c r="K61">
+        <v>787248921</v>
+      </c>
+      <c r="L61" t="s">
+        <v>235</v>
+      </c>
+      <c r="M61">
+        <v>2</v>
+      </c>
+      <c r="N61" t="s">
+        <v>45</v>
+      </c>
+      <c r="O61" t="s">
+        <v>32</v>
+      </c>
+      <c r="P61" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>47</v>
+      </c>
+      <c r="R61" t="s">
+        <v>35</v>
+      </c>
+      <c r="S61" t="s">
+        <v>36</v>
+      </c>
+      <c r="T61" t="s">
+        <v>37</v>
+      </c>
+      <c r="U61" t="s">
+        <v>48</v>
+      </c>
+      <c r="V61" t="s">
+        <v>111</v>
+      </c>
+      <c r="W61" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>191</v>
+      </c>
+      <c r="B62" s="1">
+        <v>10012</v>
+      </c>
+      <c r="C62" t="s">
+        <v>236</v>
+      </c>
+      <c r="D62" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" t="s">
+        <v>237</v>
+      </c>
+      <c r="F62" t="s">
+        <v>228</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H62">
+        <v>33.978102999999997</v>
+      </c>
+      <c r="I62">
+        <v>-6.8678489999999996</v>
+      </c>
+      <c r="J62" s="2">
+        <v>10112</v>
+      </c>
+      <c r="K62">
+        <v>838412388</v>
+      </c>
+      <c r="L62" t="s">
+        <v>238</v>
+      </c>
+      <c r="M62">
+        <v>2</v>
+      </c>
+      <c r="N62" t="s">
+        <v>45</v>
+      </c>
+      <c r="O62" t="s">
+        <v>32</v>
+      </c>
+      <c r="P62" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>47</v>
+      </c>
+      <c r="R62" t="s">
+        <v>35</v>
+      </c>
+      <c r="S62" t="s">
+        <v>36</v>
+      </c>
+      <c r="T62" t="s">
+        <v>37</v>
+      </c>
+      <c r="U62" t="s">
+        <v>48</v>
+      </c>
+      <c r="V62" t="s">
+        <v>92</v>
+      </c>
+      <c r="W62" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>191</v>
+      </c>
+      <c r="B63" s="1">
+        <v>10013</v>
+      </c>
+      <c r="C63" t="s">
+        <v>239</v>
+      </c>
+      <c r="D63" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" t="s">
+        <v>240</v>
+      </c>
+      <c r="F63" t="s">
+        <v>228</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H63">
+        <v>33.953930999999997</v>
+      </c>
+      <c r="I63">
+        <v>-6.8747350000000003</v>
+      </c>
+      <c r="J63" s="2">
+        <v>10104</v>
+      </c>
+      <c r="K63">
+        <v>751913644</v>
+      </c>
+      <c r="L63" t="s">
+        <v>241</v>
+      </c>
+      <c r="M63">
+        <v>2</v>
+      </c>
+      <c r="N63" t="s">
+        <v>45</v>
+      </c>
+      <c r="O63" t="s">
+        <v>32</v>
+      </c>
+      <c r="P63" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>47</v>
+      </c>
+      <c r="R63" t="s">
+        <v>35</v>
+      </c>
+      <c r="S63" t="s">
+        <v>36</v>
+      </c>
+      <c r="T63" t="s">
+        <v>37</v>
+      </c>
+      <c r="U63" t="s">
+        <v>48</v>
+      </c>
+      <c r="V63" t="s">
+        <v>99</v>
+      </c>
+      <c r="W63" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>191</v>
+      </c>
+      <c r="B64" s="1">
+        <v>10014</v>
+      </c>
+      <c r="C64" t="s">
+        <v>242</v>
+      </c>
+      <c r="D64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" t="s">
+        <v>243</v>
+      </c>
+      <c r="F64" t="s">
+        <v>228</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H64">
+        <v>34.027757000000001</v>
+      </c>
+      <c r="I64">
+        <v>-6.8341469999999997</v>
+      </c>
+      <c r="J64" s="2">
+        <v>10036</v>
+      </c>
+      <c r="K64">
+        <v>965639376</v>
+      </c>
+      <c r="L64" t="s">
+        <v>244</v>
+      </c>
+      <c r="M64">
+        <v>2</v>
+      </c>
+      <c r="N64" t="s">
+        <v>45</v>
+      </c>
+      <c r="O64" t="s">
+        <v>32</v>
+      </c>
+      <c r="P64" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>47</v>
+      </c>
+      <c r="R64" t="s">
+        <v>35</v>
+      </c>
+      <c r="S64" t="s">
+        <v>36</v>
+      </c>
+      <c r="T64" t="s">
+        <v>37</v>
+      </c>
+      <c r="U64" t="s">
+        <v>48</v>
+      </c>
+      <c r="V64" t="s">
+        <v>105</v>
+      </c>
+      <c r="W64" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>191</v>
+      </c>
+      <c r="B65" s="1">
+        <v>10015</v>
+      </c>
+      <c r="C65" t="s">
+        <v>245</v>
+      </c>
+      <c r="D65" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" t="s">
+        <v>246</v>
+      </c>
+      <c r="F65" t="s">
+        <v>228</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="H65">
+        <v>33.995612000000001</v>
+      </c>
+      <c r="I65">
+        <v>-6.8152809999999997</v>
+      </c>
+      <c r="J65" s="2">
+        <v>10190</v>
+      </c>
+      <c r="K65">
+        <v>803062069</v>
+      </c>
+      <c r="L65" t="s">
+        <v>247</v>
+      </c>
+      <c r="M65">
+        <v>2</v>
+      </c>
+      <c r="N65" t="s">
+        <v>45</v>
+      </c>
+      <c r="O65" t="s">
+        <v>32</v>
+      </c>
+      <c r="P65" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>47</v>
+      </c>
+      <c r="R65" t="s">
+        <v>35</v>
+      </c>
+      <c r="S65" t="s">
+        <v>36</v>
+      </c>
+      <c r="T65" t="s">
+        <v>37</v>
+      </c>
+      <c r="U65" t="s">
+        <v>48</v>
+      </c>
+      <c r="V65" t="s">
+        <v>111</v>
+      </c>
+      <c r="W65" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>248</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" t="s">
+        <v>249</v>
+      </c>
+      <c r="D66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="F66" t="s">
+        <v>251</v>
+      </c>
+      <c r="G66" t="s">
+        <v>252</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66" t="s">
+        <v>31</v>
+      </c>
+      <c r="O66" t="s">
+        <v>32</v>
+      </c>
+      <c r="P66" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>34</v>
+      </c>
+      <c r="R66" t="s">
+        <v>35</v>
+      </c>
+      <c r="S66" t="s">
+        <v>36</v>
+      </c>
+      <c r="T66" t="s">
+        <v>37</v>
+      </c>
+      <c r="U66" t="s">
+        <v>38</v>
+      </c>
+      <c r="V66" t="s">
+        <v>30</v>
+      </c>
+      <c r="W66" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>248</v>
+      </c>
+      <c r="B67" s="1">
+        <v>10001</v>
+      </c>
+      <c r="C67" t="s">
+        <v>253</v>
+      </c>
+      <c r="D67" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" t="s">
+        <v>42</v>
+      </c>
+      <c r="F67" t="s">
+        <v>254</v>
+      </c>
+      <c r="G67" t="s">
+        <v>252</v>
+      </c>
+      <c r="H67">
+        <v>34.521169999999998</v>
+      </c>
+      <c r="I67">
+        <v>-6.4532749999999997</v>
+      </c>
+      <c r="J67" s="2">
+        <v>14022</v>
+      </c>
+      <c r="K67">
+        <v>779517433</v>
+      </c>
+      <c r="L67" t="s">
+        <v>255</v>
+      </c>
+      <c r="M67">
+        <v>3</v>
+      </c>
+      <c r="N67" t="s">
+        <v>45</v>
+      </c>
+      <c r="O67" t="s">
+        <v>32</v>
+      </c>
+      <c r="P67" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>47</v>
+      </c>
+      <c r="R67" t="s">
+        <v>35</v>
+      </c>
+      <c r="S67" t="s">
+        <v>36</v>
+      </c>
+      <c r="T67" t="s">
+        <v>37</v>
+      </c>
+      <c r="U67" t="s">
+        <v>38</v>
+      </c>
+      <c r="V67" t="s">
+        <v>48</v>
+      </c>
+      <c r="W67" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>248</v>
+      </c>
+      <c r="B68" s="1">
+        <v>10002</v>
+      </c>
+      <c r="C68" t="s">
+        <v>256</v>
+      </c>
+      <c r="D68" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" t="s">
+        <v>257</v>
+      </c>
+      <c r="F68" t="s">
+        <v>54</v>
+      </c>
+      <c r="G68" t="s">
+        <v>252</v>
+      </c>
+      <c r="H68">
+        <v>34.360207000000003</v>
+      </c>
+      <c r="I68">
+        <v>-6.5500749999999996</v>
+      </c>
+      <c r="J68" s="2">
+        <v>14053</v>
+      </c>
+      <c r="K68">
+        <v>753476995</v>
+      </c>
+      <c r="L68" t="s">
+        <v>258</v>
+      </c>
+      <c r="M68">
+        <v>2</v>
+      </c>
+      <c r="N68" t="s">
+        <v>45</v>
+      </c>
+      <c r="O68" t="s">
+        <v>32</v>
+      </c>
+      <c r="P68" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>47</v>
+      </c>
+      <c r="R68" t="s">
+        <v>35</v>
+      </c>
+      <c r="S68" t="s">
+        <v>36</v>
+      </c>
+      <c r="T68" t="s">
+        <v>37</v>
+      </c>
+      <c r="U68" t="s">
+        <v>38</v>
+      </c>
+      <c r="V68" t="s">
+        <v>38</v>
+      </c>
+      <c r="W68" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>248</v>
+      </c>
+      <c r="B69" s="1">
+        <v>10003</v>
+      </c>
+      <c r="C69" t="s">
+        <v>259</v>
+      </c>
+      <c r="D69" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" t="s">
+        <v>260</v>
+      </c>
+      <c r="F69" t="s">
+        <v>261</v>
+      </c>
+      <c r="G69" t="s">
+        <v>252</v>
+      </c>
+      <c r="H69">
+        <v>34.405692000000002</v>
+      </c>
+      <c r="I69">
+        <v>-6.4333679999999998</v>
+      </c>
+      <c r="J69" s="2">
+        <v>14023</v>
+      </c>
+      <c r="K69">
+        <v>734239083</v>
+      </c>
+      <c r="L69" t="s">
+        <v>262</v>
+      </c>
+      <c r="M69">
+        <v>4</v>
+      </c>
+      <c r="N69" t="s">
+        <v>45</v>
+      </c>
+      <c r="O69" t="s">
+        <v>32</v>
+      </c>
+      <c r="P69" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>47</v>
+      </c>
+      <c r="R69" t="s">
+        <v>35</v>
+      </c>
+      <c r="S69" t="s">
+        <v>36</v>
+      </c>
+      <c r="T69" t="s">
+        <v>37</v>
+      </c>
+      <c r="U69" t="s">
+        <v>38</v>
+      </c>
+      <c r="V69" t="s">
+        <v>61</v>
+      </c>
+      <c r="W69" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>248</v>
+      </c>
+      <c r="B70" s="1">
+        <v>10004</v>
+      </c>
+      <c r="C70" t="s">
+        <v>263</v>
+      </c>
+      <c r="D70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" t="s">
+        <v>264</v>
+      </c>
+      <c r="F70" t="s">
+        <v>265</v>
+      </c>
+      <c r="G70" t="s">
+        <v>252</v>
+      </c>
+      <c r="H70">
+        <v>34.287878999999997</v>
+      </c>
+      <c r="I70">
+        <v>-6.5164280000000003</v>
+      </c>
+      <c r="J70" s="2">
+        <v>14000</v>
+      </c>
+      <c r="K70">
+        <v>937997757</v>
+      </c>
+      <c r="L70" t="s">
+        <v>266</v>
+      </c>
+      <c r="M70">
+        <v>2</v>
+      </c>
+      <c r="N70" t="s">
+        <v>45</v>
+      </c>
+      <c r="O70" t="s">
+        <v>32</v>
+      </c>
+      <c r="P70" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>47</v>
+      </c>
+      <c r="R70" t="s">
+        <v>35</v>
+      </c>
+      <c r="S70" t="s">
+        <v>36</v>
+      </c>
+      <c r="T70" t="s">
+        <v>37</v>
+      </c>
+      <c r="U70" t="s">
+        <v>38</v>
+      </c>
+      <c r="V70" t="s">
+        <v>48</v>
+      </c>
+      <c r="W70" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>248</v>
+      </c>
+      <c r="B71" s="1">
+        <v>10005</v>
+      </c>
+      <c r="C71" t="s">
+        <v>267</v>
+      </c>
+      <c r="D71" t="s">
+        <v>26</v>
+      </c>
+      <c r="E71" t="s">
+        <v>268</v>
+      </c>
+      <c r="F71" t="s">
+        <v>265</v>
+      </c>
+      <c r="G71" t="s">
+        <v>269</v>
+      </c>
+      <c r="H71">
+        <v>34.256413999999999</v>
+      </c>
+      <c r="I71">
+        <v>-6.6754990000000003</v>
+      </c>
+      <c r="J71" s="2">
+        <v>14110</v>
+      </c>
+      <c r="K71">
+        <v>887311749</v>
+      </c>
+      <c r="L71" t="s">
+        <v>270</v>
+      </c>
+      <c r="M71">
+        <v>1</v>
+      </c>
+      <c r="N71" t="s">
+        <v>45</v>
+      </c>
+      <c r="O71" t="s">
+        <v>32</v>
+      </c>
+      <c r="P71" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>47</v>
+      </c>
+      <c r="R71" t="s">
+        <v>35</v>
+      </c>
+      <c r="S71" t="s">
+        <v>36</v>
+      </c>
+      <c r="T71" t="s">
+        <v>37</v>
+      </c>
+      <c r="U71" t="s">
+        <v>38</v>
+      </c>
+      <c r="V71" t="s">
+        <v>73</v>
+      </c>
+      <c r="W71" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>248</v>
+      </c>
+      <c r="B72" s="1">
+        <v>10006</v>
+      </c>
+      <c r="C72" t="s">
+        <v>271</v>
+      </c>
+      <c r="D72" t="s">
+        <v>26</v>
+      </c>
+      <c r="E72" t="s">
+        <v>272</v>
+      </c>
+      <c r="F72" t="s">
+        <v>265</v>
+      </c>
+      <c r="G72" t="s">
+        <v>269</v>
+      </c>
+      <c r="H72">
+        <v>34.262476999999997</v>
+      </c>
+      <c r="I72">
+        <v>-6.6186049999999996</v>
+      </c>
+      <c r="J72" s="2">
+        <v>14080</v>
+      </c>
+      <c r="K72">
+        <v>915790305</v>
+      </c>
+      <c r="L72" t="s">
+        <v>273</v>
+      </c>
+      <c r="M72">
+        <v>5</v>
+      </c>
+      <c r="N72" t="s">
+        <v>45</v>
+      </c>
+      <c r="O72" t="s">
+        <v>32</v>
+      </c>
+      <c r="P72" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>47</v>
+      </c>
+      <c r="R72" t="s">
+        <v>35</v>
+      </c>
+      <c r="S72" t="s">
+        <v>36</v>
+      </c>
+      <c r="T72" t="s">
+        <v>37</v>
+      </c>
+      <c r="U72" t="s">
+        <v>38</v>
+      </c>
+      <c r="V72" t="s">
+        <v>79</v>
+      </c>
+      <c r="W72" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>248</v>
+      </c>
+      <c r="B73" s="1">
+        <v>10007</v>
+      </c>
+      <c r="C73" t="s">
+        <v>274</v>
+      </c>
+      <c r="D73" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" t="s">
+        <v>275</v>
+      </c>
+      <c r="F73" t="s">
+        <v>276</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H73">
+        <v>34.192861000000001</v>
+      </c>
+      <c r="I73">
+        <v>-6.683662</v>
+      </c>
+      <c r="J73" s="2">
+        <v>14025</v>
+      </c>
+      <c r="K73">
+        <v>811552880</v>
+      </c>
+      <c r="L73" t="s">
+        <v>277</v>
+      </c>
+      <c r="M73">
+        <v>2</v>
+      </c>
+      <c r="N73" t="s">
+        <v>45</v>
+      </c>
+      <c r="O73" t="s">
+        <v>32</v>
+      </c>
+      <c r="P73" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>47</v>
+      </c>
+      <c r="R73" t="s">
+        <v>35</v>
+      </c>
+      <c r="S73" t="s">
+        <v>36</v>
+      </c>
+      <c r="T73" t="s">
+        <v>37</v>
+      </c>
+      <c r="U73" t="s">
+        <v>38</v>
+      </c>
+      <c r="V73" t="s">
+        <v>85</v>
+      </c>
+      <c r="W73" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>248</v>
+      </c>
+      <c r="B74" s="1">
+        <v>10008</v>
+      </c>
+      <c r="C74" t="s">
+        <v>278</v>
+      </c>
+      <c r="D74" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" t="s">
+        <v>279</v>
+      </c>
+      <c r="F74" t="s">
+        <v>280</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H74">
+        <v>34.522413999999998</v>
+      </c>
+      <c r="I74">
+        <v>-6.3204710000000004</v>
+      </c>
+      <c r="J74" s="2">
+        <v>14050</v>
+      </c>
+      <c r="K74">
+        <v>695325692</v>
+      </c>
+      <c r="L74" t="s">
+        <v>281</v>
+      </c>
+      <c r="M74">
+        <v>2</v>
+      </c>
+      <c r="N74" t="s">
+        <v>45</v>
+      </c>
+      <c r="O74" t="s">
+        <v>32</v>
+      </c>
+      <c r="P74" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>47</v>
+      </c>
+      <c r="R74" t="s">
+        <v>35</v>
+      </c>
+      <c r="S74" t="s">
+        <v>36</v>
+      </c>
+      <c r="T74" t="s">
+        <v>37</v>
+      </c>
+      <c r="U74" t="s">
+        <v>38</v>
+      </c>
+      <c r="V74" t="s">
+        <v>92</v>
+      </c>
+      <c r="W74" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>248</v>
+      </c>
+      <c r="B75" s="1">
+        <v>10009</v>
+      </c>
+      <c r="C75" t="s">
+        <v>282</v>
+      </c>
+      <c r="D75" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75" t="s">
+        <v>283</v>
+      </c>
+      <c r="F75" t="s">
+        <v>284</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H75">
+        <v>33.998232000000002</v>
+      </c>
+      <c r="I75">
+        <v>-6.8457280000000003</v>
+      </c>
+      <c r="J75" s="2">
+        <v>10106</v>
+      </c>
+      <c r="K75">
+        <v>745360421</v>
+      </c>
+      <c r="L75" t="s">
+        <v>285</v>
+      </c>
+      <c r="M75">
+        <v>2</v>
+      </c>
+      <c r="N75" t="s">
+        <v>45</v>
+      </c>
+      <c r="O75" t="s">
+        <v>32</v>
+      </c>
+      <c r="P75" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>47</v>
+      </c>
+      <c r="R75" t="s">
+        <v>35</v>
+      </c>
+      <c r="S75" t="s">
+        <v>36</v>
+      </c>
+      <c r="T75" t="s">
+        <v>37</v>
+      </c>
+      <c r="U75" t="s">
+        <v>48</v>
+      </c>
+      <c r="V75" t="s">
+        <v>99</v>
+      </c>
+      <c r="W75" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>248</v>
+      </c>
+      <c r="B76" s="1">
+        <v>10010</v>
+      </c>
+      <c r="C76" t="s">
+        <v>286</v>
+      </c>
+      <c r="D76" t="s">
+        <v>26</v>
+      </c>
+      <c r="E76" t="s">
+        <v>287</v>
+      </c>
+      <c r="F76" t="s">
+        <v>284</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H76">
+        <v>34.017502</v>
+      </c>
+      <c r="I76">
+        <v>-6.8347449999999998</v>
+      </c>
+      <c r="J76" s="2">
+        <v>10000</v>
+      </c>
+      <c r="K76">
+        <v>766074745</v>
+      </c>
+      <c r="L76" t="s">
+        <v>288</v>
+      </c>
+      <c r="M76">
+        <v>2</v>
+      </c>
+      <c r="N76" t="s">
+        <v>45</v>
+      </c>
+      <c r="O76" t="s">
+        <v>32</v>
+      </c>
+      <c r="P76" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>47</v>
+      </c>
+      <c r="R76" t="s">
+        <v>35</v>
+      </c>
+      <c r="S76" t="s">
+        <v>36</v>
+      </c>
+      <c r="T76" t="s">
+        <v>37</v>
+      </c>
+      <c r="U76" t="s">
+        <v>48</v>
+      </c>
+      <c r="V76" t="s">
+        <v>105</v>
+      </c>
+      <c r="W76" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>248</v>
+      </c>
+      <c r="B77" s="1">
+        <v>10011</v>
+      </c>
+      <c r="C77" t="s">
+        <v>289</v>
+      </c>
+      <c r="D77" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77" t="s">
+        <v>290</v>
+      </c>
+      <c r="F77" t="s">
+        <v>284</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H77">
+        <v>33.986607999999997</v>
+      </c>
+      <c r="I77">
+        <v>-6.8288729999999997</v>
+      </c>
+      <c r="J77" s="2">
+        <v>10105</v>
+      </c>
+      <c r="K77">
+        <v>787248921</v>
+      </c>
+      <c r="L77" t="s">
+        <v>291</v>
+      </c>
+      <c r="M77">
+        <v>2</v>
+      </c>
+      <c r="N77" t="s">
+        <v>45</v>
+      </c>
+      <c r="O77" t="s">
+        <v>32</v>
+      </c>
+      <c r="P77" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>47</v>
+      </c>
+      <c r="R77" t="s">
+        <v>35</v>
+      </c>
+      <c r="S77" t="s">
+        <v>36</v>
+      </c>
+      <c r="T77" t="s">
+        <v>37</v>
+      </c>
+      <c r="U77" t="s">
+        <v>48</v>
+      </c>
+      <c r="V77" t="s">
+        <v>111</v>
+      </c>
+      <c r="W77" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>248</v>
+      </c>
+      <c r="B78" s="1">
+        <v>10012</v>
+      </c>
+      <c r="C78" t="s">
+        <v>292</v>
+      </c>
+      <c r="D78" t="s">
+        <v>26</v>
+      </c>
+      <c r="E78" t="s">
+        <v>293</v>
+      </c>
+      <c r="F78" t="s">
+        <v>284</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H78">
+        <v>33.978102999999997</v>
+      </c>
+      <c r="I78">
+        <v>-6.8678489999999996</v>
+      </c>
+      <c r="J78" s="2">
+        <v>10112</v>
+      </c>
+      <c r="K78">
+        <v>838412388</v>
+      </c>
+      <c r="L78" t="s">
+        <v>294</v>
+      </c>
+      <c r="M78">
+        <v>2</v>
+      </c>
+      <c r="N78" t="s">
+        <v>45</v>
+      </c>
+      <c r="O78" t="s">
+        <v>32</v>
+      </c>
+      <c r="P78" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>47</v>
+      </c>
+      <c r="R78" t="s">
+        <v>35</v>
+      </c>
+      <c r="S78" t="s">
+        <v>36</v>
+      </c>
+      <c r="T78" t="s">
+        <v>37</v>
+      </c>
+      <c r="U78" t="s">
+        <v>48</v>
+      </c>
+      <c r="V78" t="s">
+        <v>92</v>
+      </c>
+      <c r="W78" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>248</v>
+      </c>
+      <c r="B79" s="1">
+        <v>10013</v>
+      </c>
+      <c r="C79" t="s">
+        <v>295</v>
+      </c>
+      <c r="D79" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" t="s">
+        <v>296</v>
+      </c>
+      <c r="F79" t="s">
+        <v>284</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H79">
+        <v>33.953930999999997</v>
+      </c>
+      <c r="I79">
+        <v>-6.8747350000000003</v>
+      </c>
+      <c r="J79" s="2">
+        <v>10104</v>
+      </c>
+      <c r="K79">
+        <v>751913644</v>
+      </c>
+      <c r="L79" t="s">
+        <v>297</v>
+      </c>
+      <c r="M79">
+        <v>2</v>
+      </c>
+      <c r="N79" t="s">
+        <v>45</v>
+      </c>
+      <c r="O79" t="s">
+        <v>32</v>
+      </c>
+      <c r="P79" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>47</v>
+      </c>
+      <c r="R79" t="s">
+        <v>35</v>
+      </c>
+      <c r="S79" t="s">
+        <v>36</v>
+      </c>
+      <c r="T79" t="s">
+        <v>37</v>
+      </c>
+      <c r="U79" t="s">
+        <v>48</v>
+      </c>
+      <c r="V79" t="s">
+        <v>99</v>
+      </c>
+      <c r="W79" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>248</v>
+      </c>
+      <c r="B80" s="1">
+        <v>10014</v>
+      </c>
+      <c r="C80" t="s">
+        <v>298</v>
+      </c>
+      <c r="D80" t="s">
+        <v>26</v>
+      </c>
+      <c r="E80" t="s">
+        <v>299</v>
+      </c>
+      <c r="F80" t="s">
+        <v>284</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H80">
+        <v>34.027757000000001</v>
+      </c>
+      <c r="I80">
+        <v>-6.8341469999999997</v>
+      </c>
+      <c r="J80" s="2">
+        <v>10036</v>
+      </c>
+      <c r="K80">
+        <v>965639376</v>
+      </c>
+      <c r="L80" t="s">
+        <v>300</v>
+      </c>
+      <c r="M80">
+        <v>2</v>
+      </c>
+      <c r="N80" t="s">
+        <v>45</v>
+      </c>
+      <c r="O80" t="s">
+        <v>32</v>
+      </c>
+      <c r="P80" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>47</v>
+      </c>
+      <c r="R80" t="s">
+        <v>35</v>
+      </c>
+      <c r="S80" t="s">
+        <v>36</v>
+      </c>
+      <c r="T80" t="s">
+        <v>37</v>
+      </c>
+      <c r="U80" t="s">
+        <v>48</v>
+      </c>
+      <c r="V80" t="s">
+        <v>105</v>
+      </c>
+      <c r="W80" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>248</v>
+      </c>
+      <c r="B81" s="1">
+        <v>10015</v>
+      </c>
+      <c r="C81" t="s">
+        <v>301</v>
+      </c>
+      <c r="D81" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" t="s">
+        <v>302</v>
+      </c>
+      <c r="F81" t="s">
+        <v>284</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H81">
+        <v>33.995612000000001</v>
+      </c>
+      <c r="I81">
+        <v>-6.8152809999999997</v>
+      </c>
+      <c r="J81" s="2">
+        <v>10190</v>
+      </c>
+      <c r="K81">
+        <v>803062069</v>
+      </c>
+      <c r="L81" t="s">
+        <v>303</v>
+      </c>
+      <c r="M81">
+        <v>2</v>
+      </c>
+      <c r="N81" t="s">
+        <v>45</v>
+      </c>
+      <c r="O81" t="s">
+        <v>32</v>
+      </c>
+      <c r="P81" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>47</v>
+      </c>
+      <c r="R81" t="s">
+        <v>35</v>
+      </c>
+      <c r="S81" t="s">
+        <v>36</v>
+      </c>
+      <c r="T81" t="s">
+        <v>37</v>
+      </c>
+      <c r="U81" t="s">
+        <v>48</v>
+      </c>
+      <c r="V81" t="s">
+        <v>111</v>
+      </c>
+      <c r="W81" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>304</v>
+      </c>
+      <c r="B82">
+        <v>10137</v>
+      </c>
+      <c r="C82" t="s">
+        <v>305</v>
+      </c>
+      <c r="D82" t="s">
+        <v>26</v>
+      </c>
+      <c r="E82" t="s">
+        <v>53</v>
+      </c>
+      <c r="F82" t="s">
+        <v>54</v>
+      </c>
+      <c r="G82" t="s">
+        <v>320</v>
+      </c>
+      <c r="H82">
+        <v>34.360207000000003</v>
+      </c>
+      <c r="I82">
+        <v>-6.5500749999999996</v>
+      </c>
+      <c r="J82">
+        <v>14053</v>
+      </c>
+      <c r="K82">
+        <v>753476995</v>
+      </c>
+      <c r="L82" t="s">
+        <v>55</v>
+      </c>
+      <c r="M82">
+        <v>2</v>
+      </c>
+      <c r="N82" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O82" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P82" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q82" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R82" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S82" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T82" t="s">
+        <v>37</v>
+      </c>
+      <c r="U82" t="s">
+        <v>38</v>
+      </c>
+      <c r="V82" t="s">
+        <v>38</v>
+      </c>
+      <c r="W82" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>304</v>
+      </c>
+      <c r="B83">
+        <v>10138</v>
+      </c>
+      <c r="C83" t="s">
+        <v>306</v>
+      </c>
+      <c r="D83" t="s">
+        <v>26</v>
+      </c>
+      <c r="E83" t="s">
+        <v>58</v>
+      </c>
+      <c r="F83" t="s">
+        <v>59</v>
+      </c>
+      <c r="G83" t="s">
+        <v>320</v>
+      </c>
+      <c r="H83">
+        <v>34.405692000000002</v>
+      </c>
+      <c r="I83">
+        <v>-6.4333679999999998</v>
+      </c>
+      <c r="J83">
+        <v>14023</v>
+      </c>
+      <c r="K83">
+        <v>734239083</v>
+      </c>
+      <c r="L83" t="s">
+        <v>60</v>
+      </c>
+      <c r="M83">
+        <v>4</v>
+      </c>
+      <c r="N83" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O83" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P83" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q83" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R83" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S83" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T83" t="s">
+        <v>37</v>
+      </c>
+      <c r="U83" t="s">
+        <v>38</v>
+      </c>
+      <c r="V83" t="s">
+        <v>61</v>
+      </c>
+      <c r="W83" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>304</v>
+      </c>
+      <c r="B84">
+        <v>10139</v>
+      </c>
+      <c r="C84" t="s">
+        <v>307</v>
+      </c>
+      <c r="D84" t="s">
+        <v>26</v>
+      </c>
+      <c r="E84" t="s">
+        <v>71</v>
+      </c>
+      <c r="F84" t="s">
+        <v>65</v>
+      </c>
+      <c r="G84" t="s">
+        <v>321</v>
+      </c>
+      <c r="H84">
+        <v>34.256413999999999</v>
+      </c>
+      <c r="I84">
+        <v>-6.6754990000000003</v>
+      </c>
+      <c r="J84">
+        <v>14110</v>
+      </c>
+      <c r="K84">
+        <v>887311749</v>
+      </c>
+      <c r="L84" t="s">
+        <v>326</v>
+      </c>
+      <c r="M84">
+        <v>1</v>
+      </c>
+      <c r="N84" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O84" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P84" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q84" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R84" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S84" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T84" t="s">
+        <v>37</v>
+      </c>
+      <c r="U84" t="s">
+        <v>38</v>
+      </c>
+      <c r="V84" t="s">
+        <v>73</v>
+      </c>
+      <c r="W84" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>304</v>
+      </c>
+      <c r="B85">
+        <v>10140</v>
+      </c>
+      <c r="C85" t="s">
+        <v>308</v>
+      </c>
+      <c r="D85" t="s">
+        <v>26</v>
+      </c>
+      <c r="E85" t="s">
+        <v>77</v>
+      </c>
+      <c r="F85" t="s">
+        <v>65</v>
+      </c>
+      <c r="G85" t="s">
+        <v>321</v>
+      </c>
+      <c r="H85">
+        <v>34.262476999999997</v>
+      </c>
+      <c r="I85">
+        <v>-6.6186049999999996</v>
+      </c>
+      <c r="J85">
+        <v>14080</v>
+      </c>
+      <c r="K85">
+        <v>915790305</v>
+      </c>
+      <c r="L85" t="s">
+        <v>327</v>
+      </c>
+      <c r="M85">
+        <v>5</v>
+      </c>
+      <c r="N85" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O85" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P85" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q85" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R85" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S85" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T85" t="s">
+        <v>37</v>
+      </c>
+      <c r="U85" t="s">
+        <v>38</v>
+      </c>
+      <c r="V85" t="s">
+        <v>79</v>
+      </c>
+      <c r="W85" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>304</v>
+      </c>
+      <c r="B86">
+        <v>10141</v>
+      </c>
+      <c r="C86" t="s">
+        <v>309</v>
+      </c>
+      <c r="D86" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86" t="s">
+        <v>82</v>
+      </c>
+      <c r="F86" t="s">
+        <v>83</v>
+      </c>
+      <c r="G86" t="s">
+        <v>322</v>
+      </c>
+      <c r="H86">
+        <v>34.192861000000001</v>
+      </c>
+      <c r="I86">
+        <v>-6.683662</v>
+      </c>
+      <c r="J86">
+        <v>14025</v>
+      </c>
+      <c r="K86">
+        <v>811552880</v>
+      </c>
+      <c r="L86" t="s">
+        <v>84</v>
+      </c>
+      <c r="M86">
+        <v>2</v>
+      </c>
+      <c r="N86" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O86" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P86" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q86" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R86" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S86" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T86" t="s">
+        <v>37</v>
+      </c>
+      <c r="U86" t="s">
+        <v>38</v>
+      </c>
+      <c r="V86" t="s">
+        <v>85</v>
+      </c>
+      <c r="W86" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>304</v>
+      </c>
+      <c r="B87">
+        <v>10142</v>
+      </c>
+      <c r="C87" t="s">
+        <v>310</v>
+      </c>
+      <c r="D87" t="s">
+        <v>26</v>
+      </c>
+      <c r="E87" t="s">
+        <v>96</v>
+      </c>
+      <c r="F87" t="s">
+        <v>97</v>
+      </c>
+      <c r="G87" t="s">
+        <v>320</v>
+      </c>
+      <c r="H87">
+        <v>33.998232000000002</v>
+      </c>
+      <c r="I87">
+        <v>-6.8457280000000003</v>
+      </c>
+      <c r="J87">
+        <v>10106</v>
+      </c>
+      <c r="K87">
+        <v>745360421</v>
+      </c>
+      <c r="L87" t="s">
+        <v>328</v>
+      </c>
+      <c r="M87">
+        <v>2</v>
+      </c>
+      <c r="N87" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O87" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P87" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q87" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R87" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S87" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T87" t="s">
+        <v>37</v>
+      </c>
+      <c r="U87" t="s">
+        <v>48</v>
+      </c>
+      <c r="V87" t="s">
+        <v>99</v>
+      </c>
+      <c r="W87" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>304</v>
+      </c>
+      <c r="B88">
+        <v>10143</v>
+      </c>
+      <c r="C88" t="s">
+        <v>311</v>
+      </c>
+      <c r="D88" t="s">
+        <v>26</v>
+      </c>
+      <c r="E88" t="s">
+        <v>103</v>
+      </c>
+      <c r="F88" t="s">
+        <v>97</v>
+      </c>
+      <c r="G88" t="s">
+        <v>320</v>
+      </c>
+      <c r="H88">
+        <v>34.017502</v>
+      </c>
+      <c r="I88">
+        <v>-6.8347449999999998</v>
+      </c>
+      <c r="J88">
+        <v>10000</v>
+      </c>
+      <c r="K88">
+        <v>766074745</v>
+      </c>
+      <c r="L88" t="s">
+        <v>104</v>
+      </c>
+      <c r="M88">
+        <v>2</v>
+      </c>
+      <c r="N88" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O88" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P88" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q88" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R88" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S88" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T88" t="s">
+        <v>37</v>
+      </c>
+      <c r="U88" t="s">
+        <v>48</v>
+      </c>
+      <c r="V88" t="s">
+        <v>105</v>
+      </c>
+      <c r="W88" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>304</v>
+      </c>
+      <c r="B89">
+        <v>10144</v>
+      </c>
+      <c r="C89" t="s">
+        <v>312</v>
+      </c>
+      <c r="D89" t="s">
+        <v>26</v>
+      </c>
+      <c r="E89" t="s">
+        <v>109</v>
+      </c>
+      <c r="F89" t="s">
+        <v>97</v>
+      </c>
+      <c r="G89" t="s">
+        <v>320</v>
+      </c>
+      <c r="H89">
+        <v>33.986607999999997</v>
+      </c>
+      <c r="I89">
+        <v>-6.8288729999999997</v>
+      </c>
+      <c r="J89">
+        <v>10105</v>
+      </c>
+      <c r="K89">
+        <v>787248921</v>
+      </c>
+      <c r="L89" t="s">
+        <v>329</v>
+      </c>
+      <c r="M89">
+        <v>2</v>
+      </c>
+      <c r="N89" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O89" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P89" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R89" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S89" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T89" t="s">
+        <v>37</v>
+      </c>
+      <c r="U89" t="s">
+        <v>48</v>
+      </c>
+      <c r="V89" t="s">
+        <v>111</v>
+      </c>
+      <c r="W89" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>304</v>
+      </c>
+      <c r="B90">
+        <v>10145</v>
+      </c>
+      <c r="C90" t="s">
+        <v>313</v>
+      </c>
+      <c r="D90" t="s">
+        <v>26</v>
+      </c>
+      <c r="E90" t="s">
+        <v>115</v>
+      </c>
+      <c r="F90" t="s">
+        <v>97</v>
+      </c>
+      <c r="G90" t="s">
+        <v>320</v>
+      </c>
+      <c r="H90">
+        <v>33.978102999999997</v>
+      </c>
+      <c r="I90">
+        <v>-6.8678489999999996</v>
+      </c>
+      <c r="J90">
+        <v>10112</v>
+      </c>
+      <c r="K90">
+        <v>838412388</v>
+      </c>
+      <c r="L90" t="s">
+        <v>116</v>
+      </c>
+      <c r="M90">
+        <v>2</v>
+      </c>
+      <c r="N90" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O90" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P90" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R90" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S90" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T90" t="s">
+        <v>37</v>
+      </c>
+      <c r="U90" t="s">
+        <v>48</v>
+      </c>
+      <c r="V90" t="s">
+        <v>92</v>
+      </c>
+      <c r="W90" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>304</v>
+      </c>
+      <c r="B91">
+        <v>10146</v>
+      </c>
+      <c r="C91" t="s">
+        <v>314</v>
+      </c>
+      <c r="D91" t="s">
+        <v>26</v>
+      </c>
+      <c r="E91" t="s">
+        <v>120</v>
+      </c>
+      <c r="F91" t="s">
+        <v>97</v>
+      </c>
+      <c r="G91" t="s">
+        <v>320</v>
+      </c>
+      <c r="H91">
+        <v>33.953930999999997</v>
+      </c>
+      <c r="I91">
+        <v>-6.8747350000000003</v>
+      </c>
+      <c r="J91">
+        <v>10104</v>
+      </c>
+      <c r="K91">
+        <v>751913644</v>
+      </c>
+      <c r="L91" t="s">
+        <v>330</v>
+      </c>
+      <c r="M91">
+        <v>2</v>
+      </c>
+      <c r="N91" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O91" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P91" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q91" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R91" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S91" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T91" t="s">
+        <v>37</v>
+      </c>
+      <c r="U91" t="s">
+        <v>48</v>
+      </c>
+      <c r="V91" t="s">
+        <v>99</v>
+      </c>
+      <c r="W91" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>304</v>
+      </c>
+      <c r="B92">
+        <v>10147</v>
+      </c>
+      <c r="C92" t="s">
+        <v>315</v>
+      </c>
+      <c r="D92" t="s">
+        <v>26</v>
+      </c>
+      <c r="E92" t="s">
+        <v>125</v>
+      </c>
+      <c r="F92" t="s">
+        <v>97</v>
+      </c>
+      <c r="G92" t="s">
+        <v>320</v>
+      </c>
+      <c r="H92">
+        <v>34.027757000000001</v>
+      </c>
+      <c r="I92">
+        <v>-6.8341469999999997</v>
+      </c>
+      <c r="J92">
+        <v>10036</v>
+      </c>
+      <c r="K92">
+        <v>965639376</v>
+      </c>
+      <c r="L92" t="s">
+        <v>331</v>
+      </c>
+      <c r="M92">
+        <v>2</v>
+      </c>
+      <c r="N92" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O92" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P92" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q92" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R92" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S92" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T92" t="s">
+        <v>37</v>
+      </c>
+      <c r="U92" t="s">
+        <v>48</v>
+      </c>
+      <c r="V92" t="s">
+        <v>105</v>
+      </c>
+      <c r="W92" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>304</v>
+      </c>
+      <c r="B93">
+        <v>10148</v>
+      </c>
+      <c r="C93" t="s">
+        <v>316</v>
+      </c>
+      <c r="D93" t="s">
+        <v>26</v>
+      </c>
+      <c r="E93" t="s">
+        <v>42</v>
+      </c>
+      <c r="F93" t="s">
+        <v>43</v>
+      </c>
+      <c r="G93" t="s">
+        <v>320</v>
+      </c>
+      <c r="H93">
+        <v>12.89515492</v>
+      </c>
+      <c r="I93">
+        <v>77.653300299999998</v>
+      </c>
+      <c r="J93">
+        <v>14022</v>
+      </c>
+      <c r="K93">
+        <v>779517433</v>
+      </c>
+      <c r="L93" t="s">
+        <v>332</v>
+      </c>
+      <c r="M93">
+        <v>3</v>
+      </c>
+      <c r="N93" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O93" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P93" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q93" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R93" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S93" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T93" t="s">
+        <v>37</v>
+      </c>
+      <c r="U93" t="s">
+        <v>38</v>
+      </c>
+      <c r="V93" t="s">
+        <v>48</v>
+      </c>
+      <c r="W93" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>304</v>
+      </c>
+      <c r="B94">
+        <v>10149</v>
+      </c>
+      <c r="C94" t="s">
+        <v>317</v>
+      </c>
+      <c r="D94" t="s">
+        <v>26</v>
+      </c>
+      <c r="E94" t="s">
+        <v>64</v>
+      </c>
+      <c r="F94" t="s">
+        <v>65</v>
+      </c>
+      <c r="G94" t="s">
+        <v>320</v>
+      </c>
+      <c r="H94">
+        <v>12.89515492</v>
+      </c>
+      <c r="I94">
+        <v>77.653300299999998</v>
+      </c>
+      <c r="J94">
+        <v>14000</v>
+      </c>
+      <c r="K94">
+        <v>937997757</v>
+      </c>
+      <c r="L94" t="s">
+        <v>66</v>
+      </c>
+      <c r="M94">
+        <v>2</v>
+      </c>
+      <c r="N94" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O94" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P94" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q94" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R94" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S94" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T94" t="s">
+        <v>37</v>
+      </c>
+      <c r="U94" t="s">
+        <v>38</v>
+      </c>
+      <c r="V94" t="s">
+        <v>48</v>
+      </c>
+      <c r="W94" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>304</v>
+      </c>
+      <c r="B95">
+        <v>10150</v>
+      </c>
+      <c r="C95" t="s">
+        <v>318</v>
+      </c>
+      <c r="D95" t="s">
+        <v>26</v>
+      </c>
+      <c r="E95" t="s">
+        <v>130</v>
+      </c>
+      <c r="F95" t="s">
+        <v>97</v>
+      </c>
+      <c r="G95" t="s">
+        <v>320</v>
+      </c>
+      <c r="H95">
+        <v>33.995612000000001</v>
+      </c>
+      <c r="I95">
+        <v>-6.8152809999999997</v>
+      </c>
+      <c r="J95">
+        <v>10190</v>
+      </c>
+      <c r="K95">
+        <v>803062069</v>
+      </c>
+      <c r="L95" t="s">
+        <v>333</v>
+      </c>
+      <c r="M95">
+        <v>2</v>
+      </c>
+      <c r="N95" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O95" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P95" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q95" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R95" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="S95" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="T95" t="s">
+        <v>37</v>
+      </c>
+      <c r="U95" t="s">
+        <v>48</v>
+      </c>
+      <c r="V95" t="s">
+        <v>111</v>
+      </c>
+      <c r="W95" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>304</v>
+      </c>
+      <c r="B96">
+        <v>10151</v>
+      </c>
+      <c r="C96" t="s">
+        <v>319</v>
+      </c>
+      <c r="D96" t="s">
+        <v>26</v>
+      </c>
+      <c r="E96" t="s">
+        <v>323</v>
+      </c>
+      <c r="F96" t="s">
+        <v>324</v>
+      </c>
+      <c r="G96" t="s">
+        <v>325</v>
+      </c>
+      <c r="H96">
+        <v>78.547799999999995</v>
+      </c>
+      <c r="I96">
+        <v>45.245600000000003</v>
+      </c>
+      <c r="J96">
+        <v>10114</v>
+      </c>
+      <c r="K96">
+        <v>9663089998</v>
+      </c>
+      <c r="L96" t="s">
+        <v>334</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="O96" s="6">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="P96" s="6">
+        <v>0.375</v>
+      </c>
+      <c r="Q96" s="6">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R96" s="6">
+        <v>0</v>
+      </c>
+      <c r="S96" s="6">
+        <v>0</v>
+      </c>
+      <c r="T96" t="s">
+        <v>335</v>
+      </c>
+      <c r="U96" t="s">
+        <v>48</v>
+      </c>
+      <c r="V96" t="s">
+        <v>336</v>
+      </c>
+      <c r="W96" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50CA5E7-C346-4A90-9CEB-D704FCEE522A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0E3D64-3BAE-4C71-86E1-BEFC8E6C3BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-12330" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="338">
   <si>
     <t>lang_code</t>
   </si>
@@ -1036,6 +1036,9 @@
   </si>
   <si>
     <t>CSB</t>
+  </si>
+  <si>
+    <t>UTO</t>
   </si>
 </sst>
 </file>
@@ -1126,9 +1129,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1166,7 +1169,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1272,7 +1275,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1414,7 +1417,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1423,33 +1426,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W96"/>
-  <sheetFormatPr defaultColWidth="11.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11.59765625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.26953125" customWidth="1"/>
-    <col min="2" max="2" width="10.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" customWidth="1"/>
-    <col min="4" max="4" width="13.08984375" customWidth="1"/>
-    <col min="5" max="5" width="29.1796875" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" customWidth="1"/>
-    <col min="8" max="8" width="8.6328125" customWidth="1"/>
-    <col min="9" max="9" width="10.08984375" customWidth="1"/>
-    <col min="10" max="10" width="13.7265625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" customWidth="1"/>
-    <col min="12" max="12" width="17.54296875" customWidth="1"/>
-    <col min="13" max="13" width="17.90625" customWidth="1"/>
-    <col min="14" max="14" width="14.90625" customWidth="1"/>
-    <col min="15" max="15" width="22.90625" customWidth="1"/>
-    <col min="16" max="16" width="17.1796875" customWidth="1"/>
-    <col min="17" max="18" width="16.36328125" customWidth="1"/>
-    <col min="19" max="19" width="15.6328125" customWidth="1"/>
+    <col min="1" max="1" width="10.265625" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.73046875" customWidth="1"/>
+    <col min="4" max="4" width="13.06640625" customWidth="1"/>
+    <col min="5" max="5" width="29.19921875" customWidth="1"/>
+    <col min="6" max="6" width="19.46484375" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" customWidth="1"/>
+    <col min="8" max="8" width="8.59765625" customWidth="1"/>
+    <col min="9" max="9" width="10.06640625" customWidth="1"/>
+    <col min="10" max="10" width="13.73046875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.53125" customWidth="1"/>
+    <col min="12" max="12" width="17.53125" customWidth="1"/>
+    <col min="13" max="13" width="17.9296875" customWidth="1"/>
+    <col min="14" max="14" width="14.9296875" customWidth="1"/>
+    <col min="15" max="15" width="22.9296875" customWidth="1"/>
+    <col min="16" max="16" width="17.19921875" customWidth="1"/>
+    <col min="17" max="18" width="16.33203125" customWidth="1"/>
+    <col min="19" max="19" width="15.59765625" customWidth="1"/>
     <col min="20" max="20" width="40" customWidth="1"/>
-    <col min="21" max="21" width="16.54296875" customWidth="1"/>
-    <col min="22" max="22" width="10.81640625" customWidth="1"/>
+    <col min="21" max="21" width="16.53125" customWidth="1"/>
+    <col min="22" max="22" width="10.796875" customWidth="1"/>
     <col min="23" max="23" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +1523,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1582,13 +1585,13 @@
         <v>38</v>
       </c>
       <c r="V2" t="s">
-        <v>30</v>
+        <v>337</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -1650,13 +1653,13 @@
         <v>38</v>
       </c>
       <c r="V3" t="s">
-        <v>30</v>
+        <v>337</v>
       </c>
       <c r="W3" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1727,7 +1730,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1798,7 +1801,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1869,7 +1872,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -1940,7 +1943,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -2011,7 +2014,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -2082,7 +2085,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -2153,7 +2156,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -2224,7 +2227,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2295,7 +2298,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -2366,7 +2369,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -2437,7 +2440,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -2508,7 +2511,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -2579,7 +2582,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2650,7 +2653,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2721,7 +2724,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -2792,7 +2795,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -2863,7 +2866,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -2934,7 +2937,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -3005,7 +3008,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3076,7 +3079,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -3147,7 +3150,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -3218,7 +3221,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -3289,7 +3292,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -3360,7 +3363,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -3431,7 +3434,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -3502,7 +3505,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -3573,7 +3576,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -3644,7 +3647,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -3715,7 +3718,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -3786,7 +3789,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>134</v>
       </c>
@@ -3848,13 +3851,13 @@
         <v>38</v>
       </c>
       <c r="V34" t="s">
-        <v>30</v>
+        <v>337</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>134</v>
       </c>
@@ -3925,7 +3928,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>134</v>
       </c>
@@ -3996,7 +3999,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>134</v>
       </c>
@@ -4067,7 +4070,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>134</v>
       </c>
@@ -4138,7 +4141,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>134</v>
       </c>
@@ -4209,7 +4212,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>134</v>
       </c>
@@ -4280,7 +4283,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>134</v>
       </c>
@@ -4351,7 +4354,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>134</v>
       </c>
@@ -4422,7 +4425,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>134</v>
       </c>
@@ -4493,7 +4496,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>134</v>
       </c>
@@ -4564,7 +4567,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>134</v>
       </c>
@@ -4635,7 +4638,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>134</v>
       </c>
@@ -4706,7 +4709,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>134</v>
       </c>
@@ -4777,7 +4780,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>134</v>
       </c>
@@ -4848,7 +4851,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>134</v>
       </c>
@@ -4919,7 +4922,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>191</v>
       </c>
@@ -4981,13 +4984,13 @@
         <v>38</v>
       </c>
       <c r="V50" t="s">
-        <v>30</v>
+        <v>337</v>
       </c>
       <c r="W50" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>191</v>
       </c>
@@ -5058,7 +5061,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>191</v>
       </c>
@@ -5129,7 +5132,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>191</v>
       </c>
@@ -5200,7 +5203,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>191</v>
       </c>
@@ -5271,7 +5274,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>191</v>
       </c>
@@ -5342,7 +5345,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>191</v>
       </c>
@@ -5413,7 +5416,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>191</v>
       </c>
@@ -5484,7 +5487,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>191</v>
       </c>
@@ -5555,7 +5558,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>191</v>
       </c>
@@ -5626,7 +5629,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>191</v>
       </c>
@@ -5697,7 +5700,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>191</v>
       </c>
@@ -5768,7 +5771,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>191</v>
       </c>
@@ -5839,7 +5842,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>191</v>
       </c>
@@ -5910,7 +5913,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>191</v>
       </c>
@@ -5981,7 +5984,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>191</v>
       </c>
@@ -6052,7 +6055,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>248</v>
       </c>
@@ -6114,13 +6117,13 @@
         <v>38</v>
       </c>
       <c r="V66" t="s">
-        <v>30</v>
+        <v>337</v>
       </c>
       <c r="W66" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>248</v>
       </c>
@@ -6191,7 +6194,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>248</v>
       </c>
@@ -6262,7 +6265,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>248</v>
       </c>
@@ -6333,7 +6336,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>248</v>
       </c>
@@ -6404,7 +6407,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>248</v>
       </c>
@@ -6475,7 +6478,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>248</v>
       </c>
@@ -6546,7 +6549,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>248</v>
       </c>
@@ -6617,7 +6620,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>248</v>
       </c>
@@ -6688,7 +6691,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>248</v>
       </c>
@@ -6759,7 +6762,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>248</v>
       </c>
@@ -6830,7 +6833,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>248</v>
       </c>
@@ -6901,7 +6904,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>248</v>
       </c>
@@ -6972,7 +6975,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>248</v>
       </c>
@@ -7043,7 +7046,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>248</v>
       </c>
@@ -7114,7 +7117,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>248</v>
       </c>
@@ -7185,7 +7188,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>304</v>
       </c>
@@ -7256,7 +7259,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>304</v>
       </c>
@@ -7327,7 +7330,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>304</v>
       </c>
@@ -7398,7 +7401,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>304</v>
       </c>
@@ -7469,7 +7472,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>304</v>
       </c>
@@ -7540,7 +7543,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>304</v>
       </c>
@@ -7611,7 +7614,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>304</v>
       </c>
@@ -7682,7 +7685,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>304</v>
       </c>
@@ -7753,7 +7756,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>304</v>
       </c>
@@ -7824,7 +7827,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>304</v>
       </c>
@@ -7895,7 +7898,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>304</v>
       </c>
@@ -7966,7 +7969,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>304</v>
       </c>
@@ -8037,7 +8040,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>304</v>
       </c>
@@ -8108,7 +8111,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>304</v>
       </c>
@@ -8179,7 +8182,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>304</v>
       </c>

--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0E3D64-3BAE-4C71-86E1-BEFC8E6C3BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D88D771-D774-495B-8A21-C2B74EAC5491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-12330" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1553" uniqueCount="337">
   <si>
     <t>lang_code</t>
   </si>
@@ -115,9 +115,6 @@
   </si>
   <si>
     <t>MyCountry</t>
-  </si>
-  <si>
-    <t>MOR</t>
   </si>
   <si>
     <t>24:00:00</t>
@@ -1552,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>30</v>
+        <v>336</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1561,39 +1558,39 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
         <v>31</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>32</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>33</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>34</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>35</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>36</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>37</v>
       </c>
-      <c r="U2" t="s">
-        <v>38</v>
-      </c>
       <c r="V2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>24</v>
@@ -1620,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
+        <v>336</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -1629,34 +1626,34 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" t="s">
         <v>31</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>32</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>34</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>35</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>36</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>37</v>
       </c>
-      <c r="U3" t="s">
-        <v>38</v>
-      </c>
       <c r="V3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.45">
@@ -1667,16 +1664,16 @@
         <v>10001</v>
       </c>
       <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
         <v>41</v>
       </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>42</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
       </c>
       <c r="G4" t="s">
         <v>29</v>
@@ -1694,63 +1691,63 @@
         <v>779517433</v>
       </c>
       <c r="L4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M4">
         <v>3</v>
       </c>
       <c r="N4" t="s">
+        <v>44</v>
+      </c>
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" t="s">
         <v>45</v>
       </c>
-      <c r="O4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>46</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V4" t="s">
         <v>47</v>
       </c>
-      <c r="R4" t="s">
-        <v>35</v>
-      </c>
-      <c r="S4" t="s">
-        <v>36</v>
-      </c>
-      <c r="T4" t="s">
-        <v>37</v>
-      </c>
-      <c r="U4" t="s">
-        <v>38</v>
-      </c>
-      <c r="V4" t="s">
-        <v>48</v>
-      </c>
       <c r="W4" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="1">
         <v>10001</v>
       </c>
       <c r="C5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
         <v>49</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" t="s">
-        <v>50</v>
       </c>
       <c r="H5">
         <v>34.521169999999998</v>
@@ -1765,40 +1762,40 @@
         <v>993556086</v>
       </c>
       <c r="L5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M5">
         <v>3</v>
       </c>
       <c r="N5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O5" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" t="s">
         <v>45</v>
       </c>
-      <c r="O5" t="s">
-        <v>32</v>
-      </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>46</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
+        <v>34</v>
+      </c>
+      <c r="S5" t="s">
+        <v>35</v>
+      </c>
+      <c r="T5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U5" t="s">
+        <v>37</v>
+      </c>
+      <c r="V5" t="s">
         <v>47</v>
       </c>
-      <c r="R5" t="s">
-        <v>35</v>
-      </c>
-      <c r="S5" t="s">
-        <v>36</v>
-      </c>
-      <c r="T5" t="s">
-        <v>51</v>
-      </c>
-      <c r="U5" t="s">
-        <v>38</v>
-      </c>
-      <c r="V5" t="s">
-        <v>48</v>
-      </c>
       <c r="W5" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
@@ -1809,16 +1806,16 @@
         <v>10002</v>
       </c>
       <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
         <v>52</v>
       </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>53</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
       </c>
       <c r="G6" t="s">
         <v>29</v>
@@ -1836,63 +1833,63 @@
         <v>753476995</v>
       </c>
       <c r="L6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M6">
         <v>2</v>
       </c>
       <c r="N6" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" t="s">
         <v>45</v>
       </c>
-      <c r="O6" t="s">
-        <v>32</v>
-      </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>46</v>
       </c>
-      <c r="Q6" t="s">
-        <v>47</v>
-      </c>
       <c r="R6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S6" t="s">
         <v>35</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>36</v>
       </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
         <v>37</v>
       </c>
-      <c r="U6" t="s">
-        <v>38</v>
-      </c>
       <c r="V6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="1">
         <v>10002</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
       </c>
       <c r="E7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s">
         <v>53</v>
       </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H7">
         <v>34.360207000000003</v>
@@ -1907,40 +1904,40 @@
         <v>984996886</v>
       </c>
       <c r="L7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M7">
         <v>2</v>
       </c>
       <c r="N7" t="s">
+        <v>44</v>
+      </c>
+      <c r="O7" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" t="s">
         <v>45</v>
       </c>
-      <c r="O7" t="s">
-        <v>32</v>
-      </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>46</v>
       </c>
-      <c r="Q7" t="s">
-        <v>47</v>
-      </c>
       <c r="R7" t="s">
+        <v>34</v>
+      </c>
+      <c r="S7" t="s">
         <v>35</v>
       </c>
-      <c r="S7" t="s">
-        <v>36</v>
-      </c>
       <c r="T7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
@@ -1951,16 +1948,16 @@
         <v>10003</v>
       </c>
       <c r="C8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
         <v>57</v>
       </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>58</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>
@@ -1978,63 +1975,63 @@
         <v>734239083</v>
       </c>
       <c r="L8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M8">
         <v>4</v>
       </c>
       <c r="N8" t="s">
+        <v>44</v>
+      </c>
+      <c r="O8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" t="s">
         <v>45</v>
       </c>
-      <c r="O8" t="s">
-        <v>32</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>46</v>
       </c>
-      <c r="Q8" t="s">
-        <v>47</v>
-      </c>
       <c r="R8" t="s">
+        <v>34</v>
+      </c>
+      <c r="S8" t="s">
         <v>35</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>36</v>
       </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
         <v>37</v>
       </c>
-      <c r="U8" t="s">
-        <v>38</v>
-      </c>
       <c r="V8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1">
         <v>10003</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H9">
         <v>34.405692000000002</v>
@@ -2049,40 +2046,40 @@
         <v>675470523</v>
       </c>
       <c r="L9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M9">
         <v>4</v>
       </c>
       <c r="N9" t="s">
+        <v>44</v>
+      </c>
+      <c r="O9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" t="s">
         <v>45</v>
       </c>
-      <c r="O9" t="s">
-        <v>32</v>
-      </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>46</v>
       </c>
-      <c r="Q9" t="s">
-        <v>47</v>
-      </c>
       <c r="R9" t="s">
+        <v>34</v>
+      </c>
+      <c r="S9" t="s">
         <v>35</v>
       </c>
-      <c r="S9" t="s">
-        <v>36</v>
-      </c>
       <c r="T9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
@@ -2093,16 +2090,16 @@
         <v>10004</v>
       </c>
       <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
         <v>63</v>
       </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>64</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
@@ -2120,63 +2117,63 @@
         <v>937997757</v>
       </c>
       <c r="L10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M10">
         <v>2</v>
       </c>
       <c r="N10" t="s">
+        <v>44</v>
+      </c>
+      <c r="O10" t="s">
+        <v>31</v>
+      </c>
+      <c r="P10" t="s">
         <v>45</v>
       </c>
-      <c r="O10" t="s">
-        <v>32</v>
-      </c>
-      <c r="P10" t="s">
+      <c r="Q10" t="s">
         <v>46</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
+        <v>34</v>
+      </c>
+      <c r="S10" t="s">
+        <v>35</v>
+      </c>
+      <c r="T10" t="s">
+        <v>36</v>
+      </c>
+      <c r="U10" t="s">
+        <v>37</v>
+      </c>
+      <c r="V10" t="s">
         <v>47</v>
       </c>
-      <c r="R10" t="s">
-        <v>35</v>
-      </c>
-      <c r="S10" t="s">
-        <v>36</v>
-      </c>
-      <c r="T10" t="s">
-        <v>37</v>
-      </c>
-      <c r="U10" t="s">
-        <v>38</v>
-      </c>
-      <c r="V10" t="s">
-        <v>48</v>
-      </c>
       <c r="W10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="1">
         <v>10004</v>
       </c>
       <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
         <v>67</v>
       </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H11">
         <v>34.287878999999997</v>
@@ -2191,40 +2188,40 @@
         <v>852492117</v>
       </c>
       <c r="L11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M11">
         <v>2</v>
       </c>
       <c r="N11" t="s">
+        <v>44</v>
+      </c>
+      <c r="O11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P11" t="s">
         <v>45</v>
       </c>
-      <c r="O11" t="s">
-        <v>32</v>
-      </c>
-      <c r="P11" t="s">
+      <c r="Q11" t="s">
         <v>46</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
+        <v>34</v>
+      </c>
+      <c r="S11" t="s">
+        <v>35</v>
+      </c>
+      <c r="T11" t="s">
+        <v>50</v>
+      </c>
+      <c r="U11" t="s">
+        <v>37</v>
+      </c>
+      <c r="V11" t="s">
         <v>47</v>
       </c>
-      <c r="R11" t="s">
-        <v>35</v>
-      </c>
-      <c r="S11" t="s">
-        <v>36</v>
-      </c>
-      <c r="T11" t="s">
-        <v>51</v>
-      </c>
-      <c r="U11" t="s">
-        <v>38</v>
-      </c>
-      <c r="V11" t="s">
-        <v>48</v>
-      </c>
       <c r="W11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
@@ -2235,19 +2232,19 @@
         <v>10005</v>
       </c>
       <c r="C12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
         <v>70</v>
       </c>
-      <c r="D12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" t="s">
-        <v>71</v>
-      </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H12">
         <v>34.256413999999999</v>
@@ -2262,63 +2259,63 @@
         <v>887311749</v>
       </c>
       <c r="L12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12" t="s">
+        <v>44</v>
+      </c>
+      <c r="O12" t="s">
+        <v>31</v>
+      </c>
+      <c r="P12" t="s">
         <v>45</v>
       </c>
-      <c r="O12" t="s">
-        <v>32</v>
-      </c>
-      <c r="P12" t="s">
+      <c r="Q12" t="s">
         <v>46</v>
       </c>
-      <c r="Q12" t="s">
-        <v>47</v>
-      </c>
       <c r="R12" t="s">
+        <v>34</v>
+      </c>
+      <c r="S12" t="s">
         <v>35</v>
       </c>
-      <c r="S12" t="s">
+      <c r="T12" t="s">
         <v>36</v>
       </c>
-      <c r="T12" t="s">
+      <c r="U12" t="s">
         <v>37</v>
       </c>
-      <c r="U12" t="s">
-        <v>38</v>
-      </c>
       <c r="V12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1">
         <v>10005</v>
       </c>
       <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" t="s">
         <v>74</v>
       </c>
-      <c r="D13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" t="s">
-        <v>75</v>
-      </c>
       <c r="F13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H13">
         <v>34.256413999999999</v>
@@ -2333,40 +2330,40 @@
         <v>658302699</v>
       </c>
       <c r="L13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13" t="s">
+        <v>44</v>
+      </c>
+      <c r="O13" t="s">
+        <v>31</v>
+      </c>
+      <c r="P13" t="s">
         <v>45</v>
       </c>
-      <c r="O13" t="s">
-        <v>32</v>
-      </c>
-      <c r="P13" t="s">
+      <c r="Q13" t="s">
         <v>46</v>
       </c>
-      <c r="Q13" t="s">
-        <v>47</v>
-      </c>
       <c r="R13" t="s">
+        <v>34</v>
+      </c>
+      <c r="S13" t="s">
         <v>35</v>
       </c>
-      <c r="S13" t="s">
-        <v>36</v>
-      </c>
       <c r="T13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
@@ -2377,19 +2374,19 @@
         <v>10006</v>
       </c>
       <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
         <v>76</v>
       </c>
-      <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" t="s">
-        <v>77</v>
-      </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H14">
         <v>34.262476999999997</v>
@@ -2404,63 +2401,63 @@
         <v>915790305</v>
       </c>
       <c r="L14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M14">
         <v>5</v>
       </c>
       <c r="N14" t="s">
+        <v>44</v>
+      </c>
+      <c r="O14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P14" t="s">
         <v>45</v>
       </c>
-      <c r="O14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P14" t="s">
+      <c r="Q14" t="s">
         <v>46</v>
       </c>
-      <c r="Q14" t="s">
-        <v>47</v>
-      </c>
       <c r="R14" t="s">
+        <v>34</v>
+      </c>
+      <c r="S14" t="s">
         <v>35</v>
       </c>
-      <c r="S14" t="s">
+      <c r="T14" t="s">
         <v>36</v>
       </c>
-      <c r="T14" t="s">
+      <c r="U14" t="s">
         <v>37</v>
       </c>
-      <c r="U14" t="s">
-        <v>38</v>
-      </c>
       <c r="V14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1">
         <v>10006</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H15">
         <v>34.262476999999997</v>
@@ -2475,40 +2472,40 @@
         <v>888439793</v>
       </c>
       <c r="L15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M15">
         <v>5</v>
       </c>
       <c r="N15" t="s">
+        <v>44</v>
+      </c>
+      <c r="O15" t="s">
+        <v>31</v>
+      </c>
+      <c r="P15" t="s">
         <v>45</v>
       </c>
-      <c r="O15" t="s">
-        <v>32</v>
-      </c>
-      <c r="P15" t="s">
+      <c r="Q15" t="s">
         <v>46</v>
       </c>
-      <c r="Q15" t="s">
-        <v>47</v>
-      </c>
       <c r="R15" t="s">
+        <v>34</v>
+      </c>
+      <c r="S15" t="s">
         <v>35</v>
       </c>
-      <c r="S15" t="s">
-        <v>36</v>
-      </c>
       <c r="T15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.45">
@@ -2519,16 +2516,16 @@
         <v>10007</v>
       </c>
       <c r="C16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" t="s">
         <v>81</v>
       </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>82</v>
-      </c>
-      <c r="F16" t="s">
-        <v>83</v>
       </c>
       <c r="G16" t="s">
         <v>29</v>
@@ -2546,63 +2543,63 @@
         <v>811552880</v>
       </c>
       <c r="L16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M16">
         <v>2</v>
       </c>
       <c r="N16" t="s">
+        <v>44</v>
+      </c>
+      <c r="O16" t="s">
+        <v>31</v>
+      </c>
+      <c r="P16" t="s">
         <v>45</v>
       </c>
-      <c r="O16" t="s">
-        <v>32</v>
-      </c>
-      <c r="P16" t="s">
+      <c r="Q16" t="s">
         <v>46</v>
       </c>
-      <c r="Q16" t="s">
-        <v>47</v>
-      </c>
       <c r="R16" t="s">
+        <v>34</v>
+      </c>
+      <c r="S16" t="s">
         <v>35</v>
       </c>
-      <c r="S16" t="s">
+      <c r="T16" t="s">
         <v>36</v>
       </c>
-      <c r="T16" t="s">
+      <c r="U16" t="s">
         <v>37</v>
       </c>
-      <c r="U16" t="s">
-        <v>38</v>
-      </c>
       <c r="V16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1">
         <v>10007</v>
       </c>
       <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" t="s">
         <v>86</v>
       </c>
-      <c r="D17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" t="s">
-        <v>87</v>
-      </c>
       <c r="F17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H17">
         <v>34.192861000000001</v>
@@ -2617,40 +2614,40 @@
         <v>753640112</v>
       </c>
       <c r="L17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M17">
         <v>2</v>
       </c>
       <c r="N17" t="s">
+        <v>44</v>
+      </c>
+      <c r="O17" t="s">
+        <v>31</v>
+      </c>
+      <c r="P17" t="s">
         <v>45</v>
       </c>
-      <c r="O17" t="s">
-        <v>32</v>
-      </c>
-      <c r="P17" t="s">
+      <c r="Q17" t="s">
         <v>46</v>
       </c>
-      <c r="Q17" t="s">
-        <v>47</v>
-      </c>
       <c r="R17" t="s">
+        <v>34</v>
+      </c>
+      <c r="S17" t="s">
         <v>35</v>
       </c>
-      <c r="S17" t="s">
-        <v>36</v>
-      </c>
       <c r="T17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.45">
@@ -2661,16 +2658,16 @@
         <v>10008</v>
       </c>
       <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" t="s">
         <v>88</v>
       </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>89</v>
-      </c>
-      <c r="F18" t="s">
-        <v>90</v>
       </c>
       <c r="G18" t="s">
         <v>29</v>
@@ -2688,63 +2685,63 @@
         <v>695325692</v>
       </c>
       <c r="L18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M18">
         <v>2</v>
       </c>
       <c r="N18" t="s">
+        <v>44</v>
+      </c>
+      <c r="O18" t="s">
+        <v>31</v>
+      </c>
+      <c r="P18" t="s">
         <v>45</v>
       </c>
-      <c r="O18" t="s">
-        <v>32</v>
-      </c>
-      <c r="P18" t="s">
+      <c r="Q18" t="s">
         <v>46</v>
       </c>
-      <c r="Q18" t="s">
-        <v>47</v>
-      </c>
       <c r="R18" t="s">
+        <v>34</v>
+      </c>
+      <c r="S18" t="s">
         <v>35</v>
       </c>
-      <c r="S18" t="s">
+      <c r="T18" t="s">
         <v>36</v>
       </c>
-      <c r="T18" t="s">
+      <c r="U18" t="s">
         <v>37</v>
       </c>
-      <c r="U18" t="s">
-        <v>38</v>
-      </c>
       <c r="V18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="1">
         <v>10008</v>
       </c>
       <c r="C19" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" t="s">
         <v>93</v>
       </c>
-      <c r="D19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" t="s">
-        <v>94</v>
-      </c>
       <c r="F19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H19">
         <v>34.522413999999998</v>
@@ -2759,40 +2756,40 @@
         <v>862899075</v>
       </c>
       <c r="L19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M19">
         <v>2</v>
       </c>
       <c r="N19" t="s">
+        <v>44</v>
+      </c>
+      <c r="O19" t="s">
+        <v>31</v>
+      </c>
+      <c r="P19" t="s">
         <v>45</v>
       </c>
-      <c r="O19" t="s">
-        <v>32</v>
-      </c>
-      <c r="P19" t="s">
+      <c r="Q19" t="s">
         <v>46</v>
       </c>
-      <c r="Q19" t="s">
-        <v>47</v>
-      </c>
       <c r="R19" t="s">
+        <v>34</v>
+      </c>
+      <c r="S19" t="s">
         <v>35</v>
       </c>
-      <c r="S19" t="s">
-        <v>36</v>
-      </c>
       <c r="T19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="V19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.45">
@@ -2803,16 +2800,16 @@
         <v>10009</v>
       </c>
       <c r="C20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" t="s">
         <v>95</v>
       </c>
-      <c r="D20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>96</v>
-      </c>
-      <c r="F20" t="s">
-        <v>97</v>
       </c>
       <c r="G20" t="s">
         <v>29</v>
@@ -2830,63 +2827,63 @@
         <v>745360421</v>
       </c>
       <c r="L20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M20">
         <v>2</v>
       </c>
       <c r="N20" t="s">
+        <v>44</v>
+      </c>
+      <c r="O20" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" t="s">
         <v>45</v>
       </c>
-      <c r="O20" t="s">
-        <v>32</v>
-      </c>
-      <c r="P20" t="s">
+      <c r="Q20" t="s">
         <v>46</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
+        <v>34</v>
+      </c>
+      <c r="S20" t="s">
+        <v>35</v>
+      </c>
+      <c r="T20" t="s">
+        <v>36</v>
+      </c>
+      <c r="U20" t="s">
         <v>47</v>
       </c>
-      <c r="R20" t="s">
-        <v>35</v>
-      </c>
-      <c r="S20" t="s">
-        <v>36</v>
-      </c>
-      <c r="T20" t="s">
-        <v>37</v>
-      </c>
-      <c r="U20" t="s">
-        <v>48</v>
-      </c>
       <c r="V20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="1">
         <v>10009</v>
       </c>
       <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" t="s">
         <v>100</v>
       </c>
-      <c r="D21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" t="s">
-        <v>101</v>
-      </c>
       <c r="F21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H21">
         <v>33.998232000000002</v>
@@ -2901,40 +2898,40 @@
         <v>676186831</v>
       </c>
       <c r="L21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M21">
         <v>2</v>
       </c>
       <c r="N21" t="s">
+        <v>44</v>
+      </c>
+      <c r="O21" t="s">
+        <v>31</v>
+      </c>
+      <c r="P21" t="s">
         <v>45</v>
       </c>
-      <c r="O21" t="s">
-        <v>32</v>
-      </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>46</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
+        <v>34</v>
+      </c>
+      <c r="S21" t="s">
+        <v>35</v>
+      </c>
+      <c r="T21" t="s">
+        <v>50</v>
+      </c>
+      <c r="U21" t="s">
         <v>47</v>
       </c>
-      <c r="R21" t="s">
-        <v>35</v>
-      </c>
-      <c r="S21" t="s">
-        <v>36</v>
-      </c>
-      <c r="T21" t="s">
-        <v>51</v>
-      </c>
-      <c r="U21" t="s">
-        <v>48</v>
-      </c>
       <c r="V21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.45">
@@ -2945,16 +2942,16 @@
         <v>10010</v>
       </c>
       <c r="C22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" t="s">
         <v>102</v>
       </c>
-      <c r="D22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" t="s">
-        <v>103</v>
-      </c>
       <c r="F22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G22" t="s">
         <v>29</v>
@@ -2972,63 +2969,63 @@
         <v>766074745</v>
       </c>
       <c r="L22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M22">
         <v>2</v>
       </c>
       <c r="N22" t="s">
+        <v>44</v>
+      </c>
+      <c r="O22" t="s">
+        <v>31</v>
+      </c>
+      <c r="P22" t="s">
         <v>45</v>
       </c>
-      <c r="O22" t="s">
-        <v>32</v>
-      </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>46</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
+        <v>34</v>
+      </c>
+      <c r="S22" t="s">
+        <v>35</v>
+      </c>
+      <c r="T22" t="s">
+        <v>36</v>
+      </c>
+      <c r="U22" t="s">
         <v>47</v>
       </c>
-      <c r="R22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S22" t="s">
-        <v>36</v>
-      </c>
-      <c r="T22" t="s">
-        <v>37</v>
-      </c>
-      <c r="U22" t="s">
-        <v>48</v>
-      </c>
       <c r="V22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="1">
         <v>10010</v>
       </c>
       <c r="C23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" t="s">
         <v>106</v>
       </c>
-      <c r="D23" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" t="s">
-        <v>107</v>
-      </c>
       <c r="F23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H23">
         <v>34.017502</v>
@@ -3043,40 +3040,40 @@
         <v>773606891</v>
       </c>
       <c r="L23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M23">
         <v>2</v>
       </c>
       <c r="N23" t="s">
+        <v>44</v>
+      </c>
+      <c r="O23" t="s">
+        <v>31</v>
+      </c>
+      <c r="P23" t="s">
         <v>45</v>
       </c>
-      <c r="O23" t="s">
-        <v>32</v>
-      </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>46</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
+        <v>34</v>
+      </c>
+      <c r="S23" t="s">
+        <v>35</v>
+      </c>
+      <c r="T23" t="s">
+        <v>50</v>
+      </c>
+      <c r="U23" t="s">
         <v>47</v>
       </c>
-      <c r="R23" t="s">
-        <v>35</v>
-      </c>
-      <c r="S23" t="s">
-        <v>36</v>
-      </c>
-      <c r="T23" t="s">
-        <v>51</v>
-      </c>
-      <c r="U23" t="s">
-        <v>48</v>
-      </c>
       <c r="V23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.45">
@@ -3087,16 +3084,16 @@
         <v>10011</v>
       </c>
       <c r="C24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
         <v>108</v>
       </c>
-      <c r="D24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" t="s">
-        <v>109</v>
-      </c>
       <c r="F24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G24" t="s">
         <v>29</v>
@@ -3114,63 +3111,63 @@
         <v>787248921</v>
       </c>
       <c r="L24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M24">
         <v>2</v>
       </c>
       <c r="N24" t="s">
+        <v>44</v>
+      </c>
+      <c r="O24" t="s">
+        <v>31</v>
+      </c>
+      <c r="P24" t="s">
         <v>45</v>
       </c>
-      <c r="O24" t="s">
-        <v>32</v>
-      </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>46</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
+        <v>34</v>
+      </c>
+      <c r="S24" t="s">
+        <v>35</v>
+      </c>
+      <c r="T24" t="s">
+        <v>36</v>
+      </c>
+      <c r="U24" t="s">
         <v>47</v>
       </c>
-      <c r="R24" t="s">
-        <v>35</v>
-      </c>
-      <c r="S24" t="s">
-        <v>36</v>
-      </c>
-      <c r="T24" t="s">
-        <v>37</v>
-      </c>
-      <c r="U24" t="s">
-        <v>48</v>
-      </c>
       <c r="V24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="1">
         <v>10011</v>
       </c>
       <c r="C25" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" t="s">
         <v>112</v>
       </c>
-      <c r="D25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25" t="s">
-        <v>113</v>
-      </c>
       <c r="F25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H25">
         <v>33.986607999999997</v>
@@ -3185,40 +3182,40 @@
         <v>878691008</v>
       </c>
       <c r="L25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M25">
         <v>2</v>
       </c>
       <c r="N25" t="s">
+        <v>44</v>
+      </c>
+      <c r="O25" t="s">
+        <v>31</v>
+      </c>
+      <c r="P25" t="s">
         <v>45</v>
       </c>
-      <c r="O25" t="s">
-        <v>32</v>
-      </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>46</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
+        <v>34</v>
+      </c>
+      <c r="S25" t="s">
+        <v>35</v>
+      </c>
+      <c r="T25" t="s">
+        <v>50</v>
+      </c>
+      <c r="U25" t="s">
         <v>47</v>
       </c>
-      <c r="R25" t="s">
-        <v>35</v>
-      </c>
-      <c r="S25" t="s">
-        <v>36</v>
-      </c>
-      <c r="T25" t="s">
-        <v>51</v>
-      </c>
-      <c r="U25" t="s">
-        <v>48</v>
-      </c>
       <c r="V25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.45">
@@ -3229,16 +3226,16 @@
         <v>10012</v>
       </c>
       <c r="C26" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s">
         <v>114</v>
       </c>
-      <c r="D26" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" t="s">
-        <v>115</v>
-      </c>
       <c r="F26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G26" t="s">
         <v>29</v>
@@ -3256,63 +3253,63 @@
         <v>838412388</v>
       </c>
       <c r="L26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M26">
         <v>2</v>
       </c>
       <c r="N26" t="s">
+        <v>44</v>
+      </c>
+      <c r="O26" t="s">
+        <v>31</v>
+      </c>
+      <c r="P26" t="s">
         <v>45</v>
       </c>
-      <c r="O26" t="s">
-        <v>32</v>
-      </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>46</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
+        <v>34</v>
+      </c>
+      <c r="S26" t="s">
+        <v>35</v>
+      </c>
+      <c r="T26" t="s">
+        <v>36</v>
+      </c>
+      <c r="U26" t="s">
         <v>47</v>
       </c>
-      <c r="R26" t="s">
-        <v>35</v>
-      </c>
-      <c r="S26" t="s">
-        <v>36</v>
-      </c>
-      <c r="T26" t="s">
-        <v>37</v>
-      </c>
-      <c r="U26" t="s">
-        <v>48</v>
-      </c>
       <c r="V26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="1">
         <v>10012</v>
       </c>
       <c r="C27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" t="s">
         <v>117</v>
       </c>
-      <c r="D27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" t="s">
-        <v>118</v>
-      </c>
       <c r="F27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H27">
         <v>33.978102999999997</v>
@@ -3327,40 +3324,40 @@
         <v>719952201</v>
       </c>
       <c r="L27" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M27">
         <v>2</v>
       </c>
       <c r="N27" t="s">
+        <v>44</v>
+      </c>
+      <c r="O27" t="s">
+        <v>31</v>
+      </c>
+      <c r="P27" t="s">
         <v>45</v>
       </c>
-      <c r="O27" t="s">
-        <v>32</v>
-      </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>46</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
+        <v>34</v>
+      </c>
+      <c r="S27" t="s">
+        <v>35</v>
+      </c>
+      <c r="T27" t="s">
+        <v>50</v>
+      </c>
+      <c r="U27" t="s">
         <v>47</v>
       </c>
-      <c r="R27" t="s">
-        <v>35</v>
-      </c>
-      <c r="S27" t="s">
-        <v>36</v>
-      </c>
-      <c r="T27" t="s">
-        <v>51</v>
-      </c>
-      <c r="U27" t="s">
-        <v>48</v>
-      </c>
       <c r="V27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.45">
@@ -3371,16 +3368,16 @@
         <v>10013</v>
       </c>
       <c r="C28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="s">
         <v>119</v>
       </c>
-      <c r="D28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" t="s">
-        <v>120</v>
-      </c>
       <c r="F28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
         <v>29</v>
@@ -3398,63 +3395,63 @@
         <v>751913644</v>
       </c>
       <c r="L28" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M28">
         <v>2</v>
       </c>
       <c r="N28" t="s">
+        <v>44</v>
+      </c>
+      <c r="O28" t="s">
+        <v>31</v>
+      </c>
+      <c r="P28" t="s">
         <v>45</v>
       </c>
-      <c r="O28" t="s">
-        <v>32</v>
-      </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>46</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" t="s">
+        <v>34</v>
+      </c>
+      <c r="S28" t="s">
+        <v>35</v>
+      </c>
+      <c r="T28" t="s">
+        <v>36</v>
+      </c>
+      <c r="U28" t="s">
         <v>47</v>
       </c>
-      <c r="R28" t="s">
-        <v>35</v>
-      </c>
-      <c r="S28" t="s">
-        <v>36</v>
-      </c>
-      <c r="T28" t="s">
-        <v>37</v>
-      </c>
-      <c r="U28" t="s">
-        <v>48</v>
-      </c>
       <c r="V28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="1">
         <v>10013</v>
       </c>
       <c r="C29" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" t="s">
         <v>122</v>
       </c>
-      <c r="D29" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29" t="s">
-        <v>123</v>
-      </c>
       <c r="F29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H29">
         <v>33.953930999999997</v>
@@ -3469,40 +3466,40 @@
         <v>956537434</v>
       </c>
       <c r="L29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M29">
         <v>2</v>
       </c>
       <c r="N29" t="s">
+        <v>44</v>
+      </c>
+      <c r="O29" t="s">
+        <v>31</v>
+      </c>
+      <c r="P29" t="s">
         <v>45</v>
       </c>
-      <c r="O29" t="s">
-        <v>32</v>
-      </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>46</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
+        <v>34</v>
+      </c>
+      <c r="S29" t="s">
+        <v>35</v>
+      </c>
+      <c r="T29" t="s">
+        <v>50</v>
+      </c>
+      <c r="U29" t="s">
         <v>47</v>
       </c>
-      <c r="R29" t="s">
-        <v>35</v>
-      </c>
-      <c r="S29" t="s">
-        <v>36</v>
-      </c>
-      <c r="T29" t="s">
-        <v>51</v>
-      </c>
-      <c r="U29" t="s">
-        <v>48</v>
-      </c>
       <c r="V29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.45">
@@ -3513,16 +3510,16 @@
         <v>10014</v>
       </c>
       <c r="C30" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
         <v>124</v>
       </c>
-      <c r="D30" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" t="s">
-        <v>125</v>
-      </c>
       <c r="F30" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G30" t="s">
         <v>29</v>
@@ -3540,63 +3537,63 @@
         <v>965639376</v>
       </c>
       <c r="L30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M30">
         <v>2</v>
       </c>
       <c r="N30" t="s">
+        <v>44</v>
+      </c>
+      <c r="O30" t="s">
+        <v>31</v>
+      </c>
+      <c r="P30" t="s">
         <v>45</v>
       </c>
-      <c r="O30" t="s">
-        <v>32</v>
-      </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
         <v>46</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="R30" t="s">
+        <v>34</v>
+      </c>
+      <c r="S30" t="s">
+        <v>35</v>
+      </c>
+      <c r="T30" t="s">
+        <v>36</v>
+      </c>
+      <c r="U30" t="s">
         <v>47</v>
       </c>
-      <c r="R30" t="s">
-        <v>35</v>
-      </c>
-      <c r="S30" t="s">
-        <v>36</v>
-      </c>
-      <c r="T30" t="s">
-        <v>37</v>
-      </c>
-      <c r="U30" t="s">
-        <v>48</v>
-      </c>
       <c r="V30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1">
         <v>10014</v>
       </c>
       <c r="C31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" t="s">
         <v>127</v>
       </c>
-      <c r="D31" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" t="s">
-        <v>128</v>
-      </c>
       <c r="F31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H31">
         <v>34.027757000000001</v>
@@ -3611,40 +3608,40 @@
         <v>781039430</v>
       </c>
       <c r="L31" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M31">
         <v>2</v>
       </c>
       <c r="N31" t="s">
+        <v>44</v>
+      </c>
+      <c r="O31" t="s">
+        <v>31</v>
+      </c>
+      <c r="P31" t="s">
         <v>45</v>
       </c>
-      <c r="O31" t="s">
-        <v>32</v>
-      </c>
-      <c r="P31" t="s">
+      <c r="Q31" t="s">
         <v>46</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="R31" t="s">
+        <v>34</v>
+      </c>
+      <c r="S31" t="s">
+        <v>35</v>
+      </c>
+      <c r="T31" t="s">
+        <v>50</v>
+      </c>
+      <c r="U31" t="s">
         <v>47</v>
       </c>
-      <c r="R31" t="s">
-        <v>35</v>
-      </c>
-      <c r="S31" t="s">
-        <v>36</v>
-      </c>
-      <c r="T31" t="s">
-        <v>51</v>
-      </c>
-      <c r="U31" t="s">
-        <v>48</v>
-      </c>
       <c r="V31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.45">
@@ -3655,16 +3652,16 @@
         <v>10015</v>
       </c>
       <c r="C32" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" t="s">
         <v>129</v>
       </c>
-      <c r="D32" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" t="s">
-        <v>130</v>
-      </c>
       <c r="F32" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G32" t="s">
         <v>29</v>
@@ -3682,63 +3679,63 @@
         <v>803062069</v>
       </c>
       <c r="L32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M32">
         <v>2</v>
       </c>
       <c r="N32" t="s">
+        <v>44</v>
+      </c>
+      <c r="O32" t="s">
+        <v>31</v>
+      </c>
+      <c r="P32" t="s">
         <v>45</v>
       </c>
-      <c r="O32" t="s">
-        <v>32</v>
-      </c>
-      <c r="P32" t="s">
+      <c r="Q32" t="s">
         <v>46</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="R32" t="s">
+        <v>34</v>
+      </c>
+      <c r="S32" t="s">
+        <v>35</v>
+      </c>
+      <c r="T32" t="s">
+        <v>36</v>
+      </c>
+      <c r="U32" t="s">
         <v>47</v>
       </c>
-      <c r="R32" t="s">
-        <v>35</v>
-      </c>
-      <c r="S32" t="s">
-        <v>36</v>
-      </c>
-      <c r="T32" t="s">
-        <v>37</v>
-      </c>
-      <c r="U32" t="s">
-        <v>48</v>
-      </c>
       <c r="V32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1">
         <v>10015</v>
       </c>
       <c r="C33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" t="s">
         <v>132</v>
       </c>
-      <c r="D33" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" t="s">
-        <v>133</v>
-      </c>
       <c r="F33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H33">
         <v>33.995612000000001</v>
@@ -3753,63 +3750,63 @@
         <v>731435978</v>
       </c>
       <c r="L33" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M33">
         <v>2</v>
       </c>
       <c r="N33" t="s">
+        <v>44</v>
+      </c>
+      <c r="O33" t="s">
+        <v>31</v>
+      </c>
+      <c r="P33" t="s">
         <v>45</v>
       </c>
-      <c r="O33" t="s">
-        <v>32</v>
-      </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
         <v>46</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="R33" t="s">
+        <v>34</v>
+      </c>
+      <c r="S33" t="s">
+        <v>35</v>
+      </c>
+      <c r="T33" t="s">
+        <v>50</v>
+      </c>
+      <c r="U33" t="s">
         <v>47</v>
       </c>
-      <c r="R33" t="s">
-        <v>35</v>
-      </c>
-      <c r="S33" t="s">
-        <v>36</v>
-      </c>
-      <c r="T33" t="s">
-        <v>51</v>
-      </c>
-      <c r="U33" t="s">
-        <v>48</v>
-      </c>
       <c r="V33" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C34" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D34" t="s">
-        <v>26</v>
-      </c>
-      <c r="E34" s="5" t="s">
+      <c r="F34" t="s">
         <v>136</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>137</v>
-      </c>
-      <c r="G34" t="s">
-        <v>138</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -3818,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>30</v>
+        <v>336</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -3827,57 +3824,57 @@
         <v>0</v>
       </c>
       <c r="N34" t="s">
+        <v>30</v>
+      </c>
+      <c r="O34" t="s">
         <v>31</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>32</v>
       </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
         <v>33</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="R34" t="s">
         <v>34</v>
       </c>
-      <c r="R34" t="s">
+      <c r="S34" t="s">
         <v>35</v>
       </c>
-      <c r="S34" t="s">
+      <c r="T34" t="s">
         <v>36</v>
       </c>
-      <c r="T34" t="s">
+      <c r="U34" t="s">
         <v>37</v>
       </c>
-      <c r="U34" t="s">
-        <v>38</v>
-      </c>
       <c r="V34" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B35" s="1">
         <v>10001</v>
       </c>
       <c r="C35" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" t="s">
+        <v>41</v>
+      </c>
+      <c r="F35" t="s">
         <v>139</v>
       </c>
-      <c r="D35" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" t="s">
-        <v>140</v>
-      </c>
       <c r="G35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H35">
         <v>34.521169999999998</v>
@@ -3892,63 +3889,63 @@
         <v>779517433</v>
       </c>
       <c r="L35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M35">
         <v>3</v>
       </c>
       <c r="N35" t="s">
+        <v>44</v>
+      </c>
+      <c r="O35" t="s">
+        <v>31</v>
+      </c>
+      <c r="P35" t="s">
         <v>45</v>
       </c>
-      <c r="O35" t="s">
-        <v>32</v>
-      </c>
-      <c r="P35" t="s">
+      <c r="Q35" t="s">
         <v>46</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="R35" t="s">
+        <v>34</v>
+      </c>
+      <c r="S35" t="s">
+        <v>35</v>
+      </c>
+      <c r="T35" t="s">
+        <v>36</v>
+      </c>
+      <c r="U35" t="s">
+        <v>37</v>
+      </c>
+      <c r="V35" t="s">
         <v>47</v>
       </c>
-      <c r="R35" t="s">
-        <v>35</v>
-      </c>
-      <c r="S35" t="s">
-        <v>36</v>
-      </c>
-      <c r="T35" t="s">
-        <v>37</v>
-      </c>
-      <c r="U35" t="s">
-        <v>38</v>
-      </c>
-      <c r="V35" t="s">
-        <v>48</v>
-      </c>
       <c r="W35" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B36" s="1">
         <v>10002</v>
       </c>
       <c r="C36" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" t="s">
         <v>142</v>
       </c>
-      <c r="D36" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>143</v>
       </c>
-      <c r="F36" t="s">
-        <v>144</v>
-      </c>
       <c r="G36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H36">
         <v>34.360207000000003</v>
@@ -3963,63 +3960,63 @@
         <v>753476995</v>
       </c>
       <c r="L36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M36">
         <v>2</v>
       </c>
       <c r="N36" t="s">
+        <v>44</v>
+      </c>
+      <c r="O36" t="s">
+        <v>31</v>
+      </c>
+      <c r="P36" t="s">
         <v>45</v>
       </c>
-      <c r="O36" t="s">
-        <v>32</v>
-      </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
         <v>46</v>
       </c>
-      <c r="Q36" t="s">
-        <v>47</v>
-      </c>
       <c r="R36" t="s">
+        <v>34</v>
+      </c>
+      <c r="S36" t="s">
         <v>35</v>
       </c>
-      <c r="S36" t="s">
+      <c r="T36" t="s">
         <v>36</v>
       </c>
-      <c r="T36" t="s">
+      <c r="U36" t="s">
         <v>37</v>
       </c>
-      <c r="U36" t="s">
-        <v>38</v>
-      </c>
       <c r="V36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B37" s="1">
         <v>10003</v>
       </c>
       <c r="C37" t="s">
+        <v>145</v>
+      </c>
+      <c r="D37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" t="s">
         <v>146</v>
       </c>
-      <c r="D37" t="s">
-        <v>26</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>147</v>
       </c>
-      <c r="F37" t="s">
-        <v>148</v>
-      </c>
       <c r="G37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H37">
         <v>34.405692000000002</v>
@@ -4034,63 +4031,63 @@
         <v>734239083</v>
       </c>
       <c r="L37" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M37">
         <v>4</v>
       </c>
       <c r="N37" t="s">
+        <v>44</v>
+      </c>
+      <c r="O37" t="s">
+        <v>31</v>
+      </c>
+      <c r="P37" t="s">
         <v>45</v>
       </c>
-      <c r="O37" t="s">
-        <v>32</v>
-      </c>
-      <c r="P37" t="s">
+      <c r="Q37" t="s">
         <v>46</v>
       </c>
-      <c r="Q37" t="s">
-        <v>47</v>
-      </c>
       <c r="R37" t="s">
+        <v>34</v>
+      </c>
+      <c r="S37" t="s">
         <v>35</v>
       </c>
-      <c r="S37" t="s">
+      <c r="T37" t="s">
         <v>36</v>
       </c>
-      <c r="T37" t="s">
+      <c r="U37" t="s">
         <v>37</v>
       </c>
-      <c r="U37" t="s">
-        <v>38</v>
-      </c>
       <c r="V37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B38" s="1">
         <v>10004</v>
       </c>
       <c r="C38" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" t="s">
         <v>150</v>
       </c>
-      <c r="D38" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>151</v>
       </c>
-      <c r="F38" t="s">
-        <v>152</v>
-      </c>
       <c r="G38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H38">
         <v>34.287878999999997</v>
@@ -4105,63 +4102,63 @@
         <v>937997757</v>
       </c>
       <c r="L38" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38" t="s">
+        <v>44</v>
+      </c>
+      <c r="O38" t="s">
+        <v>31</v>
+      </c>
+      <c r="P38" t="s">
         <v>45</v>
       </c>
-      <c r="O38" t="s">
-        <v>32</v>
-      </c>
-      <c r="P38" t="s">
+      <c r="Q38" t="s">
         <v>46</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="R38" t="s">
+        <v>34</v>
+      </c>
+      <c r="S38" t="s">
+        <v>35</v>
+      </c>
+      <c r="T38" t="s">
+        <v>36</v>
+      </c>
+      <c r="U38" t="s">
+        <v>37</v>
+      </c>
+      <c r="V38" t="s">
         <v>47</v>
       </c>
-      <c r="R38" t="s">
-        <v>35</v>
-      </c>
-      <c r="S38" t="s">
-        <v>36</v>
-      </c>
-      <c r="T38" t="s">
-        <v>37</v>
-      </c>
-      <c r="U38" t="s">
-        <v>38</v>
-      </c>
-      <c r="V38" t="s">
-        <v>48</v>
-      </c>
       <c r="W38" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B39" s="1">
         <v>10005</v>
       </c>
       <c r="C39" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" t="s">
         <v>154</v>
       </c>
-      <c r="D39" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
+        <v>151</v>
+      </c>
+      <c r="G39" t="s">
         <v>155</v>
-      </c>
-      <c r="F39" t="s">
-        <v>152</v>
-      </c>
-      <c r="G39" t="s">
-        <v>156</v>
       </c>
       <c r="H39">
         <v>34.256413999999999</v>
@@ -4176,63 +4173,63 @@
         <v>887311749</v>
       </c>
       <c r="L39" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39" t="s">
+        <v>44</v>
+      </c>
+      <c r="O39" t="s">
+        <v>31</v>
+      </c>
+      <c r="P39" t="s">
         <v>45</v>
       </c>
-      <c r="O39" t="s">
-        <v>32</v>
-      </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
         <v>46</v>
       </c>
-      <c r="Q39" t="s">
-        <v>47</v>
-      </c>
       <c r="R39" t="s">
+        <v>34</v>
+      </c>
+      <c r="S39" t="s">
         <v>35</v>
       </c>
-      <c r="S39" t="s">
+      <c r="T39" t="s">
         <v>36</v>
       </c>
-      <c r="T39" t="s">
+      <c r="U39" t="s">
         <v>37</v>
       </c>
-      <c r="U39" t="s">
-        <v>38</v>
-      </c>
       <c r="V39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B40" s="1">
         <v>10006</v>
       </c>
       <c r="C40" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" t="s">
         <v>158</v>
       </c>
-      <c r="D40" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40" t="s">
-        <v>159</v>
-      </c>
       <c r="F40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G40" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H40">
         <v>34.262476999999997</v>
@@ -4247,63 +4244,63 @@
         <v>915790305</v>
       </c>
       <c r="L40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M40">
         <v>5</v>
       </c>
       <c r="N40" t="s">
+        <v>44</v>
+      </c>
+      <c r="O40" t="s">
+        <v>31</v>
+      </c>
+      <c r="P40" t="s">
         <v>45</v>
       </c>
-      <c r="O40" t="s">
-        <v>32</v>
-      </c>
-      <c r="P40" t="s">
+      <c r="Q40" t="s">
         <v>46</v>
       </c>
-      <c r="Q40" t="s">
-        <v>47</v>
-      </c>
       <c r="R40" t="s">
+        <v>34</v>
+      </c>
+      <c r="S40" t="s">
         <v>35</v>
       </c>
-      <c r="S40" t="s">
+      <c r="T40" t="s">
         <v>36</v>
       </c>
-      <c r="T40" t="s">
+      <c r="U40" t="s">
         <v>37</v>
       </c>
-      <c r="U40" t="s">
-        <v>38</v>
-      </c>
       <c r="V40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B41" s="1">
         <v>10007</v>
       </c>
       <c r="C41" t="s">
+        <v>160</v>
+      </c>
+      <c r="D41" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" t="s">
         <v>161</v>
       </c>
-      <c r="D41" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>162</v>
       </c>
-      <c r="F41" t="s">
-        <v>163</v>
-      </c>
       <c r="G41" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H41">
         <v>34.192861000000001</v>
@@ -4318,63 +4315,63 @@
         <v>811552880</v>
       </c>
       <c r="L41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M41">
         <v>2</v>
       </c>
       <c r="N41" t="s">
+        <v>44</v>
+      </c>
+      <c r="O41" t="s">
+        <v>31</v>
+      </c>
+      <c r="P41" t="s">
         <v>45</v>
       </c>
-      <c r="O41" t="s">
-        <v>32</v>
-      </c>
-      <c r="P41" t="s">
+      <c r="Q41" t="s">
         <v>46</v>
       </c>
-      <c r="Q41" t="s">
-        <v>47</v>
-      </c>
       <c r="R41" t="s">
+        <v>34</v>
+      </c>
+      <c r="S41" t="s">
         <v>35</v>
       </c>
-      <c r="S41" t="s">
+      <c r="T41" t="s">
         <v>36</v>
       </c>
-      <c r="T41" t="s">
+      <c r="U41" t="s">
         <v>37</v>
       </c>
-      <c r="U41" t="s">
-        <v>38</v>
-      </c>
       <c r="V41" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B42" s="1">
         <v>10008</v>
       </c>
       <c r="C42" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" t="s">
         <v>165</v>
       </c>
-      <c r="D42" t="s">
-        <v>26</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>166</v>
       </c>
-      <c r="F42" t="s">
-        <v>167</v>
-      </c>
       <c r="G42" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H42">
         <v>34.522413999999998</v>
@@ -4389,63 +4386,63 @@
         <v>695325692</v>
       </c>
       <c r="L42" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M42">
         <v>2</v>
       </c>
       <c r="N42" t="s">
+        <v>44</v>
+      </c>
+      <c r="O42" t="s">
+        <v>31</v>
+      </c>
+      <c r="P42" t="s">
         <v>45</v>
       </c>
-      <c r="O42" t="s">
-        <v>32</v>
-      </c>
-      <c r="P42" t="s">
+      <c r="Q42" t="s">
         <v>46</v>
       </c>
-      <c r="Q42" t="s">
-        <v>47</v>
-      </c>
       <c r="R42" t="s">
+        <v>34</v>
+      </c>
+      <c r="S42" t="s">
         <v>35</v>
       </c>
-      <c r="S42" t="s">
+      <c r="T42" t="s">
         <v>36</v>
       </c>
-      <c r="T42" t="s">
+      <c r="U42" t="s">
         <v>37</v>
       </c>
-      <c r="U42" t="s">
-        <v>38</v>
-      </c>
       <c r="V42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B43" s="1">
         <v>10009</v>
       </c>
       <c r="C43" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" t="s">
         <v>169</v>
       </c>
-      <c r="D43" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>170</v>
       </c>
-      <c r="F43" t="s">
-        <v>171</v>
-      </c>
       <c r="G43" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H43">
         <v>33.998232000000002</v>
@@ -4460,63 +4457,63 @@
         <v>745360421</v>
       </c>
       <c r="L43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M43">
         <v>2</v>
       </c>
       <c r="N43" t="s">
+        <v>44</v>
+      </c>
+      <c r="O43" t="s">
+        <v>31</v>
+      </c>
+      <c r="P43" t="s">
         <v>45</v>
       </c>
-      <c r="O43" t="s">
-        <v>32</v>
-      </c>
-      <c r="P43" t="s">
+      <c r="Q43" t="s">
         <v>46</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="R43" t="s">
+        <v>34</v>
+      </c>
+      <c r="S43" t="s">
+        <v>35</v>
+      </c>
+      <c r="T43" t="s">
+        <v>36</v>
+      </c>
+      <c r="U43" t="s">
         <v>47</v>
       </c>
-      <c r="R43" t="s">
-        <v>35</v>
-      </c>
-      <c r="S43" t="s">
-        <v>36</v>
-      </c>
-      <c r="T43" t="s">
-        <v>37</v>
-      </c>
-      <c r="U43" t="s">
-        <v>48</v>
-      </c>
       <c r="V43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B44" s="1">
         <v>10010</v>
       </c>
       <c r="C44" t="s">
+        <v>172</v>
+      </c>
+      <c r="D44" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" t="s">
         <v>173</v>
       </c>
-      <c r="D44" t="s">
-        <v>26</v>
-      </c>
-      <c r="E44" t="s">
-        <v>174</v>
-      </c>
       <c r="F44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H44">
         <v>34.017502</v>
@@ -4531,63 +4528,63 @@
         <v>766074745</v>
       </c>
       <c r="L44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M44">
         <v>2</v>
       </c>
       <c r="N44" t="s">
+        <v>44</v>
+      </c>
+      <c r="O44" t="s">
+        <v>31</v>
+      </c>
+      <c r="P44" t="s">
         <v>45</v>
       </c>
-      <c r="O44" t="s">
-        <v>32</v>
-      </c>
-      <c r="P44" t="s">
+      <c r="Q44" t="s">
         <v>46</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="R44" t="s">
+        <v>34</v>
+      </c>
+      <c r="S44" t="s">
+        <v>35</v>
+      </c>
+      <c r="T44" t="s">
+        <v>36</v>
+      </c>
+      <c r="U44" t="s">
         <v>47</v>
       </c>
-      <c r="R44" t="s">
-        <v>35</v>
-      </c>
-      <c r="S44" t="s">
-        <v>36</v>
-      </c>
-      <c r="T44" t="s">
-        <v>37</v>
-      </c>
-      <c r="U44" t="s">
-        <v>48</v>
-      </c>
       <c r="V44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B45" s="1">
         <v>10011</v>
       </c>
       <c r="C45" t="s">
+        <v>175</v>
+      </c>
+      <c r="D45" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" t="s">
         <v>176</v>
       </c>
-      <c r="D45" t="s">
-        <v>26</v>
-      </c>
-      <c r="E45" t="s">
-        <v>177</v>
-      </c>
       <c r="F45" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H45">
         <v>33.986607999999997</v>
@@ -4602,63 +4599,63 @@
         <v>787248921</v>
       </c>
       <c r="L45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M45">
         <v>2</v>
       </c>
       <c r="N45" t="s">
+        <v>44</v>
+      </c>
+      <c r="O45" t="s">
+        <v>31</v>
+      </c>
+      <c r="P45" t="s">
         <v>45</v>
       </c>
-      <c r="O45" t="s">
-        <v>32</v>
-      </c>
-      <c r="P45" t="s">
+      <c r="Q45" t="s">
         <v>46</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="R45" t="s">
+        <v>34</v>
+      </c>
+      <c r="S45" t="s">
+        <v>35</v>
+      </c>
+      <c r="T45" t="s">
+        <v>36</v>
+      </c>
+      <c r="U45" t="s">
         <v>47</v>
       </c>
-      <c r="R45" t="s">
-        <v>35</v>
-      </c>
-      <c r="S45" t="s">
-        <v>36</v>
-      </c>
-      <c r="T45" t="s">
-        <v>37</v>
-      </c>
-      <c r="U45" t="s">
-        <v>48</v>
-      </c>
       <c r="V45" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B46" s="1">
         <v>10012</v>
       </c>
       <c r="C46" t="s">
+        <v>178</v>
+      </c>
+      <c r="D46" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" t="s">
         <v>179</v>
       </c>
-      <c r="D46" t="s">
-        <v>26</v>
-      </c>
-      <c r="E46" t="s">
-        <v>180</v>
-      </c>
       <c r="F46" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H46">
         <v>33.978102999999997</v>
@@ -4673,63 +4670,63 @@
         <v>838412388</v>
       </c>
       <c r="L46" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M46">
         <v>2</v>
       </c>
       <c r="N46" t="s">
+        <v>44</v>
+      </c>
+      <c r="O46" t="s">
+        <v>31</v>
+      </c>
+      <c r="P46" t="s">
         <v>45</v>
       </c>
-      <c r="O46" t="s">
-        <v>32</v>
-      </c>
-      <c r="P46" t="s">
+      <c r="Q46" t="s">
         <v>46</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="R46" t="s">
+        <v>34</v>
+      </c>
+      <c r="S46" t="s">
+        <v>35</v>
+      </c>
+      <c r="T46" t="s">
+        <v>36</v>
+      </c>
+      <c r="U46" t="s">
         <v>47</v>
       </c>
-      <c r="R46" t="s">
-        <v>35</v>
-      </c>
-      <c r="S46" t="s">
-        <v>36</v>
-      </c>
-      <c r="T46" t="s">
-        <v>37</v>
-      </c>
-      <c r="U46" t="s">
-        <v>48</v>
-      </c>
       <c r="V46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B47" s="1">
         <v>10013</v>
       </c>
       <c r="C47" t="s">
+        <v>181</v>
+      </c>
+      <c r="D47" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" t="s">
         <v>182</v>
       </c>
-      <c r="D47" t="s">
-        <v>26</v>
-      </c>
-      <c r="E47" t="s">
-        <v>183</v>
-      </c>
       <c r="F47" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H47">
         <v>33.953930999999997</v>
@@ -4744,63 +4741,63 @@
         <v>751913644</v>
       </c>
       <c r="L47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M47">
         <v>2</v>
       </c>
       <c r="N47" t="s">
+        <v>44</v>
+      </c>
+      <c r="O47" t="s">
+        <v>31</v>
+      </c>
+      <c r="P47" t="s">
         <v>45</v>
       </c>
-      <c r="O47" t="s">
-        <v>32</v>
-      </c>
-      <c r="P47" t="s">
+      <c r="Q47" t="s">
         <v>46</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="R47" t="s">
+        <v>34</v>
+      </c>
+      <c r="S47" t="s">
+        <v>35</v>
+      </c>
+      <c r="T47" t="s">
+        <v>36</v>
+      </c>
+      <c r="U47" t="s">
         <v>47</v>
       </c>
-      <c r="R47" t="s">
-        <v>35</v>
-      </c>
-      <c r="S47" t="s">
-        <v>36</v>
-      </c>
-      <c r="T47" t="s">
-        <v>37</v>
-      </c>
-      <c r="U47" t="s">
-        <v>48</v>
-      </c>
       <c r="V47" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B48" s="1">
         <v>10014</v>
       </c>
       <c r="C48" t="s">
+        <v>184</v>
+      </c>
+      <c r="D48" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" t="s">
         <v>185</v>
       </c>
-      <c r="D48" t="s">
-        <v>26</v>
-      </c>
-      <c r="E48" t="s">
-        <v>186</v>
-      </c>
       <c r="F48" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H48">
         <v>34.027757000000001</v>
@@ -4815,63 +4812,63 @@
         <v>965639376</v>
       </c>
       <c r="L48" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M48">
         <v>2</v>
       </c>
       <c r="N48" t="s">
+        <v>44</v>
+      </c>
+      <c r="O48" t="s">
+        <v>31</v>
+      </c>
+      <c r="P48" t="s">
         <v>45</v>
       </c>
-      <c r="O48" t="s">
-        <v>32</v>
-      </c>
-      <c r="P48" t="s">
+      <c r="Q48" t="s">
         <v>46</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="R48" t="s">
+        <v>34</v>
+      </c>
+      <c r="S48" t="s">
+        <v>35</v>
+      </c>
+      <c r="T48" t="s">
+        <v>36</v>
+      </c>
+      <c r="U48" t="s">
         <v>47</v>
       </c>
-      <c r="R48" t="s">
-        <v>35</v>
-      </c>
-      <c r="S48" t="s">
-        <v>36</v>
-      </c>
-      <c r="T48" t="s">
-        <v>37</v>
-      </c>
-      <c r="U48" t="s">
-        <v>48</v>
-      </c>
       <c r="V48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B49" s="1">
         <v>10015</v>
       </c>
       <c r="C49" t="s">
+        <v>187</v>
+      </c>
+      <c r="D49" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" t="s">
         <v>188</v>
       </c>
-      <c r="D49" t="s">
-        <v>26</v>
-      </c>
-      <c r="E49" t="s">
-        <v>189</v>
-      </c>
       <c r="F49" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H49">
         <v>33.995612000000001</v>
@@ -4886,63 +4883,63 @@
         <v>803062069</v>
       </c>
       <c r="L49" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M49">
         <v>2</v>
       </c>
       <c r="N49" t="s">
+        <v>44</v>
+      </c>
+      <c r="O49" t="s">
+        <v>31</v>
+      </c>
+      <c r="P49" t="s">
         <v>45</v>
       </c>
-      <c r="O49" t="s">
-        <v>32</v>
-      </c>
-      <c r="P49" t="s">
+      <c r="Q49" t="s">
         <v>46</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="R49" t="s">
+        <v>34</v>
+      </c>
+      <c r="S49" t="s">
+        <v>35</v>
+      </c>
+      <c r="T49" t="s">
+        <v>36</v>
+      </c>
+      <c r="U49" t="s">
         <v>47</v>
       </c>
-      <c r="R49" t="s">
-        <v>35</v>
-      </c>
-      <c r="S49" t="s">
-        <v>36</v>
-      </c>
-      <c r="T49" t="s">
-        <v>37</v>
-      </c>
-      <c r="U49" t="s">
-        <v>48</v>
-      </c>
       <c r="V49" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C50" t="s">
+        <v>191</v>
+      </c>
+      <c r="D50" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" t="s">
         <v>192</v>
       </c>
-      <c r="D50" t="s">
-        <v>26</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="F50" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="G50" t="s">
         <v>194</v>
-      </c>
-      <c r="G50" t="s">
-        <v>195</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -4951,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>30</v>
+        <v>336</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -4960,57 +4957,57 @@
         <v>0</v>
       </c>
       <c r="N50" t="s">
+        <v>30</v>
+      </c>
+      <c r="O50" t="s">
         <v>31</v>
       </c>
-      <c r="O50" t="s">
+      <c r="P50" t="s">
         <v>32</v>
       </c>
-      <c r="P50" t="s">
+      <c r="Q50" t="s">
         <v>33</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="R50" t="s">
         <v>34</v>
       </c>
-      <c r="R50" t="s">
+      <c r="S50" t="s">
         <v>35</v>
       </c>
-      <c r="S50" t="s">
+      <c r="T50" t="s">
         <v>36</v>
       </c>
-      <c r="T50" t="s">
+      <c r="U50" t="s">
         <v>37</v>
       </c>
-      <c r="U50" t="s">
-        <v>38</v>
-      </c>
       <c r="V50" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B51" s="1">
         <v>10001</v>
       </c>
       <c r="C51" t="s">
+        <v>195</v>
+      </c>
+      <c r="D51" t="s">
+        <v>26</v>
+      </c>
+      <c r="E51" t="s">
+        <v>41</v>
+      </c>
+      <c r="F51" t="s">
         <v>196</v>
       </c>
-      <c r="D51" t="s">
-        <v>26</v>
-      </c>
-      <c r="E51" t="s">
-        <v>42</v>
-      </c>
-      <c r="F51" t="s">
-        <v>197</v>
-      </c>
       <c r="G51" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H51">
         <v>34.521169999999998</v>
@@ -5025,63 +5022,63 @@
         <v>779517433</v>
       </c>
       <c r="L51" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M51">
         <v>3</v>
       </c>
       <c r="N51" t="s">
+        <v>44</v>
+      </c>
+      <c r="O51" t="s">
+        <v>31</v>
+      </c>
+      <c r="P51" t="s">
         <v>45</v>
       </c>
-      <c r="O51" t="s">
-        <v>32</v>
-      </c>
-      <c r="P51" t="s">
+      <c r="Q51" t="s">
         <v>46</v>
       </c>
-      <c r="Q51" t="s">
+      <c r="R51" t="s">
+        <v>34</v>
+      </c>
+      <c r="S51" t="s">
+        <v>35</v>
+      </c>
+      <c r="T51" t="s">
+        <v>36</v>
+      </c>
+      <c r="U51" t="s">
+        <v>37</v>
+      </c>
+      <c r="V51" t="s">
         <v>47</v>
       </c>
-      <c r="R51" t="s">
-        <v>35</v>
-      </c>
-      <c r="S51" t="s">
-        <v>36</v>
-      </c>
-      <c r="T51" t="s">
-        <v>37</v>
-      </c>
-      <c r="U51" t="s">
-        <v>38</v>
-      </c>
-      <c r="V51" t="s">
-        <v>48</v>
-      </c>
       <c r="W51" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B52" s="1">
         <v>10002</v>
       </c>
       <c r="C52" t="s">
+        <v>198</v>
+      </c>
+      <c r="D52" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" t="s">
         <v>199</v>
       </c>
-      <c r="D52" t="s">
-        <v>26</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>200</v>
       </c>
-      <c r="F52" t="s">
-        <v>201</v>
-      </c>
       <c r="G52" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H52">
         <v>34.360207000000003</v>
@@ -5096,63 +5093,63 @@
         <v>753476995</v>
       </c>
       <c r="L52" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M52">
         <v>2</v>
       </c>
       <c r="N52" t="s">
+        <v>44</v>
+      </c>
+      <c r="O52" t="s">
+        <v>31</v>
+      </c>
+      <c r="P52" t="s">
         <v>45</v>
       </c>
-      <c r="O52" t="s">
-        <v>32</v>
-      </c>
-      <c r="P52" t="s">
+      <c r="Q52" t="s">
         <v>46</v>
       </c>
-      <c r="Q52" t="s">
-        <v>47</v>
-      </c>
       <c r="R52" t="s">
+        <v>34</v>
+      </c>
+      <c r="S52" t="s">
         <v>35</v>
       </c>
-      <c r="S52" t="s">
+      <c r="T52" t="s">
         <v>36</v>
       </c>
-      <c r="T52" t="s">
+      <c r="U52" t="s">
         <v>37</v>
       </c>
-      <c r="U52" t="s">
-        <v>38</v>
-      </c>
       <c r="V52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B53" s="1">
         <v>10003</v>
       </c>
       <c r="C53" t="s">
+        <v>202</v>
+      </c>
+      <c r="D53" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53" t="s">
         <v>203</v>
       </c>
-      <c r="D53" t="s">
-        <v>26</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>204</v>
       </c>
-      <c r="F53" t="s">
-        <v>205</v>
-      </c>
       <c r="G53" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H53">
         <v>34.405692000000002</v>
@@ -5167,63 +5164,63 @@
         <v>734239083</v>
       </c>
       <c r="L53" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M53">
         <v>4</v>
       </c>
       <c r="N53" t="s">
+        <v>44</v>
+      </c>
+      <c r="O53" t="s">
+        <v>31</v>
+      </c>
+      <c r="P53" t="s">
         <v>45</v>
       </c>
-      <c r="O53" t="s">
-        <v>32</v>
-      </c>
-      <c r="P53" t="s">
+      <c r="Q53" t="s">
         <v>46</v>
       </c>
-      <c r="Q53" t="s">
-        <v>47</v>
-      </c>
       <c r="R53" t="s">
+        <v>34</v>
+      </c>
+      <c r="S53" t="s">
         <v>35</v>
       </c>
-      <c r="S53" t="s">
+      <c r="T53" t="s">
         <v>36</v>
       </c>
-      <c r="T53" t="s">
+      <c r="U53" t="s">
         <v>37</v>
       </c>
-      <c r="U53" t="s">
-        <v>38</v>
-      </c>
       <c r="V53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B54" s="1">
         <v>10004</v>
       </c>
       <c r="C54" t="s">
+        <v>206</v>
+      </c>
+      <c r="D54" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54" t="s">
         <v>207</v>
       </c>
-      <c r="D54" t="s">
-        <v>26</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>208</v>
       </c>
-      <c r="F54" t="s">
-        <v>209</v>
-      </c>
       <c r="G54" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H54">
         <v>34.287878999999997</v>
@@ -5238,63 +5235,63 @@
         <v>937997757</v>
       </c>
       <c r="L54" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M54">
         <v>2</v>
       </c>
       <c r="N54" t="s">
+        <v>44</v>
+      </c>
+      <c r="O54" t="s">
+        <v>31</v>
+      </c>
+      <c r="P54" t="s">
         <v>45</v>
       </c>
-      <c r="O54" t="s">
-        <v>32</v>
-      </c>
-      <c r="P54" t="s">
+      <c r="Q54" t="s">
         <v>46</v>
       </c>
-      <c r="Q54" t="s">
+      <c r="R54" t="s">
+        <v>34</v>
+      </c>
+      <c r="S54" t="s">
+        <v>35</v>
+      </c>
+      <c r="T54" t="s">
+        <v>36</v>
+      </c>
+      <c r="U54" t="s">
+        <v>37</v>
+      </c>
+      <c r="V54" t="s">
         <v>47</v>
       </c>
-      <c r="R54" t="s">
-        <v>35</v>
-      </c>
-      <c r="S54" t="s">
-        <v>36</v>
-      </c>
-      <c r="T54" t="s">
-        <v>37</v>
-      </c>
-      <c r="U54" t="s">
-        <v>38</v>
-      </c>
-      <c r="V54" t="s">
-        <v>48</v>
-      </c>
       <c r="W54" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B55" s="1">
         <v>10005</v>
       </c>
       <c r="C55" t="s">
+        <v>210</v>
+      </c>
+      <c r="D55" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" t="s">
         <v>211</v>
       </c>
-      <c r="D55" t="s">
-        <v>26</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
+        <v>208</v>
+      </c>
+      <c r="G55" t="s">
         <v>212</v>
-      </c>
-      <c r="F55" t="s">
-        <v>209</v>
-      </c>
-      <c r="G55" t="s">
-        <v>213</v>
       </c>
       <c r="H55">
         <v>34.256413999999999</v>
@@ -5309,63 +5306,63 @@
         <v>887311749</v>
       </c>
       <c r="L55" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55" t="s">
+        <v>44</v>
+      </c>
+      <c r="O55" t="s">
+        <v>31</v>
+      </c>
+      <c r="P55" t="s">
         <v>45</v>
       </c>
-      <c r="O55" t="s">
-        <v>32</v>
-      </c>
-      <c r="P55" t="s">
+      <c r="Q55" t="s">
         <v>46</v>
       </c>
-      <c r="Q55" t="s">
-        <v>47</v>
-      </c>
       <c r="R55" t="s">
+        <v>34</v>
+      </c>
+      <c r="S55" t="s">
         <v>35</v>
       </c>
-      <c r="S55" t="s">
+      <c r="T55" t="s">
         <v>36</v>
       </c>
-      <c r="T55" t="s">
+      <c r="U55" t="s">
         <v>37</v>
       </c>
-      <c r="U55" t="s">
-        <v>38</v>
-      </c>
       <c r="V55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W55" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B56" s="1">
         <v>10006</v>
       </c>
       <c r="C56" t="s">
+        <v>214</v>
+      </c>
+      <c r="D56" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" t="s">
         <v>215</v>
       </c>
-      <c r="D56" t="s">
-        <v>26</v>
-      </c>
-      <c r="E56" t="s">
-        <v>216</v>
-      </c>
       <c r="F56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G56" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H56">
         <v>34.262476999999997</v>
@@ -5380,63 +5377,63 @@
         <v>915790305</v>
       </c>
       <c r="L56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M56">
         <v>5</v>
       </c>
       <c r="N56" t="s">
+        <v>44</v>
+      </c>
+      <c r="O56" t="s">
+        <v>31</v>
+      </c>
+      <c r="P56" t="s">
         <v>45</v>
       </c>
-      <c r="O56" t="s">
-        <v>32</v>
-      </c>
-      <c r="P56" t="s">
+      <c r="Q56" t="s">
         <v>46</v>
       </c>
-      <c r="Q56" t="s">
-        <v>47</v>
-      </c>
       <c r="R56" t="s">
+        <v>34</v>
+      </c>
+      <c r="S56" t="s">
         <v>35</v>
       </c>
-      <c r="S56" t="s">
+      <c r="T56" t="s">
         <v>36</v>
       </c>
-      <c r="T56" t="s">
+      <c r="U56" t="s">
         <v>37</v>
       </c>
-      <c r="U56" t="s">
-        <v>38</v>
-      </c>
       <c r="V56" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W56" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B57" s="1">
         <v>10007</v>
       </c>
       <c r="C57" t="s">
+        <v>217</v>
+      </c>
+      <c r="D57" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57" t="s">
         <v>218</v>
       </c>
-      <c r="D57" t="s">
-        <v>26</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>219</v>
       </c>
-      <c r="F57" t="s">
-        <v>220</v>
-      </c>
       <c r="G57" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H57">
         <v>34.192861000000001</v>
@@ -5451,63 +5448,63 @@
         <v>811552880</v>
       </c>
       <c r="L57" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M57">
         <v>2</v>
       </c>
       <c r="N57" t="s">
+        <v>44</v>
+      </c>
+      <c r="O57" t="s">
+        <v>31</v>
+      </c>
+      <c r="P57" t="s">
         <v>45</v>
       </c>
-      <c r="O57" t="s">
-        <v>32</v>
-      </c>
-      <c r="P57" t="s">
+      <c r="Q57" t="s">
         <v>46</v>
       </c>
-      <c r="Q57" t="s">
-        <v>47</v>
-      </c>
       <c r="R57" t="s">
+        <v>34</v>
+      </c>
+      <c r="S57" t="s">
         <v>35</v>
       </c>
-      <c r="S57" t="s">
+      <c r="T57" t="s">
         <v>36</v>
       </c>
-      <c r="T57" t="s">
+      <c r="U57" t="s">
         <v>37</v>
       </c>
-      <c r="U57" t="s">
-        <v>38</v>
-      </c>
       <c r="V57" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B58" s="1">
         <v>10008</v>
       </c>
       <c r="C58" t="s">
+        <v>221</v>
+      </c>
+      <c r="D58" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" t="s">
         <v>222</v>
       </c>
-      <c r="D58" t="s">
-        <v>26</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>223</v>
       </c>
-      <c r="F58" t="s">
-        <v>224</v>
-      </c>
       <c r="G58" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H58">
         <v>34.522413999999998</v>
@@ -5522,63 +5519,63 @@
         <v>695325692</v>
       </c>
       <c r="L58" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M58">
         <v>2</v>
       </c>
       <c r="N58" t="s">
+        <v>44</v>
+      </c>
+      <c r="O58" t="s">
+        <v>31</v>
+      </c>
+      <c r="P58" t="s">
         <v>45</v>
       </c>
-      <c r="O58" t="s">
-        <v>32</v>
-      </c>
-      <c r="P58" t="s">
+      <c r="Q58" t="s">
         <v>46</v>
       </c>
-      <c r="Q58" t="s">
-        <v>47</v>
-      </c>
       <c r="R58" t="s">
+        <v>34</v>
+      </c>
+      <c r="S58" t="s">
         <v>35</v>
       </c>
-      <c r="S58" t="s">
+      <c r="T58" t="s">
         <v>36</v>
       </c>
-      <c r="T58" t="s">
+      <c r="U58" t="s">
         <v>37</v>
       </c>
-      <c r="U58" t="s">
-        <v>38</v>
-      </c>
       <c r="V58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B59" s="1">
         <v>10009</v>
       </c>
       <c r="C59" t="s">
+        <v>225</v>
+      </c>
+      <c r="D59" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" t="s">
         <v>226</v>
       </c>
-      <c r="D59" t="s">
-        <v>26</v>
-      </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>227</v>
       </c>
-      <c r="F59" t="s">
-        <v>228</v>
-      </c>
       <c r="G59" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H59">
         <v>33.998232000000002</v>
@@ -5593,63 +5590,63 @@
         <v>745360421</v>
       </c>
       <c r="L59" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M59">
         <v>2</v>
       </c>
       <c r="N59" t="s">
+        <v>44</v>
+      </c>
+      <c r="O59" t="s">
+        <v>31</v>
+      </c>
+      <c r="P59" t="s">
         <v>45</v>
       </c>
-      <c r="O59" t="s">
-        <v>32</v>
-      </c>
-      <c r="P59" t="s">
+      <c r="Q59" t="s">
         <v>46</v>
       </c>
-      <c r="Q59" t="s">
+      <c r="R59" t="s">
+        <v>34</v>
+      </c>
+      <c r="S59" t="s">
+        <v>35</v>
+      </c>
+      <c r="T59" t="s">
+        <v>36</v>
+      </c>
+      <c r="U59" t="s">
         <v>47</v>
       </c>
-      <c r="R59" t="s">
-        <v>35</v>
-      </c>
-      <c r="S59" t="s">
-        <v>36</v>
-      </c>
-      <c r="T59" t="s">
-        <v>37</v>
-      </c>
-      <c r="U59" t="s">
-        <v>48</v>
-      </c>
       <c r="V59" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B60" s="1">
         <v>10010</v>
       </c>
       <c r="C60" t="s">
+        <v>229</v>
+      </c>
+      <c r="D60" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" t="s">
         <v>230</v>
       </c>
-      <c r="D60" t="s">
-        <v>26</v>
-      </c>
-      <c r="E60" t="s">
-        <v>231</v>
-      </c>
       <c r="F60" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H60">
         <v>34.017502</v>
@@ -5664,63 +5661,63 @@
         <v>766074745</v>
       </c>
       <c r="L60" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="M60">
         <v>2</v>
       </c>
       <c r="N60" t="s">
+        <v>44</v>
+      </c>
+      <c r="O60" t="s">
+        <v>31</v>
+      </c>
+      <c r="P60" t="s">
         <v>45</v>
       </c>
-      <c r="O60" t="s">
-        <v>32</v>
-      </c>
-      <c r="P60" t="s">
+      <c r="Q60" t="s">
         <v>46</v>
       </c>
-      <c r="Q60" t="s">
+      <c r="R60" t="s">
+        <v>34</v>
+      </c>
+      <c r="S60" t="s">
+        <v>35</v>
+      </c>
+      <c r="T60" t="s">
+        <v>36</v>
+      </c>
+      <c r="U60" t="s">
         <v>47</v>
       </c>
-      <c r="R60" t="s">
-        <v>35</v>
-      </c>
-      <c r="S60" t="s">
-        <v>36</v>
-      </c>
-      <c r="T60" t="s">
-        <v>37</v>
-      </c>
-      <c r="U60" t="s">
-        <v>48</v>
-      </c>
       <c r="V60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B61" s="1">
         <v>10011</v>
       </c>
       <c r="C61" t="s">
+        <v>232</v>
+      </c>
+      <c r="D61" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" t="s">
         <v>233</v>
       </c>
-      <c r="D61" t="s">
-        <v>26</v>
-      </c>
-      <c r="E61" t="s">
-        <v>234</v>
-      </c>
       <c r="F61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H61">
         <v>33.986607999999997</v>
@@ -5735,63 +5732,63 @@
         <v>787248921</v>
       </c>
       <c r="L61" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M61">
         <v>2</v>
       </c>
       <c r="N61" t="s">
+        <v>44</v>
+      </c>
+      <c r="O61" t="s">
+        <v>31</v>
+      </c>
+      <c r="P61" t="s">
         <v>45</v>
       </c>
-      <c r="O61" t="s">
-        <v>32</v>
-      </c>
-      <c r="P61" t="s">
+      <c r="Q61" t="s">
         <v>46</v>
       </c>
-      <c r="Q61" t="s">
+      <c r="R61" t="s">
+        <v>34</v>
+      </c>
+      <c r="S61" t="s">
+        <v>35</v>
+      </c>
+      <c r="T61" t="s">
+        <v>36</v>
+      </c>
+      <c r="U61" t="s">
         <v>47</v>
       </c>
-      <c r="R61" t="s">
-        <v>35</v>
-      </c>
-      <c r="S61" t="s">
-        <v>36</v>
-      </c>
-      <c r="T61" t="s">
-        <v>37</v>
-      </c>
-      <c r="U61" t="s">
-        <v>48</v>
-      </c>
       <c r="V61" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B62" s="1">
         <v>10012</v>
       </c>
       <c r="C62" t="s">
+        <v>235</v>
+      </c>
+      <c r="D62" t="s">
+        <v>26</v>
+      </c>
+      <c r="E62" t="s">
         <v>236</v>
       </c>
-      <c r="D62" t="s">
-        <v>26</v>
-      </c>
-      <c r="E62" t="s">
-        <v>237</v>
-      </c>
       <c r="F62" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H62">
         <v>33.978102999999997</v>
@@ -5806,63 +5803,63 @@
         <v>838412388</v>
       </c>
       <c r="L62" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="M62">
         <v>2</v>
       </c>
       <c r="N62" t="s">
+        <v>44</v>
+      </c>
+      <c r="O62" t="s">
+        <v>31</v>
+      </c>
+      <c r="P62" t="s">
         <v>45</v>
       </c>
-      <c r="O62" t="s">
-        <v>32</v>
-      </c>
-      <c r="P62" t="s">
+      <c r="Q62" t="s">
         <v>46</v>
       </c>
-      <c r="Q62" t="s">
+      <c r="R62" t="s">
+        <v>34</v>
+      </c>
+      <c r="S62" t="s">
+        <v>35</v>
+      </c>
+      <c r="T62" t="s">
+        <v>36</v>
+      </c>
+      <c r="U62" t="s">
         <v>47</v>
       </c>
-      <c r="R62" t="s">
-        <v>35</v>
-      </c>
-      <c r="S62" t="s">
-        <v>36</v>
-      </c>
-      <c r="T62" t="s">
-        <v>37</v>
-      </c>
-      <c r="U62" t="s">
-        <v>48</v>
-      </c>
       <c r="V62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B63" s="1">
         <v>10013</v>
       </c>
       <c r="C63" t="s">
+        <v>238</v>
+      </c>
+      <c r="D63" t="s">
+        <v>26</v>
+      </c>
+      <c r="E63" t="s">
         <v>239</v>
       </c>
-      <c r="D63" t="s">
-        <v>26</v>
-      </c>
-      <c r="E63" t="s">
-        <v>240</v>
-      </c>
       <c r="F63" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H63">
         <v>33.953930999999997</v>
@@ -5877,63 +5874,63 @@
         <v>751913644</v>
       </c>
       <c r="L63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="M63">
         <v>2</v>
       </c>
       <c r="N63" t="s">
+        <v>44</v>
+      </c>
+      <c r="O63" t="s">
+        <v>31</v>
+      </c>
+      <c r="P63" t="s">
         <v>45</v>
       </c>
-      <c r="O63" t="s">
-        <v>32</v>
-      </c>
-      <c r="P63" t="s">
+      <c r="Q63" t="s">
         <v>46</v>
       </c>
-      <c r="Q63" t="s">
+      <c r="R63" t="s">
+        <v>34</v>
+      </c>
+      <c r="S63" t="s">
+        <v>35</v>
+      </c>
+      <c r="T63" t="s">
+        <v>36</v>
+      </c>
+      <c r="U63" t="s">
         <v>47</v>
       </c>
-      <c r="R63" t="s">
-        <v>35</v>
-      </c>
-      <c r="S63" t="s">
-        <v>36</v>
-      </c>
-      <c r="T63" t="s">
-        <v>37</v>
-      </c>
-      <c r="U63" t="s">
-        <v>48</v>
-      </c>
       <c r="V63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W63" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B64" s="1">
         <v>10014</v>
       </c>
       <c r="C64" t="s">
+        <v>241</v>
+      </c>
+      <c r="D64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" t="s">
         <v>242</v>
       </c>
-      <c r="D64" t="s">
-        <v>26</v>
-      </c>
-      <c r="E64" t="s">
-        <v>243</v>
-      </c>
       <c r="F64" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H64">
         <v>34.027757000000001</v>
@@ -5948,63 +5945,63 @@
         <v>965639376</v>
       </c>
       <c r="L64" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M64">
         <v>2</v>
       </c>
       <c r="N64" t="s">
+        <v>44</v>
+      </c>
+      <c r="O64" t="s">
+        <v>31</v>
+      </c>
+      <c r="P64" t="s">
         <v>45</v>
       </c>
-      <c r="O64" t="s">
-        <v>32</v>
-      </c>
-      <c r="P64" t="s">
+      <c r="Q64" t="s">
         <v>46</v>
       </c>
-      <c r="Q64" t="s">
+      <c r="R64" t="s">
+        <v>34</v>
+      </c>
+      <c r="S64" t="s">
+        <v>35</v>
+      </c>
+      <c r="T64" t="s">
+        <v>36</v>
+      </c>
+      <c r="U64" t="s">
         <v>47</v>
       </c>
-      <c r="R64" t="s">
-        <v>35</v>
-      </c>
-      <c r="S64" t="s">
-        <v>36</v>
-      </c>
-      <c r="T64" t="s">
-        <v>37</v>
-      </c>
-      <c r="U64" t="s">
-        <v>48</v>
-      </c>
       <c r="V64" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W64" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B65" s="1">
         <v>10015</v>
       </c>
       <c r="C65" t="s">
+        <v>244</v>
+      </c>
+      <c r="D65" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" t="s">
         <v>245</v>
       </c>
-      <c r="D65" t="s">
-        <v>26</v>
-      </c>
-      <c r="E65" t="s">
-        <v>246</v>
-      </c>
       <c r="F65" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H65">
         <v>33.995612000000001</v>
@@ -6019,63 +6016,63 @@
         <v>803062069</v>
       </c>
       <c r="L65" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65" t="s">
+        <v>44</v>
+      </c>
+      <c r="O65" t="s">
+        <v>31</v>
+      </c>
+      <c r="P65" t="s">
         <v>45</v>
       </c>
-      <c r="O65" t="s">
-        <v>32</v>
-      </c>
-      <c r="P65" t="s">
+      <c r="Q65" t="s">
         <v>46</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="R65" t="s">
+        <v>34</v>
+      </c>
+      <c r="S65" t="s">
+        <v>35</v>
+      </c>
+      <c r="T65" t="s">
+        <v>36</v>
+      </c>
+      <c r="U65" t="s">
         <v>47</v>
       </c>
-      <c r="R65" t="s">
-        <v>35</v>
-      </c>
-      <c r="S65" t="s">
-        <v>36</v>
-      </c>
-      <c r="T65" t="s">
-        <v>37</v>
-      </c>
-      <c r="U65" t="s">
-        <v>48</v>
-      </c>
       <c r="V65" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C66" t="s">
+        <v>248</v>
+      </c>
+      <c r="D66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="D66" t="s">
-        <v>26</v>
-      </c>
-      <c r="E66" s="5" t="s">
+      <c r="F66" t="s">
         <v>250</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>251</v>
-      </c>
-      <c r="G66" t="s">
-        <v>252</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -6084,7 +6081,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>30</v>
+        <v>336</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -6093,57 +6090,57 @@
         <v>0</v>
       </c>
       <c r="N66" t="s">
+        <v>30</v>
+      </c>
+      <c r="O66" t="s">
         <v>31</v>
       </c>
-      <c r="O66" t="s">
+      <c r="P66" t="s">
         <v>32</v>
       </c>
-      <c r="P66" t="s">
+      <c r="Q66" t="s">
         <v>33</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="R66" t="s">
         <v>34</v>
       </c>
-      <c r="R66" t="s">
+      <c r="S66" t="s">
         <v>35</v>
       </c>
-      <c r="S66" t="s">
+      <c r="T66" t="s">
         <v>36</v>
       </c>
-      <c r="T66" t="s">
+      <c r="U66" t="s">
         <v>37</v>
       </c>
-      <c r="U66" t="s">
-        <v>38</v>
-      </c>
       <c r="V66" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="W66" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B67" s="1">
         <v>10001</v>
       </c>
       <c r="C67" t="s">
+        <v>252</v>
+      </c>
+      <c r="D67" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" t="s">
+        <v>41</v>
+      </c>
+      <c r="F67" t="s">
         <v>253</v>
       </c>
-      <c r="D67" t="s">
-        <v>26</v>
-      </c>
-      <c r="E67" t="s">
-        <v>42</v>
-      </c>
-      <c r="F67" t="s">
-        <v>254</v>
-      </c>
       <c r="G67" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H67">
         <v>34.521169999999998</v>
@@ -6158,63 +6155,63 @@
         <v>779517433</v>
       </c>
       <c r="L67" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M67">
         <v>3</v>
       </c>
       <c r="N67" t="s">
+        <v>44</v>
+      </c>
+      <c r="O67" t="s">
+        <v>31</v>
+      </c>
+      <c r="P67" t="s">
         <v>45</v>
       </c>
-      <c r="O67" t="s">
-        <v>32</v>
-      </c>
-      <c r="P67" t="s">
+      <c r="Q67" t="s">
         <v>46</v>
       </c>
-      <c r="Q67" t="s">
+      <c r="R67" t="s">
+        <v>34</v>
+      </c>
+      <c r="S67" t="s">
+        <v>35</v>
+      </c>
+      <c r="T67" t="s">
+        <v>36</v>
+      </c>
+      <c r="U67" t="s">
+        <v>37</v>
+      </c>
+      <c r="V67" t="s">
         <v>47</v>
       </c>
-      <c r="R67" t="s">
-        <v>35</v>
-      </c>
-      <c r="S67" t="s">
-        <v>36</v>
-      </c>
-      <c r="T67" t="s">
-        <v>37</v>
-      </c>
-      <c r="U67" t="s">
-        <v>38</v>
-      </c>
-      <c r="V67" t="s">
-        <v>48</v>
-      </c>
       <c r="W67" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B68" s="1">
         <v>10002</v>
       </c>
       <c r="C68" t="s">
+        <v>255</v>
+      </c>
+      <c r="D68" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" t="s">
         <v>256</v>
       </c>
-      <c r="D68" t="s">
-        <v>26</v>
-      </c>
-      <c r="E68" t="s">
-        <v>257</v>
-      </c>
       <c r="F68" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G68" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H68">
         <v>34.360207000000003</v>
@@ -6229,63 +6226,63 @@
         <v>753476995</v>
       </c>
       <c r="L68" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68" t="s">
+        <v>44</v>
+      </c>
+      <c r="O68" t="s">
+        <v>31</v>
+      </c>
+      <c r="P68" t="s">
         <v>45</v>
       </c>
-      <c r="O68" t="s">
-        <v>32</v>
-      </c>
-      <c r="P68" t="s">
+      <c r="Q68" t="s">
         <v>46</v>
       </c>
-      <c r="Q68" t="s">
-        <v>47</v>
-      </c>
       <c r="R68" t="s">
+        <v>34</v>
+      </c>
+      <c r="S68" t="s">
         <v>35</v>
       </c>
-      <c r="S68" t="s">
+      <c r="T68" t="s">
         <v>36</v>
       </c>
-      <c r="T68" t="s">
+      <c r="U68" t="s">
         <v>37</v>
       </c>
-      <c r="U68" t="s">
-        <v>38</v>
-      </c>
       <c r="V68" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W68" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B69" s="1">
         <v>10003</v>
       </c>
       <c r="C69" t="s">
+        <v>258</v>
+      </c>
+      <c r="D69" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" t="s">
         <v>259</v>
       </c>
-      <c r="D69" t="s">
-        <v>26</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>260</v>
       </c>
-      <c r="F69" t="s">
-        <v>261</v>
-      </c>
       <c r="G69" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H69">
         <v>34.405692000000002</v>
@@ -6300,63 +6297,63 @@
         <v>734239083</v>
       </c>
       <c r="L69" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M69">
         <v>4</v>
       </c>
       <c r="N69" t="s">
+        <v>44</v>
+      </c>
+      <c r="O69" t="s">
+        <v>31</v>
+      </c>
+      <c r="P69" t="s">
         <v>45</v>
       </c>
-      <c r="O69" t="s">
-        <v>32</v>
-      </c>
-      <c r="P69" t="s">
+      <c r="Q69" t="s">
         <v>46</v>
       </c>
-      <c r="Q69" t="s">
-        <v>47</v>
-      </c>
       <c r="R69" t="s">
+        <v>34</v>
+      </c>
+      <c r="S69" t="s">
         <v>35</v>
       </c>
-      <c r="S69" t="s">
+      <c r="T69" t="s">
         <v>36</v>
       </c>
-      <c r="T69" t="s">
+      <c r="U69" t="s">
         <v>37</v>
       </c>
-      <c r="U69" t="s">
-        <v>38</v>
-      </c>
       <c r="V69" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W69" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B70" s="1">
         <v>10004</v>
       </c>
       <c r="C70" t="s">
+        <v>262</v>
+      </c>
+      <c r="D70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" t="s">
         <v>263</v>
       </c>
-      <c r="D70" t="s">
-        <v>26</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>264</v>
       </c>
-      <c r="F70" t="s">
-        <v>265</v>
-      </c>
       <c r="G70" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H70">
         <v>34.287878999999997</v>
@@ -6371,63 +6368,63 @@
         <v>937997757</v>
       </c>
       <c r="L70" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70" t="s">
+        <v>44</v>
+      </c>
+      <c r="O70" t="s">
+        <v>31</v>
+      </c>
+      <c r="P70" t="s">
         <v>45</v>
       </c>
-      <c r="O70" t="s">
-        <v>32</v>
-      </c>
-      <c r="P70" t="s">
+      <c r="Q70" t="s">
         <v>46</v>
       </c>
-      <c r="Q70" t="s">
+      <c r="R70" t="s">
+        <v>34</v>
+      </c>
+      <c r="S70" t="s">
+        <v>35</v>
+      </c>
+      <c r="T70" t="s">
+        <v>36</v>
+      </c>
+      <c r="U70" t="s">
+        <v>37</v>
+      </c>
+      <c r="V70" t="s">
         <v>47</v>
       </c>
-      <c r="R70" t="s">
-        <v>35</v>
-      </c>
-      <c r="S70" t="s">
-        <v>36</v>
-      </c>
-      <c r="T70" t="s">
-        <v>37</v>
-      </c>
-      <c r="U70" t="s">
-        <v>38</v>
-      </c>
-      <c r="V70" t="s">
-        <v>48</v>
-      </c>
       <c r="W70" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B71" s="1">
         <v>10005</v>
       </c>
       <c r="C71" t="s">
+        <v>266</v>
+      </c>
+      <c r="D71" t="s">
+        <v>26</v>
+      </c>
+      <c r="E71" t="s">
         <v>267</v>
       </c>
-      <c r="D71" t="s">
-        <v>26</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
+        <v>264</v>
+      </c>
+      <c r="G71" t="s">
         <v>268</v>
-      </c>
-      <c r="F71" t="s">
-        <v>265</v>
-      </c>
-      <c r="G71" t="s">
-        <v>269</v>
       </c>
       <c r="H71">
         <v>34.256413999999999</v>
@@ -6442,63 +6439,63 @@
         <v>887311749</v>
       </c>
       <c r="L71" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71" t="s">
+        <v>44</v>
+      </c>
+      <c r="O71" t="s">
+        <v>31</v>
+      </c>
+      <c r="P71" t="s">
         <v>45</v>
       </c>
-      <c r="O71" t="s">
-        <v>32</v>
-      </c>
-      <c r="P71" t="s">
+      <c r="Q71" t="s">
         <v>46</v>
       </c>
-      <c r="Q71" t="s">
-        <v>47</v>
-      </c>
       <c r="R71" t="s">
+        <v>34</v>
+      </c>
+      <c r="S71" t="s">
         <v>35</v>
       </c>
-      <c r="S71" t="s">
+      <c r="T71" t="s">
         <v>36</v>
       </c>
-      <c r="T71" t="s">
+      <c r="U71" t="s">
         <v>37</v>
       </c>
-      <c r="U71" t="s">
-        <v>38</v>
-      </c>
       <c r="V71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B72" s="1">
         <v>10006</v>
       </c>
       <c r="C72" t="s">
+        <v>270</v>
+      </c>
+      <c r="D72" t="s">
+        <v>26</v>
+      </c>
+      <c r="E72" t="s">
         <v>271</v>
       </c>
-      <c r="D72" t="s">
-        <v>26</v>
-      </c>
-      <c r="E72" t="s">
-        <v>272</v>
-      </c>
       <c r="F72" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G72" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H72">
         <v>34.262476999999997</v>
@@ -6513,63 +6510,63 @@
         <v>915790305</v>
       </c>
       <c r="L72" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M72">
         <v>5</v>
       </c>
       <c r="N72" t="s">
+        <v>44</v>
+      </c>
+      <c r="O72" t="s">
+        <v>31</v>
+      </c>
+      <c r="P72" t="s">
         <v>45</v>
       </c>
-      <c r="O72" t="s">
-        <v>32</v>
-      </c>
-      <c r="P72" t="s">
+      <c r="Q72" t="s">
         <v>46</v>
       </c>
-      <c r="Q72" t="s">
-        <v>47</v>
-      </c>
       <c r="R72" t="s">
+        <v>34</v>
+      </c>
+      <c r="S72" t="s">
         <v>35</v>
       </c>
-      <c r="S72" t="s">
+      <c r="T72" t="s">
         <v>36</v>
       </c>
-      <c r="T72" t="s">
+      <c r="U72" t="s">
         <v>37</v>
       </c>
-      <c r="U72" t="s">
-        <v>38</v>
-      </c>
       <c r="V72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B73" s="1">
         <v>10007</v>
       </c>
       <c r="C73" t="s">
+        <v>273</v>
+      </c>
+      <c r="D73" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" t="s">
         <v>274</v>
       </c>
-      <c r="D73" t="s">
-        <v>26</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>275</v>
       </c>
-      <c r="F73" t="s">
-        <v>276</v>
-      </c>
       <c r="G73" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H73">
         <v>34.192861000000001</v>
@@ -6584,63 +6581,63 @@
         <v>811552880</v>
       </c>
       <c r="L73" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M73">
         <v>2</v>
       </c>
       <c r="N73" t="s">
+        <v>44</v>
+      </c>
+      <c r="O73" t="s">
+        <v>31</v>
+      </c>
+      <c r="P73" t="s">
         <v>45</v>
       </c>
-      <c r="O73" t="s">
-        <v>32</v>
-      </c>
-      <c r="P73" t="s">
+      <c r="Q73" t="s">
         <v>46</v>
       </c>
-      <c r="Q73" t="s">
-        <v>47</v>
-      </c>
       <c r="R73" t="s">
+        <v>34</v>
+      </c>
+      <c r="S73" t="s">
         <v>35</v>
       </c>
-      <c r="S73" t="s">
+      <c r="T73" t="s">
         <v>36</v>
       </c>
-      <c r="T73" t="s">
+      <c r="U73" t="s">
         <v>37</v>
       </c>
-      <c r="U73" t="s">
-        <v>38</v>
-      </c>
       <c r="V73" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B74" s="1">
         <v>10008</v>
       </c>
       <c r="C74" t="s">
+        <v>277</v>
+      </c>
+      <c r="D74" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" t="s">
         <v>278</v>
       </c>
-      <c r="D74" t="s">
-        <v>26</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>279</v>
       </c>
-      <c r="F74" t="s">
-        <v>280</v>
-      </c>
       <c r="G74" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H74">
         <v>34.522413999999998</v>
@@ -6655,63 +6652,63 @@
         <v>695325692</v>
       </c>
       <c r="L74" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M74">
         <v>2</v>
       </c>
       <c r="N74" t="s">
+        <v>44</v>
+      </c>
+      <c r="O74" t="s">
+        <v>31</v>
+      </c>
+      <c r="P74" t="s">
         <v>45</v>
       </c>
-      <c r="O74" t="s">
-        <v>32</v>
-      </c>
-      <c r="P74" t="s">
+      <c r="Q74" t="s">
         <v>46</v>
       </c>
-      <c r="Q74" t="s">
-        <v>47</v>
-      </c>
       <c r="R74" t="s">
+        <v>34</v>
+      </c>
+      <c r="S74" t="s">
         <v>35</v>
       </c>
-      <c r="S74" t="s">
+      <c r="T74" t="s">
         <v>36</v>
       </c>
-      <c r="T74" t="s">
+      <c r="U74" t="s">
         <v>37</v>
       </c>
-      <c r="U74" t="s">
-        <v>38</v>
-      </c>
       <c r="V74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B75" s="1">
         <v>10009</v>
       </c>
       <c r="C75" t="s">
+        <v>281</v>
+      </c>
+      <c r="D75" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75" t="s">
         <v>282</v>
       </c>
-      <c r="D75" t="s">
-        <v>26</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>283</v>
       </c>
-      <c r="F75" t="s">
-        <v>284</v>
-      </c>
       <c r="G75" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H75">
         <v>33.998232000000002</v>
@@ -6726,63 +6723,63 @@
         <v>745360421</v>
       </c>
       <c r="L75" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M75">
         <v>2</v>
       </c>
       <c r="N75" t="s">
+        <v>44</v>
+      </c>
+      <c r="O75" t="s">
+        <v>31</v>
+      </c>
+      <c r="P75" t="s">
         <v>45</v>
       </c>
-      <c r="O75" t="s">
-        <v>32</v>
-      </c>
-      <c r="P75" t="s">
+      <c r="Q75" t="s">
         <v>46</v>
       </c>
-      <c r="Q75" t="s">
+      <c r="R75" t="s">
+        <v>34</v>
+      </c>
+      <c r="S75" t="s">
+        <v>35</v>
+      </c>
+      <c r="T75" t="s">
+        <v>36</v>
+      </c>
+      <c r="U75" t="s">
         <v>47</v>
       </c>
-      <c r="R75" t="s">
-        <v>35</v>
-      </c>
-      <c r="S75" t="s">
-        <v>36</v>
-      </c>
-      <c r="T75" t="s">
-        <v>37</v>
-      </c>
-      <c r="U75" t="s">
-        <v>48</v>
-      </c>
       <c r="V75" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W75" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B76" s="1">
         <v>10010</v>
       </c>
       <c r="C76" t="s">
+        <v>285</v>
+      </c>
+      <c r="D76" t="s">
+        <v>26</v>
+      </c>
+      <c r="E76" t="s">
         <v>286</v>
       </c>
-      <c r="D76" t="s">
-        <v>26</v>
-      </c>
-      <c r="E76" t="s">
-        <v>287</v>
-      </c>
       <c r="F76" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H76">
         <v>34.017502</v>
@@ -6797,63 +6794,63 @@
         <v>766074745</v>
       </c>
       <c r="L76" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M76">
         <v>2</v>
       </c>
       <c r="N76" t="s">
+        <v>44</v>
+      </c>
+      <c r="O76" t="s">
+        <v>31</v>
+      </c>
+      <c r="P76" t="s">
         <v>45</v>
       </c>
-      <c r="O76" t="s">
-        <v>32</v>
-      </c>
-      <c r="P76" t="s">
+      <c r="Q76" t="s">
         <v>46</v>
       </c>
-      <c r="Q76" t="s">
+      <c r="R76" t="s">
+        <v>34</v>
+      </c>
+      <c r="S76" t="s">
+        <v>35</v>
+      </c>
+      <c r="T76" t="s">
+        <v>36</v>
+      </c>
+      <c r="U76" t="s">
         <v>47</v>
       </c>
-      <c r="R76" t="s">
-        <v>35</v>
-      </c>
-      <c r="S76" t="s">
-        <v>36</v>
-      </c>
-      <c r="T76" t="s">
-        <v>37</v>
-      </c>
-      <c r="U76" t="s">
-        <v>48</v>
-      </c>
       <c r="V76" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W76" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B77" s="1">
         <v>10011</v>
       </c>
       <c r="C77" t="s">
+        <v>288</v>
+      </c>
+      <c r="D77" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77" t="s">
         <v>289</v>
       </c>
-      <c r="D77" t="s">
-        <v>26</v>
-      </c>
-      <c r="E77" t="s">
-        <v>290</v>
-      </c>
       <c r="F77" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H77">
         <v>33.986607999999997</v>
@@ -6868,63 +6865,63 @@
         <v>787248921</v>
       </c>
       <c r="L77" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M77">
         <v>2</v>
       </c>
       <c r="N77" t="s">
+        <v>44</v>
+      </c>
+      <c r="O77" t="s">
+        <v>31</v>
+      </c>
+      <c r="P77" t="s">
         <v>45</v>
       </c>
-      <c r="O77" t="s">
-        <v>32</v>
-      </c>
-      <c r="P77" t="s">
+      <c r="Q77" t="s">
         <v>46</v>
       </c>
-      <c r="Q77" t="s">
+      <c r="R77" t="s">
+        <v>34</v>
+      </c>
+      <c r="S77" t="s">
+        <v>35</v>
+      </c>
+      <c r="T77" t="s">
+        <v>36</v>
+      </c>
+      <c r="U77" t="s">
         <v>47</v>
       </c>
-      <c r="R77" t="s">
-        <v>35</v>
-      </c>
-      <c r="S77" t="s">
-        <v>36</v>
-      </c>
-      <c r="T77" t="s">
-        <v>37</v>
-      </c>
-      <c r="U77" t="s">
-        <v>48</v>
-      </c>
       <c r="V77" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W77" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B78" s="1">
         <v>10012</v>
       </c>
       <c r="C78" t="s">
+        <v>291</v>
+      </c>
+      <c r="D78" t="s">
+        <v>26</v>
+      </c>
+      <c r="E78" t="s">
         <v>292</v>
       </c>
-      <c r="D78" t="s">
-        <v>26</v>
-      </c>
-      <c r="E78" t="s">
-        <v>293</v>
-      </c>
       <c r="F78" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H78">
         <v>33.978102999999997</v>
@@ -6939,63 +6936,63 @@
         <v>838412388</v>
       </c>
       <c r="L78" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="M78">
         <v>2</v>
       </c>
       <c r="N78" t="s">
+        <v>44</v>
+      </c>
+      <c r="O78" t="s">
+        <v>31</v>
+      </c>
+      <c r="P78" t="s">
         <v>45</v>
       </c>
-      <c r="O78" t="s">
-        <v>32</v>
-      </c>
-      <c r="P78" t="s">
+      <c r="Q78" t="s">
         <v>46</v>
       </c>
-      <c r="Q78" t="s">
+      <c r="R78" t="s">
+        <v>34</v>
+      </c>
+      <c r="S78" t="s">
+        <v>35</v>
+      </c>
+      <c r="T78" t="s">
+        <v>36</v>
+      </c>
+      <c r="U78" t="s">
         <v>47</v>
       </c>
-      <c r="R78" t="s">
-        <v>35</v>
-      </c>
-      <c r="S78" t="s">
-        <v>36</v>
-      </c>
-      <c r="T78" t="s">
-        <v>37</v>
-      </c>
-      <c r="U78" t="s">
-        <v>48</v>
-      </c>
       <c r="V78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W78" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B79" s="1">
         <v>10013</v>
       </c>
       <c r="C79" t="s">
+        <v>294</v>
+      </c>
+      <c r="D79" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" t="s">
         <v>295</v>
       </c>
-      <c r="D79" t="s">
-        <v>26</v>
-      </c>
-      <c r="E79" t="s">
-        <v>296</v>
-      </c>
       <c r="F79" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H79">
         <v>33.953930999999997</v>
@@ -7010,63 +7007,63 @@
         <v>751913644</v>
       </c>
       <c r="L79" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M79">
         <v>2</v>
       </c>
       <c r="N79" t="s">
+        <v>44</v>
+      </c>
+      <c r="O79" t="s">
+        <v>31</v>
+      </c>
+      <c r="P79" t="s">
         <v>45</v>
       </c>
-      <c r="O79" t="s">
-        <v>32</v>
-      </c>
-      <c r="P79" t="s">
+      <c r="Q79" t="s">
         <v>46</v>
       </c>
-      <c r="Q79" t="s">
+      <c r="R79" t="s">
+        <v>34</v>
+      </c>
+      <c r="S79" t="s">
+        <v>35</v>
+      </c>
+      <c r="T79" t="s">
+        <v>36</v>
+      </c>
+      <c r="U79" t="s">
         <v>47</v>
       </c>
-      <c r="R79" t="s">
-        <v>35</v>
-      </c>
-      <c r="S79" t="s">
-        <v>36</v>
-      </c>
-      <c r="T79" t="s">
-        <v>37</v>
-      </c>
-      <c r="U79" t="s">
-        <v>48</v>
-      </c>
       <c r="V79" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W79" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B80" s="1">
         <v>10014</v>
       </c>
       <c r="C80" t="s">
+        <v>297</v>
+      </c>
+      <c r="D80" t="s">
+        <v>26</v>
+      </c>
+      <c r="E80" t="s">
         <v>298</v>
       </c>
-      <c r="D80" t="s">
-        <v>26</v>
-      </c>
-      <c r="E80" t="s">
-        <v>299</v>
-      </c>
       <c r="F80" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H80">
         <v>34.027757000000001</v>
@@ -7081,63 +7078,63 @@
         <v>965639376</v>
       </c>
       <c r="L80" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="M80">
         <v>2</v>
       </c>
       <c r="N80" t="s">
+        <v>44</v>
+      </c>
+      <c r="O80" t="s">
+        <v>31</v>
+      </c>
+      <c r="P80" t="s">
         <v>45</v>
       </c>
-      <c r="O80" t="s">
-        <v>32</v>
-      </c>
-      <c r="P80" t="s">
+      <c r="Q80" t="s">
         <v>46</v>
       </c>
-      <c r="Q80" t="s">
+      <c r="R80" t="s">
+        <v>34</v>
+      </c>
+      <c r="S80" t="s">
+        <v>35</v>
+      </c>
+      <c r="T80" t="s">
+        <v>36</v>
+      </c>
+      <c r="U80" t="s">
         <v>47</v>
       </c>
-      <c r="R80" t="s">
-        <v>35</v>
-      </c>
-      <c r="S80" t="s">
-        <v>36</v>
-      </c>
-      <c r="T80" t="s">
-        <v>37</v>
-      </c>
-      <c r="U80" t="s">
-        <v>48</v>
-      </c>
       <c r="V80" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W80" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B81" s="1">
         <v>10015</v>
       </c>
       <c r="C81" t="s">
+        <v>300</v>
+      </c>
+      <c r="D81" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" t="s">
         <v>301</v>
       </c>
-      <c r="D81" t="s">
-        <v>26</v>
-      </c>
-      <c r="E81" t="s">
-        <v>302</v>
-      </c>
       <c r="F81" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H81">
         <v>33.995612000000001</v>
@@ -7152,63 +7149,63 @@
         <v>803062069</v>
       </c>
       <c r="L81" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M81">
         <v>2</v>
       </c>
       <c r="N81" t="s">
+        <v>44</v>
+      </c>
+      <c r="O81" t="s">
+        <v>31</v>
+      </c>
+      <c r="P81" t="s">
         <v>45</v>
       </c>
-      <c r="O81" t="s">
-        <v>32</v>
-      </c>
-      <c r="P81" t="s">
+      <c r="Q81" t="s">
         <v>46</v>
       </c>
-      <c r="Q81" t="s">
+      <c r="R81" t="s">
+        <v>34</v>
+      </c>
+      <c r="S81" t="s">
+        <v>35</v>
+      </c>
+      <c r="T81" t="s">
+        <v>36</v>
+      </c>
+      <c r="U81" t="s">
         <v>47</v>
       </c>
-      <c r="R81" t="s">
-        <v>35</v>
-      </c>
-      <c r="S81" t="s">
-        <v>36</v>
-      </c>
-      <c r="T81" t="s">
-        <v>37</v>
-      </c>
-      <c r="U81" t="s">
-        <v>48</v>
-      </c>
       <c r="V81" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W81" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B82">
         <v>10137</v>
       </c>
       <c r="C82" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D82" t="s">
         <v>26</v>
       </c>
       <c r="E82" t="s">
+        <v>52</v>
+      </c>
+      <c r="F82" t="s">
         <v>53</v>
       </c>
-      <c r="F82" t="s">
-        <v>54</v>
-      </c>
       <c r="G82" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H82">
         <v>34.360207000000003</v>
@@ -7223,7 +7220,7 @@
         <v>753476995</v>
       </c>
       <c r="L82" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M82">
         <v>2</v>
@@ -7247,39 +7244,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T82" t="s">
+        <v>36</v>
+      </c>
+      <c r="U82" t="s">
         <v>37</v>
       </c>
-      <c r="U82" t="s">
-        <v>38</v>
-      </c>
       <c r="V82" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="W82" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B83">
         <v>10138</v>
       </c>
       <c r="C83" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D83" t="s">
         <v>26</v>
       </c>
       <c r="E83" t="s">
+        <v>57</v>
+      </c>
+      <c r="F83" t="s">
         <v>58</v>
       </c>
-      <c r="F83" t="s">
-        <v>59</v>
-      </c>
       <c r="G83" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H83">
         <v>34.405692000000002</v>
@@ -7294,7 +7291,7 @@
         <v>734239083</v>
       </c>
       <c r="L83" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M83">
         <v>4</v>
@@ -7318,39 +7315,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T83" t="s">
+        <v>36</v>
+      </c>
+      <c r="U83" t="s">
         <v>37</v>
       </c>
-      <c r="U83" t="s">
-        <v>38</v>
-      </c>
       <c r="V83" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W83" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B84">
         <v>10139</v>
       </c>
       <c r="C84" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D84" t="s">
         <v>26</v>
       </c>
       <c r="E84" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F84" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G84" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H84">
         <v>34.256413999999999</v>
@@ -7365,7 +7362,7 @@
         <v>887311749</v>
       </c>
       <c r="L84" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M84">
         <v>1</v>
@@ -7389,39 +7386,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T84" t="s">
+        <v>36</v>
+      </c>
+      <c r="U84" t="s">
         <v>37</v>
       </c>
-      <c r="U84" t="s">
-        <v>38</v>
-      </c>
       <c r="V84" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W84" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B85">
         <v>10140</v>
       </c>
       <c r="C85" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D85" t="s">
         <v>26</v>
       </c>
       <c r="E85" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F85" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G85" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H85">
         <v>34.262476999999997</v>
@@ -7436,7 +7433,7 @@
         <v>915790305</v>
       </c>
       <c r="L85" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M85">
         <v>5</v>
@@ -7460,39 +7457,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T85" t="s">
+        <v>36</v>
+      </c>
+      <c r="U85" t="s">
         <v>37</v>
       </c>
-      <c r="U85" t="s">
-        <v>38</v>
-      </c>
       <c r="V85" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="W85" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B86">
         <v>10141</v>
       </c>
       <c r="C86" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D86" t="s">
         <v>26</v>
       </c>
       <c r="E86" t="s">
+        <v>81</v>
+      </c>
+      <c r="F86" t="s">
         <v>82</v>
       </c>
-      <c r="F86" t="s">
-        <v>83</v>
-      </c>
       <c r="G86" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H86">
         <v>34.192861000000001</v>
@@ -7507,7 +7504,7 @@
         <v>811552880</v>
       </c>
       <c r="L86" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M86">
         <v>2</v>
@@ -7531,39 +7528,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T86" t="s">
+        <v>36</v>
+      </c>
+      <c r="U86" t="s">
         <v>37</v>
       </c>
-      <c r="U86" t="s">
-        <v>38</v>
-      </c>
       <c r="V86" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="W86" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B87">
         <v>10142</v>
       </c>
       <c r="C87" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D87" t="s">
         <v>26</v>
       </c>
       <c r="E87" t="s">
+        <v>95</v>
+      </c>
+      <c r="F87" t="s">
         <v>96</v>
       </c>
-      <c r="F87" t="s">
-        <v>97</v>
-      </c>
       <c r="G87" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H87">
         <v>33.998232000000002</v>
@@ -7578,7 +7575,7 @@
         <v>745360421</v>
       </c>
       <c r="L87" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M87">
         <v>2</v>
@@ -7602,39 +7599,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T87" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U87" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V87" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W87" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B88">
         <v>10143</v>
       </c>
       <c r="C88" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D88" t="s">
         <v>26</v>
       </c>
       <c r="E88" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F88" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G88" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H88">
         <v>34.017502</v>
@@ -7649,7 +7646,7 @@
         <v>766074745</v>
       </c>
       <c r="L88" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M88">
         <v>2</v>
@@ -7673,39 +7670,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T88" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U88" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V88" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W88" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B89">
         <v>10144</v>
       </c>
       <c r="C89" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D89" t="s">
         <v>26</v>
       </c>
       <c r="E89" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F89" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G89" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H89">
         <v>33.986607999999997</v>
@@ -7720,7 +7717,7 @@
         <v>787248921</v>
       </c>
       <c r="L89" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M89">
         <v>2</v>
@@ -7744,39 +7741,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T89" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U89" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V89" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W89" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B90">
         <v>10145</v>
       </c>
       <c r="C90" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D90" t="s">
         <v>26</v>
       </c>
       <c r="E90" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G90" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H90">
         <v>33.978102999999997</v>
@@ -7791,7 +7788,7 @@
         <v>838412388</v>
       </c>
       <c r="L90" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M90">
         <v>2</v>
@@ -7815,39 +7812,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T90" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U90" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V90" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="W90" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B91">
         <v>10146</v>
       </c>
       <c r="C91" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D91" t="s">
         <v>26</v>
       </c>
       <c r="E91" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F91" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G91" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H91">
         <v>33.953930999999997</v>
@@ -7862,7 +7859,7 @@
         <v>751913644</v>
       </c>
       <c r="L91" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M91">
         <v>2</v>
@@ -7886,39 +7883,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T91" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U91" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V91" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="W91" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B92">
         <v>10147</v>
       </c>
       <c r="C92" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D92" t="s">
         <v>26</v>
       </c>
       <c r="E92" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F92" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G92" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H92">
         <v>34.027757000000001</v>
@@ -7933,7 +7930,7 @@
         <v>965639376</v>
       </c>
       <c r="L92" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="M92">
         <v>2</v>
@@ -7957,39 +7954,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T92" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V92" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="W92" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B93">
         <v>10148</v>
       </c>
       <c r="C93" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D93" t="s">
         <v>26</v>
       </c>
       <c r="E93" t="s">
+        <v>41</v>
+      </c>
+      <c r="F93" t="s">
         <v>42</v>
       </c>
-      <c r="F93" t="s">
-        <v>43</v>
-      </c>
       <c r="G93" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H93">
         <v>12.89515492</v>
@@ -8004,7 +8001,7 @@
         <v>779517433</v>
       </c>
       <c r="L93" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M93">
         <v>3</v>
@@ -8028,39 +8025,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T93" t="s">
+        <v>36</v>
+      </c>
+      <c r="U93" t="s">
         <v>37</v>
       </c>
-      <c r="U93" t="s">
-        <v>38</v>
-      </c>
       <c r="V93" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W93" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B94">
         <v>10149</v>
       </c>
       <c r="C94" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D94" t="s">
         <v>26</v>
       </c>
       <c r="E94" t="s">
+        <v>63</v>
+      </c>
+      <c r="F94" t="s">
         <v>64</v>
       </c>
-      <c r="F94" t="s">
-        <v>65</v>
-      </c>
       <c r="G94" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H94">
         <v>12.89515492</v>
@@ -8075,7 +8072,7 @@
         <v>937997757</v>
       </c>
       <c r="L94" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M94">
         <v>2</v>
@@ -8099,39 +8096,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T94" t="s">
+        <v>36</v>
+      </c>
+      <c r="U94" t="s">
         <v>37</v>
       </c>
-      <c r="U94" t="s">
-        <v>38</v>
-      </c>
       <c r="V94" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W94" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B95">
         <v>10150</v>
       </c>
       <c r="C95" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D95" t="s">
         <v>26</v>
       </c>
       <c r="E95" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F95" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G95" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H95">
         <v>33.995612000000001</v>
@@ -8146,7 +8143,7 @@
         <v>803062069</v>
       </c>
       <c r="L95" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="M95">
         <v>2</v>
@@ -8170,39 +8167,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T95" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U95" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V95" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="W95" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B96">
         <v>10151</v>
       </c>
       <c r="C96" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D96" t="s">
         <v>26</v>
       </c>
       <c r="E96" t="s">
+        <v>322</v>
+      </c>
+      <c r="F96" t="s">
         <v>323</v>
       </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>324</v>
-      </c>
-      <c r="G96" t="s">
-        <v>325</v>
       </c>
       <c r="H96">
         <v>78.547799999999995</v>
@@ -8217,7 +8214,7 @@
         <v>9663089998</v>
       </c>
       <c r="L96" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M96">
         <v>0</v>
@@ -8241,16 +8238,16 @@
         <v>0</v>
       </c>
       <c r="T96" t="s">
+        <v>334</v>
+      </c>
+      <c r="U96" t="s">
+        <v>47</v>
+      </c>
+      <c r="V96" t="s">
         <v>335</v>
       </c>
-      <c r="U96" t="s">
-        <v>48</v>
-      </c>
-      <c r="V96" t="s">
-        <v>336</v>
-      </c>
       <c r="W96" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kames\IdeaProjects\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D88D771-D774-495B-8A21-C2B74EAC5491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50CA5E7-C346-4A90-9CEB-D704FCEE522A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-12330" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -117,6 +117,9 @@
     <t>MyCountry</t>
   </si>
   <si>
+    <t>MOR</t>
+  </si>
+  <si>
     <t>24:00:00</t>
   </si>
   <si>
@@ -1033,9 +1036,6 @@
   </si>
   <si>
     <t>CSB</t>
-  </si>
-  <si>
-    <t>UTO</t>
   </si>
 </sst>
 </file>
@@ -1126,9 +1126,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1166,7 +1166,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1272,7 +1272,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1414,7 +1414,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1423,33 +1423,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W96"/>
-  <sheetFormatPr defaultColWidth="11.59765625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.265625" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.73046875" customWidth="1"/>
-    <col min="4" max="4" width="13.06640625" customWidth="1"/>
-    <col min="5" max="5" width="29.19921875" customWidth="1"/>
-    <col min="6" max="6" width="19.46484375" customWidth="1"/>
-    <col min="7" max="7" width="11.19921875" customWidth="1"/>
-    <col min="8" max="8" width="8.59765625" customWidth="1"/>
-    <col min="9" max="9" width="10.06640625" customWidth="1"/>
-    <col min="10" max="10" width="13.73046875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.53125" customWidth="1"/>
-    <col min="12" max="12" width="17.53125" customWidth="1"/>
-    <col min="13" max="13" width="17.9296875" customWidth="1"/>
-    <col min="14" max="14" width="14.9296875" customWidth="1"/>
-    <col min="15" max="15" width="22.9296875" customWidth="1"/>
-    <col min="16" max="16" width="17.19921875" customWidth="1"/>
-    <col min="17" max="18" width="16.33203125" customWidth="1"/>
-    <col min="19" max="19" width="15.59765625" customWidth="1"/>
+    <col min="1" max="1" width="10.26953125" customWidth="1"/>
+    <col min="2" max="2" width="10.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" customWidth="1"/>
+    <col min="4" max="4" width="13.08984375" customWidth="1"/>
+    <col min="5" max="5" width="29.1796875" customWidth="1"/>
+    <col min="6" max="6" width="19.453125" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" customWidth="1"/>
+    <col min="8" max="8" width="8.6328125" customWidth="1"/>
+    <col min="9" max="9" width="10.08984375" customWidth="1"/>
+    <col min="10" max="10" width="13.7265625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.54296875" customWidth="1"/>
+    <col min="12" max="12" width="17.54296875" customWidth="1"/>
+    <col min="13" max="13" width="17.90625" customWidth="1"/>
+    <col min="14" max="14" width="14.90625" customWidth="1"/>
+    <col min="15" max="15" width="22.90625" customWidth="1"/>
+    <col min="16" max="16" width="17.1796875" customWidth="1"/>
+    <col min="17" max="18" width="16.36328125" customWidth="1"/>
+    <col min="19" max="19" width="15.6328125" customWidth="1"/>
     <col min="20" max="20" width="40" customWidth="1"/>
-    <col min="21" max="21" width="16.53125" customWidth="1"/>
-    <col min="22" max="22" width="10.796875" customWidth="1"/>
+    <col min="21" max="21" width="16.54296875" customWidth="1"/>
+    <col min="22" max="22" width="10.81640625" customWidth="1"/>
     <col min="23" max="23" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>336</v>
+        <v>30</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1558,39 +1558,39 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V2" t="s">
         <v>30</v>
       </c>
-      <c r="O2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>33</v>
-      </c>
-      <c r="R2" t="s">
-        <v>34</v>
-      </c>
-      <c r="S2" t="s">
-        <v>35</v>
-      </c>
-      <c r="T2" t="s">
-        <v>36</v>
-      </c>
-      <c r="U2" t="s">
-        <v>37</v>
-      </c>
-      <c r="V2" t="s">
-        <v>336</v>
-      </c>
       <c r="W2" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>24</v>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>336</v>
+        <v>30</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -1626,37 +1626,37 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" t="s">
+        <v>38</v>
+      </c>
+      <c r="V3" t="s">
         <v>30</v>
       </c>
-      <c r="O3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3" t="s">
-        <v>34</v>
-      </c>
-      <c r="S3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T3" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" t="s">
-        <v>37</v>
-      </c>
-      <c r="V3" t="s">
-        <v>336</v>
-      </c>
       <c r="W3" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1664,16 +1664,16 @@
         <v>10001</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4" t="s">
         <v>29</v>
@@ -1691,63 +1691,63 @@
         <v>779517433</v>
       </c>
       <c r="L4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M4">
         <v>3</v>
       </c>
       <c r="N4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="1">
         <v>10001</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H5">
         <v>34.521169999999998</v>
@@ -1762,43 +1762,43 @@
         <v>993556086</v>
       </c>
       <c r="L5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M5">
         <v>3</v>
       </c>
       <c r="N5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1806,16 +1806,16 @@
         <v>10002</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" t="s">
         <v>29</v>
@@ -1833,63 +1833,63 @@
         <v>753476995</v>
       </c>
       <c r="L6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M6">
         <v>2</v>
       </c>
       <c r="N6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1">
         <v>10002</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H7">
         <v>34.360207000000003</v>
@@ -1904,43 +1904,43 @@
         <v>984996886</v>
       </c>
       <c r="L7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M7">
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1948,16 +1948,16 @@
         <v>10003</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>
@@ -1975,63 +1975,63 @@
         <v>734239083</v>
       </c>
       <c r="L8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M8">
         <v>4</v>
       </c>
       <c r="N8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" s="1">
         <v>10003</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H9">
         <v>34.405692000000002</v>
@@ -2046,43 +2046,43 @@
         <v>675470523</v>
       </c>
       <c r="L9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M9">
         <v>4</v>
       </c>
       <c r="N9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -2090,16 +2090,16 @@
         <v>10004</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
         <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
@@ -2117,63 +2117,63 @@
         <v>937997757</v>
       </c>
       <c r="L10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M10">
         <v>2</v>
       </c>
       <c r="N10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="1">
         <v>10004</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
         <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H11">
         <v>34.287878999999997</v>
@@ -2188,43 +2188,43 @@
         <v>852492117</v>
       </c>
       <c r="L11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M11">
         <v>2</v>
       </c>
       <c r="N11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2232,19 +2232,19 @@
         <v>10005</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H12">
         <v>34.256413999999999</v>
@@ -2259,63 +2259,63 @@
         <v>887311749</v>
       </c>
       <c r="L12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="1">
         <v>10005</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H13">
         <v>34.256413999999999</v>
@@ -2330,43 +2330,43 @@
         <v>658302699</v>
       </c>
       <c r="L13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -2374,19 +2374,19 @@
         <v>10006</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H14">
         <v>34.262476999999997</v>
@@ -2401,63 +2401,63 @@
         <v>915790305</v>
       </c>
       <c r="L14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M14">
         <v>5</v>
       </c>
       <c r="N14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1">
         <v>10006</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H15">
         <v>34.262476999999997</v>
@@ -2472,43 +2472,43 @@
         <v>888439793</v>
       </c>
       <c r="L15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M15">
         <v>5</v>
       </c>
       <c r="N15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -2516,16 +2516,16 @@
         <v>10007</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G16" t="s">
         <v>29</v>
@@ -2543,63 +2543,63 @@
         <v>811552880</v>
       </c>
       <c r="L16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M16">
         <v>2</v>
       </c>
       <c r="N16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1">
         <v>10007</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H17">
         <v>34.192861000000001</v>
@@ -2614,43 +2614,43 @@
         <v>753640112</v>
       </c>
       <c r="L17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M17">
         <v>2</v>
       </c>
       <c r="N17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -2658,16 +2658,16 @@
         <v>10008</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s">
         <v>29</v>
@@ -2685,63 +2685,63 @@
         <v>695325692</v>
       </c>
       <c r="L18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M18">
         <v>2</v>
       </c>
       <c r="N18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="1">
         <v>10008</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H19">
         <v>34.522413999999998</v>
@@ -2756,43 +2756,43 @@
         <v>862899075</v>
       </c>
       <c r="L19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M19">
         <v>2</v>
       </c>
       <c r="N19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -2800,16 +2800,16 @@
         <v>10009</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
         <v>26</v>
       </c>
       <c r="E20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G20" t="s">
         <v>29</v>
@@ -2827,63 +2827,63 @@
         <v>745360421</v>
       </c>
       <c r="L20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M20">
         <v>2</v>
       </c>
       <c r="N20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" s="1">
         <v>10009</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
         <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H21">
         <v>33.998232000000002</v>
@@ -2898,43 +2898,43 @@
         <v>676186831</v>
       </c>
       <c r="L21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M21">
         <v>2</v>
       </c>
       <c r="N21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2942,16 +2942,16 @@
         <v>10010</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
         <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G22" t="s">
         <v>29</v>
@@ -2969,63 +2969,63 @@
         <v>766074745</v>
       </c>
       <c r="L22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M22">
         <v>2</v>
       </c>
       <c r="N22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" s="1">
         <v>10010</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D23" t="s">
         <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H23">
         <v>34.017502</v>
@@ -3040,43 +3040,43 @@
         <v>773606891</v>
       </c>
       <c r="L23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M23">
         <v>2</v>
       </c>
       <c r="N23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R23" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -3084,16 +3084,16 @@
         <v>10011</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
         <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G24" t="s">
         <v>29</v>
@@ -3111,63 +3111,63 @@
         <v>787248921</v>
       </c>
       <c r="L24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M24">
         <v>2</v>
       </c>
       <c r="N24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" s="1">
         <v>10011</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D25" t="s">
         <v>26</v>
       </c>
       <c r="E25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H25">
         <v>33.986607999999997</v>
@@ -3182,43 +3182,43 @@
         <v>878691008</v>
       </c>
       <c r="L25" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M25">
         <v>2</v>
       </c>
       <c r="N25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -3226,16 +3226,16 @@
         <v>10012</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
         <v>26</v>
       </c>
       <c r="E26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G26" t="s">
         <v>29</v>
@@ -3253,63 +3253,63 @@
         <v>838412388</v>
       </c>
       <c r="L26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M26">
         <v>2</v>
       </c>
       <c r="N26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B27" s="1">
         <v>10012</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
         <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H27">
         <v>33.978102999999997</v>
@@ -3324,43 +3324,43 @@
         <v>719952201</v>
       </c>
       <c r="L27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M27">
         <v>2</v>
       </c>
       <c r="N27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -3368,16 +3368,16 @@
         <v>10013</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
         <v>26</v>
       </c>
       <c r="E28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G28" t="s">
         <v>29</v>
@@ -3395,63 +3395,63 @@
         <v>751913644</v>
       </c>
       <c r="L28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M28">
         <v>2</v>
       </c>
       <c r="N28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="1">
         <v>10013</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D29" t="s">
         <v>26</v>
       </c>
       <c r="E29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H29">
         <v>33.953930999999997</v>
@@ -3466,43 +3466,43 @@
         <v>956537434</v>
       </c>
       <c r="L29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M29">
         <v>2</v>
       </c>
       <c r="N29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V29" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -3510,16 +3510,16 @@
         <v>10014</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
         <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G30" t="s">
         <v>29</v>
@@ -3537,63 +3537,63 @@
         <v>965639376</v>
       </c>
       <c r="L30" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M30">
         <v>2</v>
       </c>
       <c r="N30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" s="1">
         <v>10014</v>
       </c>
       <c r="C31" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H31">
         <v>34.027757000000001</v>
@@ -3608,43 +3608,43 @@
         <v>781039430</v>
       </c>
       <c r="L31" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M31">
         <v>2</v>
       </c>
       <c r="N31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U31" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -3652,16 +3652,16 @@
         <v>10015</v>
       </c>
       <c r="C32" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D32" t="s">
         <v>26</v>
       </c>
       <c r="E32" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G32" t="s">
         <v>29</v>
@@ -3679,63 +3679,63 @@
         <v>803062069</v>
       </c>
       <c r="L32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M32">
         <v>2</v>
       </c>
       <c r="N32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1">
         <v>10015</v>
       </c>
       <c r="C33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D33" t="s">
         <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H33">
         <v>33.995612000000001</v>
@@ -3750,63 +3750,63 @@
         <v>731435978</v>
       </c>
       <c r="L33" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M33">
         <v>2</v>
       </c>
       <c r="N33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F34" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G34" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -3815,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>336</v>
+        <v>30</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -3824,57 +3824,57 @@
         <v>0</v>
       </c>
       <c r="N34" t="s">
+        <v>31</v>
+      </c>
+      <c r="O34" t="s">
+        <v>32</v>
+      </c>
+      <c r="P34" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>34</v>
+      </c>
+      <c r="R34" t="s">
+        <v>35</v>
+      </c>
+      <c r="S34" t="s">
+        <v>36</v>
+      </c>
+      <c r="T34" t="s">
+        <v>37</v>
+      </c>
+      <c r="U34" t="s">
+        <v>38</v>
+      </c>
+      <c r="V34" t="s">
         <v>30</v>
       </c>
-      <c r="O34" t="s">
-        <v>31</v>
-      </c>
-      <c r="P34" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>33</v>
-      </c>
-      <c r="R34" t="s">
-        <v>34</v>
-      </c>
-      <c r="S34" t="s">
-        <v>35</v>
-      </c>
-      <c r="T34" t="s">
-        <v>36</v>
-      </c>
-      <c r="U34" t="s">
-        <v>37</v>
-      </c>
-      <c r="V34" t="s">
-        <v>336</v>
-      </c>
       <c r="W34" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B35" s="1">
         <v>10001</v>
       </c>
       <c r="C35" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" t="s">
+        <v>140</v>
+      </c>
+      <c r="G35" t="s">
         <v>138</v>
-      </c>
-      <c r="D35" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" t="s">
-        <v>41</v>
-      </c>
-      <c r="F35" t="s">
-        <v>139</v>
-      </c>
-      <c r="G35" t="s">
-        <v>137</v>
       </c>
       <c r="H35">
         <v>34.521169999999998</v>
@@ -3889,63 +3889,63 @@
         <v>779517433</v>
       </c>
       <c r="L35" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M35">
         <v>3</v>
       </c>
       <c r="N35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="1">
         <v>10002</v>
       </c>
       <c r="C36" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D36" t="s">
         <v>26</v>
       </c>
       <c r="E36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G36" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H36">
         <v>34.360207000000003</v>
@@ -3960,63 +3960,63 @@
         <v>753476995</v>
       </c>
       <c r="L36" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M36">
         <v>2</v>
       </c>
       <c r="N36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P36" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B37" s="1">
         <v>10003</v>
       </c>
       <c r="C37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D37" t="s">
         <v>26</v>
       </c>
       <c r="E37" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G37" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H37">
         <v>34.405692000000002</v>
@@ -4031,63 +4031,63 @@
         <v>734239083</v>
       </c>
       <c r="L37" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M37">
         <v>4</v>
       </c>
       <c r="N37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P37" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q37" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B38" s="1">
         <v>10004</v>
       </c>
       <c r="C38" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
         <v>26</v>
       </c>
       <c r="E38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F38" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H38">
         <v>34.287878999999997</v>
@@ -4102,63 +4102,63 @@
         <v>937997757</v>
       </c>
       <c r="L38" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M38">
         <v>2</v>
       </c>
       <c r="N38" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V38" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B39" s="1">
         <v>10005</v>
       </c>
       <c r="C39" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D39" t="s">
         <v>26</v>
       </c>
       <c r="E39" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F39" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G39" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H39">
         <v>34.256413999999999</v>
@@ -4173,63 +4173,63 @@
         <v>887311749</v>
       </c>
       <c r="L39" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M39">
         <v>1</v>
       </c>
       <c r="N39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B40" s="1">
         <v>10006</v>
       </c>
       <c r="C40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D40" t="s">
         <v>26</v>
       </c>
       <c r="E40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F40" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G40" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H40">
         <v>34.262476999999997</v>
@@ -4244,63 +4244,63 @@
         <v>915790305</v>
       </c>
       <c r="L40" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M40">
         <v>5</v>
       </c>
       <c r="N40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P40" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B41" s="1">
         <v>10007</v>
       </c>
       <c r="C41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D41" t="s">
         <v>26</v>
       </c>
       <c r="E41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F41" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H41">
         <v>34.192861000000001</v>
@@ -4315,63 +4315,63 @@
         <v>811552880</v>
       </c>
       <c r="L41" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M41">
         <v>2</v>
       </c>
       <c r="N41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O41" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P41" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S41" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B42" s="1">
         <v>10008</v>
       </c>
       <c r="C42" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D42" t="s">
         <v>26</v>
       </c>
       <c r="E42" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H42">
         <v>34.522413999999998</v>
@@ -4386,63 +4386,63 @@
         <v>695325692</v>
       </c>
       <c r="L42" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M42">
         <v>2</v>
       </c>
       <c r="N42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O42" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T42" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V42" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B43" s="1">
         <v>10009</v>
       </c>
       <c r="C43" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D43" t="s">
         <v>26</v>
       </c>
       <c r="E43" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F43" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H43">
         <v>33.998232000000002</v>
@@ -4457,63 +4457,63 @@
         <v>745360421</v>
       </c>
       <c r="L43" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M43">
         <v>2</v>
       </c>
       <c r="N43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O43" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R43" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U43" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V43" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B44" s="1">
         <v>10010</v>
       </c>
       <c r="C44" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D44" t="s">
         <v>26</v>
       </c>
       <c r="E44" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F44" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H44">
         <v>34.017502</v>
@@ -4528,63 +4528,63 @@
         <v>766074745</v>
       </c>
       <c r="L44" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M44">
         <v>2</v>
       </c>
       <c r="N44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O44" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S44" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U44" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V44" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B45" s="1">
         <v>10011</v>
       </c>
       <c r="C45" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D45" t="s">
         <v>26</v>
       </c>
       <c r="E45" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F45" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H45">
         <v>33.986607999999997</v>
@@ -4599,63 +4599,63 @@
         <v>787248921</v>
       </c>
       <c r="L45" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M45">
         <v>2</v>
       </c>
       <c r="N45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O45" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T45" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V45" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B46" s="1">
         <v>10012</v>
       </c>
       <c r="C46" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D46" t="s">
         <v>26</v>
       </c>
       <c r="E46" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H46">
         <v>33.978102999999997</v>
@@ -4670,63 +4670,63 @@
         <v>838412388</v>
       </c>
       <c r="L46" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M46">
         <v>2</v>
       </c>
       <c r="N46" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O46" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P46" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R46" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U46" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V46" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B47" s="1">
         <v>10013</v>
       </c>
       <c r="C47" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D47" t="s">
         <v>26</v>
       </c>
       <c r="E47" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F47" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H47">
         <v>33.953930999999997</v>
@@ -4741,63 +4741,63 @@
         <v>751913644</v>
       </c>
       <c r="L47" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M47">
         <v>2</v>
       </c>
       <c r="N47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O47" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P47" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R47" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S47" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T47" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U47" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B48" s="1">
         <v>10014</v>
       </c>
       <c r="C48" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D48" t="s">
         <v>26</v>
       </c>
       <c r="E48" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H48">
         <v>34.027757000000001</v>
@@ -4812,63 +4812,63 @@
         <v>965639376</v>
       </c>
       <c r="L48" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M48">
         <v>2</v>
       </c>
       <c r="N48" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O48" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P48" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R48" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S48" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T48" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V48" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B49" s="1">
         <v>10015</v>
       </c>
       <c r="C49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D49" t="s">
         <v>26</v>
       </c>
       <c r="E49" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H49">
         <v>33.995612000000001</v>
@@ -4883,63 +4883,63 @@
         <v>803062069</v>
       </c>
       <c r="L49" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M49">
         <v>2</v>
       </c>
       <c r="N49" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P49" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S49" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T49" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V49" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C50" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D50" t="s">
         <v>26</v>
       </c>
       <c r="E50" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G50" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -4948,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>336</v>
+        <v>30</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -4957,57 +4957,57 @@
         <v>0</v>
       </c>
       <c r="N50" t="s">
+        <v>31</v>
+      </c>
+      <c r="O50" t="s">
+        <v>32</v>
+      </c>
+      <c r="P50" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>34</v>
+      </c>
+      <c r="R50" t="s">
+        <v>35</v>
+      </c>
+      <c r="S50" t="s">
+        <v>36</v>
+      </c>
+      <c r="T50" t="s">
+        <v>37</v>
+      </c>
+      <c r="U50" t="s">
+        <v>38</v>
+      </c>
+      <c r="V50" t="s">
         <v>30</v>
       </c>
-      <c r="O50" t="s">
-        <v>31</v>
-      </c>
-      <c r="P50" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>33</v>
-      </c>
-      <c r="R50" t="s">
-        <v>34</v>
-      </c>
-      <c r="S50" t="s">
-        <v>35</v>
-      </c>
-      <c r="T50" t="s">
-        <v>36</v>
-      </c>
-      <c r="U50" t="s">
-        <v>37</v>
-      </c>
-      <c r="V50" t="s">
-        <v>336</v>
-      </c>
       <c r="W50" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="1">
         <v>10001</v>
       </c>
       <c r="C51" t="s">
+        <v>196</v>
+      </c>
+      <c r="D51" t="s">
+        <v>26</v>
+      </c>
+      <c r="E51" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" t="s">
+        <v>197</v>
+      </c>
+      <c r="G51" t="s">
         <v>195</v>
-      </c>
-      <c r="D51" t="s">
-        <v>26</v>
-      </c>
-      <c r="E51" t="s">
-        <v>41</v>
-      </c>
-      <c r="F51" t="s">
-        <v>196</v>
-      </c>
-      <c r="G51" t="s">
-        <v>194</v>
       </c>
       <c r="H51">
         <v>34.521169999999998</v>
@@ -5022,63 +5022,63 @@
         <v>779517433</v>
       </c>
       <c r="L51" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M51">
         <v>3</v>
       </c>
       <c r="N51" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q51" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R51" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S51" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V51" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W51" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="1">
         <v>10002</v>
       </c>
       <c r="C52" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D52" t="s">
         <v>26</v>
       </c>
       <c r="E52" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F52" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G52" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H52">
         <v>34.360207000000003</v>
@@ -5093,63 +5093,63 @@
         <v>753476995</v>
       </c>
       <c r="L52" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M52">
         <v>2</v>
       </c>
       <c r="N52" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P52" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R52" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S52" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T52" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B53" s="1">
         <v>10003</v>
       </c>
       <c r="C53" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D53" t="s">
         <v>26</v>
       </c>
       <c r="E53" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F53" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G53" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H53">
         <v>34.405692000000002</v>
@@ -5164,63 +5164,63 @@
         <v>734239083</v>
       </c>
       <c r="L53" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M53">
         <v>4</v>
       </c>
       <c r="N53" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O53" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P53" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T53" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V53" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W53" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B54" s="1">
         <v>10004</v>
       </c>
       <c r="C54" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D54" t="s">
         <v>26</v>
       </c>
       <c r="E54" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F54" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G54" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H54">
         <v>34.287878999999997</v>
@@ -5235,63 +5235,63 @@
         <v>937997757</v>
       </c>
       <c r="L54" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M54">
         <v>2</v>
       </c>
       <c r="N54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q54" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R54" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W54" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B55" s="1">
         <v>10005</v>
       </c>
       <c r="C55" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D55" t="s">
         <v>26</v>
       </c>
       <c r="E55" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F55" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G55" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H55">
         <v>34.256413999999999</v>
@@ -5306,63 +5306,63 @@
         <v>887311749</v>
       </c>
       <c r="L55" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O55" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P55" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q55" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T55" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U55" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W55" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B56" s="1">
         <v>10006</v>
       </c>
       <c r="C56" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D56" t="s">
         <v>26</v>
       </c>
       <c r="E56" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F56" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G56" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H56">
         <v>34.262476999999997</v>
@@ -5377,63 +5377,63 @@
         <v>915790305</v>
       </c>
       <c r="L56" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M56">
         <v>5</v>
       </c>
       <c r="N56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P56" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R56" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U56" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V56" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W56" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B57" s="1">
         <v>10007</v>
       </c>
       <c r="C57" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D57" t="s">
         <v>26</v>
       </c>
       <c r="E57" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F57" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H57">
         <v>34.192861000000001</v>
@@ -5448,63 +5448,63 @@
         <v>811552880</v>
       </c>
       <c r="L57" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M57">
         <v>2</v>
       </c>
       <c r="N57" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O57" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P57" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q57" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S57" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V57" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W57" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B58" s="1">
         <v>10008</v>
       </c>
       <c r="C58" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D58" t="s">
         <v>26</v>
       </c>
       <c r="E58" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F58" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H58">
         <v>34.522413999999998</v>
@@ -5519,63 +5519,63 @@
         <v>695325692</v>
       </c>
       <c r="L58" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M58">
         <v>2</v>
       </c>
       <c r="N58" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O58" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P58" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R58" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S58" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T58" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V58" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W58" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B59" s="1">
         <v>10009</v>
       </c>
       <c r="C59" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D59" t="s">
         <v>26</v>
       </c>
       <c r="E59" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F59" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H59">
         <v>33.998232000000002</v>
@@ -5590,63 +5590,63 @@
         <v>745360421</v>
       </c>
       <c r="L59" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M59">
         <v>2</v>
       </c>
       <c r="N59" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O59" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P59" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q59" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R59" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S59" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U59" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V59" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W59" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B60" s="1">
         <v>10010</v>
       </c>
       <c r="C60" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D60" t="s">
         <v>26</v>
       </c>
       <c r="E60" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F60" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H60">
         <v>34.017502</v>
@@ -5661,63 +5661,63 @@
         <v>766074745</v>
       </c>
       <c r="L60" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M60">
         <v>2</v>
       </c>
       <c r="N60" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P60" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q60" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R60" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S60" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U60" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W60" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B61" s="1">
         <v>10011</v>
       </c>
       <c r="C61" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D61" t="s">
         <v>26</v>
       </c>
       <c r="E61" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F61" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H61">
         <v>33.986607999999997</v>
@@ -5732,63 +5732,63 @@
         <v>787248921</v>
       </c>
       <c r="L61" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M61">
         <v>2</v>
       </c>
       <c r="N61" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O61" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q61" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S61" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T61" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U61" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V61" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W61" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B62" s="1">
         <v>10012</v>
       </c>
       <c r="C62" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D62" t="s">
         <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F62" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H62">
         <v>33.978102999999997</v>
@@ -5803,63 +5803,63 @@
         <v>838412388</v>
       </c>
       <c r="L62" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M62">
         <v>2</v>
       </c>
       <c r="N62" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O62" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P62" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q62" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R62" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S62" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T62" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U62" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V62" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W62" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B63" s="1">
         <v>10013</v>
       </c>
       <c r="C63" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D63" t="s">
         <v>26</v>
       </c>
       <c r="E63" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F63" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H63">
         <v>33.953930999999997</v>
@@ -5874,63 +5874,63 @@
         <v>751913644</v>
       </c>
       <c r="L63" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M63">
         <v>2</v>
       </c>
       <c r="N63" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O63" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P63" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q63" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R63" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T63" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V63" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W63" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B64" s="1">
         <v>10014</v>
       </c>
       <c r="C64" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D64" t="s">
         <v>26</v>
       </c>
       <c r="E64" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F64" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H64">
         <v>34.027757000000001</v>
@@ -5945,63 +5945,63 @@
         <v>965639376</v>
       </c>
       <c r="L64" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M64">
         <v>2</v>
       </c>
       <c r="N64" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O64" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P64" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q64" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S64" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T64" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V64" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W64" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B65" s="1">
         <v>10015</v>
       </c>
       <c r="C65" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D65" t="s">
         <v>26</v>
       </c>
       <c r="E65" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F65" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H65">
         <v>33.995612000000001</v>
@@ -6016,63 +6016,63 @@
         <v>803062069</v>
       </c>
       <c r="L65" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M65">
         <v>2</v>
       </c>
       <c r="N65" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O65" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P65" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q65" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R65" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T65" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U65" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V65" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W65" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D66" t="s">
         <v>26</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F66" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G66" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -6081,7 +6081,7 @@
         <v>0</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>336</v>
+        <v>30</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -6090,57 +6090,57 @@
         <v>0</v>
       </c>
       <c r="N66" t="s">
+        <v>31</v>
+      </c>
+      <c r="O66" t="s">
+        <v>32</v>
+      </c>
+      <c r="P66" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>34</v>
+      </c>
+      <c r="R66" t="s">
+        <v>35</v>
+      </c>
+      <c r="S66" t="s">
+        <v>36</v>
+      </c>
+      <c r="T66" t="s">
+        <v>37</v>
+      </c>
+      <c r="U66" t="s">
+        <v>38</v>
+      </c>
+      <c r="V66" t="s">
         <v>30</v>
       </c>
-      <c r="O66" t="s">
-        <v>31</v>
-      </c>
-      <c r="P66" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>33</v>
-      </c>
-      <c r="R66" t="s">
-        <v>34</v>
-      </c>
-      <c r="S66" t="s">
-        <v>35</v>
-      </c>
-      <c r="T66" t="s">
-        <v>36</v>
-      </c>
-      <c r="U66" t="s">
-        <v>37</v>
-      </c>
-      <c r="V66" t="s">
-        <v>336</v>
-      </c>
       <c r="W66" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B67" s="1">
         <v>10001</v>
       </c>
       <c r="C67" t="s">
+        <v>253</v>
+      </c>
+      <c r="D67" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" t="s">
+        <v>42</v>
+      </c>
+      <c r="F67" t="s">
+        <v>254</v>
+      </c>
+      <c r="G67" t="s">
         <v>252</v>
-      </c>
-      <c r="D67" t="s">
-        <v>26</v>
-      </c>
-      <c r="E67" t="s">
-        <v>41</v>
-      </c>
-      <c r="F67" t="s">
-        <v>253</v>
-      </c>
-      <c r="G67" t="s">
-        <v>251</v>
       </c>
       <c r="H67">
         <v>34.521169999999998</v>
@@ -6155,63 +6155,63 @@
         <v>779517433</v>
       </c>
       <c r="L67" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M67">
         <v>3</v>
       </c>
       <c r="N67" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O67" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P67" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q67" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R67" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S67" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T67" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U67" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V67" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W67" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B68" s="1">
         <v>10002</v>
       </c>
       <c r="C68" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D68" t="s">
         <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F68" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G68" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H68">
         <v>34.360207000000003</v>
@@ -6226,63 +6226,63 @@
         <v>753476995</v>
       </c>
       <c r="L68" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M68">
         <v>2</v>
       </c>
       <c r="N68" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O68" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P68" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q68" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R68" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T68" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U68" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V68" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W68" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B69" s="1">
         <v>10003</v>
       </c>
       <c r="C69" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D69" t="s">
         <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F69" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G69" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H69">
         <v>34.405692000000002</v>
@@ -6297,63 +6297,63 @@
         <v>734239083</v>
       </c>
       <c r="L69" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M69">
         <v>4</v>
       </c>
       <c r="N69" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O69" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P69" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q69" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R69" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S69" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U69" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V69" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W69" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B70" s="1">
         <v>10004</v>
       </c>
       <c r="C70" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D70" t="s">
         <v>26</v>
       </c>
       <c r="E70" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F70" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G70" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H70">
         <v>34.287878999999997</v>
@@ -6368,63 +6368,63 @@
         <v>937997757</v>
       </c>
       <c r="L70" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M70">
         <v>2</v>
       </c>
       <c r="N70" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O70" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P70" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q70" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R70" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S70" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T70" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U70" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V70" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W70" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B71" s="1">
         <v>10005</v>
       </c>
       <c r="C71" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D71" t="s">
         <v>26</v>
       </c>
       <c r="E71" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F71" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G71" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H71">
         <v>34.256413999999999</v>
@@ -6439,63 +6439,63 @@
         <v>887311749</v>
       </c>
       <c r="L71" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M71">
         <v>1</v>
       </c>
       <c r="N71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O71" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P71" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q71" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R71" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T71" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U71" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W71" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B72" s="1">
         <v>10006</v>
       </c>
       <c r="C72" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D72" t="s">
         <v>26</v>
       </c>
       <c r="E72" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F72" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G72" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H72">
         <v>34.262476999999997</v>
@@ -6510,63 +6510,63 @@
         <v>915790305</v>
       </c>
       <c r="L72" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M72">
         <v>5</v>
       </c>
       <c r="N72" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O72" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P72" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q72" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R72" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S72" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T72" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U72" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W72" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B73" s="1">
         <v>10007</v>
       </c>
       <c r="C73" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D73" t="s">
         <v>26</v>
       </c>
       <c r="E73" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F73" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H73">
         <v>34.192861000000001</v>
@@ -6581,63 +6581,63 @@
         <v>811552880</v>
       </c>
       <c r="L73" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M73">
         <v>2</v>
       </c>
       <c r="N73" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O73" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P73" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q73" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R73" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S73" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T73" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U73" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V73" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B74" s="1">
         <v>10008</v>
       </c>
       <c r="C74" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D74" t="s">
         <v>26</v>
       </c>
       <c r="E74" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F74" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H74">
         <v>34.522413999999998</v>
@@ -6652,63 +6652,63 @@
         <v>695325692</v>
       </c>
       <c r="L74" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M74">
         <v>2</v>
       </c>
       <c r="N74" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P74" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q74" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R74" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S74" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T74" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U74" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V74" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W74" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B75" s="1">
         <v>10009</v>
       </c>
       <c r="C75" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D75" t="s">
         <v>26</v>
       </c>
       <c r="E75" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F75" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H75">
         <v>33.998232000000002</v>
@@ -6723,63 +6723,63 @@
         <v>745360421</v>
       </c>
       <c r="L75" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M75">
         <v>2</v>
       </c>
       <c r="N75" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O75" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P75" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q75" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R75" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S75" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T75" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U75" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V75" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W75" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B76" s="1">
         <v>10010</v>
       </c>
       <c r="C76" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D76" t="s">
         <v>26</v>
       </c>
       <c r="E76" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F76" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H76">
         <v>34.017502</v>
@@ -6794,63 +6794,63 @@
         <v>766074745</v>
       </c>
       <c r="L76" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M76">
         <v>2</v>
       </c>
       <c r="N76" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O76" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P76" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q76" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R76" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S76" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T76" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U76" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V76" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W76" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B77" s="1">
         <v>10011</v>
       </c>
       <c r="C77" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D77" t="s">
         <v>26</v>
       </c>
       <c r="E77" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F77" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H77">
         <v>33.986607999999997</v>
@@ -6865,63 +6865,63 @@
         <v>787248921</v>
       </c>
       <c r="L77" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M77">
         <v>2</v>
       </c>
       <c r="N77" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O77" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P77" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q77" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R77" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S77" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T77" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U77" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V77" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W77" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B78" s="1">
         <v>10012</v>
       </c>
       <c r="C78" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D78" t="s">
         <v>26</v>
       </c>
       <c r="E78" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F78" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H78">
         <v>33.978102999999997</v>
@@ -6936,63 +6936,63 @@
         <v>838412388</v>
       </c>
       <c r="L78" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M78">
         <v>2</v>
       </c>
       <c r="N78" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O78" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P78" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q78" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S78" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U78" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V78" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W78" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B79" s="1">
         <v>10013</v>
       </c>
       <c r="C79" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D79" t="s">
         <v>26</v>
       </c>
       <c r="E79" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F79" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H79">
         <v>33.953930999999997</v>
@@ -7007,63 +7007,63 @@
         <v>751913644</v>
       </c>
       <c r="L79" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M79">
         <v>2</v>
       </c>
       <c r="N79" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O79" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P79" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q79" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R79" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S79" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T79" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U79" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V79" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W79" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B80" s="1">
         <v>10014</v>
       </c>
       <c r="C80" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D80" t="s">
         <v>26</v>
       </c>
       <c r="E80" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F80" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H80">
         <v>34.027757000000001</v>
@@ -7078,63 +7078,63 @@
         <v>965639376</v>
       </c>
       <c r="L80" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M80">
         <v>2</v>
       </c>
       <c r="N80" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O80" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P80" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q80" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R80" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S80" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U80" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V80" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W80" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B81" s="1">
         <v>10015</v>
       </c>
       <c r="C81" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D81" t="s">
         <v>26</v>
       </c>
       <c r="E81" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F81" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H81">
         <v>33.995612000000001</v>
@@ -7149,63 +7149,63 @@
         <v>803062069</v>
       </c>
       <c r="L81" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M81">
         <v>2</v>
       </c>
       <c r="N81" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O81" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P81" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q81" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R81" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S81" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T81" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U81" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V81" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W81" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B82">
         <v>10137</v>
       </c>
       <c r="C82" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D82" t="s">
         <v>26</v>
       </c>
       <c r="E82" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F82" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G82" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H82">
         <v>34.360207000000003</v>
@@ -7220,7 +7220,7 @@
         <v>753476995</v>
       </c>
       <c r="L82" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M82">
         <v>2</v>
@@ -7244,39 +7244,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T82" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U82" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V82" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="W82" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B83">
         <v>10138</v>
       </c>
       <c r="C83" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D83" t="s">
         <v>26</v>
       </c>
       <c r="E83" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F83" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G83" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H83">
         <v>34.405692000000002</v>
@@ -7291,7 +7291,7 @@
         <v>734239083</v>
       </c>
       <c r="L83" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M83">
         <v>4</v>
@@ -7315,39 +7315,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T83" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U83" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V83" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W83" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B84">
         <v>10139</v>
       </c>
       <c r="C84" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D84" t="s">
         <v>26</v>
       </c>
       <c r="E84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F84" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G84" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H84">
         <v>34.256413999999999</v>
@@ -7362,7 +7362,7 @@
         <v>887311749</v>
       </c>
       <c r="L84" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M84">
         <v>1</v>
@@ -7386,39 +7386,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T84" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U84" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V84" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="W84" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B85">
         <v>10140</v>
       </c>
       <c r="C85" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D85" t="s">
         <v>26</v>
       </c>
       <c r="E85" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F85" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G85" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H85">
         <v>34.262476999999997</v>
@@ -7433,7 +7433,7 @@
         <v>915790305</v>
       </c>
       <c r="L85" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M85">
         <v>5</v>
@@ -7457,39 +7457,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T85" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U85" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W85" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B86">
         <v>10141</v>
       </c>
       <c r="C86" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D86" t="s">
         <v>26</v>
       </c>
       <c r="E86" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F86" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G86" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H86">
         <v>34.192861000000001</v>
@@ -7504,7 +7504,7 @@
         <v>811552880</v>
       </c>
       <c r="L86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M86">
         <v>2</v>
@@ -7528,39 +7528,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T86" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U86" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V86" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W86" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B87">
         <v>10142</v>
       </c>
       <c r="C87" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D87" t="s">
         <v>26</v>
       </c>
       <c r="E87" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F87" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G87" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H87">
         <v>33.998232000000002</v>
@@ -7575,7 +7575,7 @@
         <v>745360421</v>
       </c>
       <c r="L87" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M87">
         <v>2</v>
@@ -7599,39 +7599,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T87" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U87" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V87" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W87" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B88">
         <v>10143</v>
       </c>
       <c r="C88" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D88" t="s">
         <v>26</v>
       </c>
       <c r="E88" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F88" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G88" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H88">
         <v>34.017502</v>
@@ -7646,7 +7646,7 @@
         <v>766074745</v>
       </c>
       <c r="L88" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M88">
         <v>2</v>
@@ -7670,39 +7670,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T88" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U88" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V88" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W88" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B89">
         <v>10144</v>
       </c>
       <c r="C89" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D89" t="s">
         <v>26</v>
       </c>
       <c r="E89" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F89" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G89" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H89">
         <v>33.986607999999997</v>
@@ -7717,7 +7717,7 @@
         <v>787248921</v>
       </c>
       <c r="L89" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M89">
         <v>2</v>
@@ -7741,39 +7741,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T89" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U89" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V89" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W89" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B90">
         <v>10145</v>
       </c>
       <c r="C90" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D90" t="s">
         <v>26</v>
       </c>
       <c r="E90" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F90" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G90" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H90">
         <v>33.978102999999997</v>
@@ -7788,7 +7788,7 @@
         <v>838412388</v>
       </c>
       <c r="L90" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M90">
         <v>2</v>
@@ -7812,39 +7812,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T90" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U90" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W90" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B91">
         <v>10146</v>
       </c>
       <c r="C91" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D91" t="s">
         <v>26</v>
       </c>
       <c r="E91" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F91" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G91" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H91">
         <v>33.953930999999997</v>
@@ -7859,7 +7859,7 @@
         <v>751913644</v>
       </c>
       <c r="L91" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M91">
         <v>2</v>
@@ -7883,39 +7883,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T91" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U91" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V91" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="W91" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B92">
         <v>10147</v>
       </c>
       <c r="C92" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D92" t="s">
         <v>26</v>
       </c>
       <c r="E92" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F92" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G92" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H92">
         <v>34.027757000000001</v>
@@ -7930,7 +7930,7 @@
         <v>965639376</v>
       </c>
       <c r="L92" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M92">
         <v>2</v>
@@ -7954,39 +7954,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T92" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U92" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="W92" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B93">
         <v>10148</v>
       </c>
       <c r="C93" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D93" t="s">
         <v>26</v>
       </c>
       <c r="E93" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F93" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G93" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H93">
         <v>12.89515492</v>
@@ -8001,7 +8001,7 @@
         <v>779517433</v>
       </c>
       <c r="L93" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M93">
         <v>3</v>
@@ -8025,39 +8025,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T93" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U93" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V93" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W93" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B94">
         <v>10149</v>
       </c>
       <c r="C94" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D94" t="s">
         <v>26</v>
       </c>
       <c r="E94" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F94" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G94" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H94">
         <v>12.89515492</v>
@@ -8072,7 +8072,7 @@
         <v>937997757</v>
       </c>
       <c r="L94" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M94">
         <v>2</v>
@@ -8096,39 +8096,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T94" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U94" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V94" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="W94" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B95">
         <v>10150</v>
       </c>
       <c r="C95" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D95" t="s">
         <v>26</v>
       </c>
       <c r="E95" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F95" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G95" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H95">
         <v>33.995612000000001</v>
@@ -8143,7 +8143,7 @@
         <v>803062069</v>
       </c>
       <c r="L95" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M95">
         <v>2</v>
@@ -8167,39 +8167,39 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="T95" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U95" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V95" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="W95" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B96">
         <v>10151</v>
       </c>
       <c r="C96" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D96" t="s">
         <v>26</v>
       </c>
       <c r="E96" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F96" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G96" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H96">
         <v>78.547799999999995</v>
@@ -8214,7 +8214,7 @@
         <v>9663089998</v>
       </c>
       <c r="L96" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M96">
         <v>0</v>
@@ -8238,16 +8238,16 @@
         <v>0</v>
       </c>
       <c r="T96" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="U96" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V96" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="W96" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EB7640-6F24-45FA-8904-563DAEF53761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80ECEB41-B1C5-4D1D-92DF-49C930FAD94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="7740" windowWidth="14610" windowHeight="7845" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>lang_code</t>
   </si>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>URE</t>
+  </si>
+  <si>
+    <t>UPO</t>
   </si>
 </sst>
 </file>
@@ -154,7 +157,7 @@
       <b/>
       <sz val="11"/>
       <name val="Cambria"/>
-      <charset val="1"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -642,8 +645,8 @@
       <c r="I2">
         <v>134.58000000000001</v>
       </c>
-      <c r="J2" s="2">
-        <v>14022</v>
+      <c r="J2" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="K2">
         <v>411111111</v>

--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80ECEB41-B1C5-4D1D-92DF-49C930FAD94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD12540C-B31A-4B2E-B3D8-01E33A3C6823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -132,13 +127,13 @@
     <t>The High Street</t>
   </si>
   <si>
-    <t>(GTM+11:00) AUSTRALIAN EASTERN STANDARD TIME</t>
-  </si>
-  <si>
     <t>URE</t>
   </si>
   <si>
     <t>UPO</t>
+  </si>
+  <si>
+    <t>(GTM+01:00) CENTRAL EUROPEAN TIME</t>
   </si>
 </sst>
 </file>
@@ -195,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -211,6 +206,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -639,14 +636,14 @@
       <c r="E2" t="s">
         <v>34</v>
       </c>
-      <c r="H2">
-        <v>-22.2333</v>
-      </c>
-      <c r="I2">
-        <v>134.58000000000001</v>
+      <c r="H2" s="7">
+        <v>34.521169999999998</v>
+      </c>
+      <c r="I2" s="7">
+        <v>-6.4532749999999997</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K2">
         <v>411111111</v>
@@ -675,14 +672,14 @@
       <c r="S2" t="s">
         <v>27</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="U2" t="s">
         <v>35</v>
       </c>
-      <c r="U2" t="s">
-        <v>36</v>
-      </c>
       <c r="V2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>28</v>

--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD12540C-B31A-4B2E-B3D8-01E33A3C6823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195A0B65-0120-49AA-88FA-C6DE9132C57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>lang_code</t>
   </si>
@@ -118,9 +118,6 @@
     <t>17:00:00</t>
   </si>
   <si>
-    <t>John Smith</t>
-  </si>
-  <si>
     <t>Utopian Centre</t>
   </si>
   <si>
@@ -134,6 +131,9 @@
   </si>
   <si>
     <t>(GTM+01:00) CENTRAL EUROPEAN TIME</t>
+  </si>
+  <si>
+    <t>UPR</t>
   </si>
 </sst>
 </file>
@@ -190,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -206,8 +206,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -628,28 +626,22 @@
         <v>10001</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" s="7">
+        <v>33</v>
+      </c>
+      <c r="H2">
         <v>34.521169999999998</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2">
         <v>-6.4532749999999997</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2">
-        <v>411111111</v>
-      </c>
-      <c r="L2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M2">
         <v>3</v>
@@ -672,14 +664,14 @@
       <c r="S2" t="s">
         <v>27</v>
       </c>
-      <c r="T2" s="8" t="s">
+      <c r="T2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" t="s">
         <v>37</v>
-      </c>
-      <c r="U2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V2" t="s">
-        <v>35</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>28</v>

--- a/mosip_master/xlsx/registration_center.xlsx
+++ b/mosip_master/xlsx/registration_center.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195A0B65-0120-49AA-88FA-C6DE9132C57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B34BFBB-BF93-492D-A9A0-35867052E57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>lang_code</t>
   </si>
@@ -115,12 +115,6 @@
     <t>9:00:00</t>
   </si>
   <si>
-    <t>17:00:00</t>
-  </si>
-  <si>
-    <t>Utopian Centre</t>
-  </si>
-  <si>
     <t>The High Street</t>
   </si>
   <si>
@@ -134,6 +128,9 @@
   </si>
   <si>
     <t>UPR</t>
+  </si>
+  <si>
+    <t>Utopian Registration Centre</t>
   </si>
 </sst>
 </file>
@@ -626,13 +623,13 @@
         <v>10001</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H2">
         <v>34.521169999999998</v>
@@ -641,7 +638,7 @@
         <v>-6.4532749999999997</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M2">
         <v>3</v>
@@ -655,8 +652,8 @@
       <c r="P2" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" t="s">
-        <v>31</v>
+      <c r="Q2" s="6">
+        <v>0.75</v>
       </c>
       <c r="R2" t="s">
         <v>26</v>
@@ -665,13 +662,13 @@
         <v>27</v>
       </c>
       <c r="T2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="U2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="V2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>28</v>
